--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.15</v>
+        <v>3.26</v>
       </c>
       <c r="C2" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="E2" t="n">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0292</v>
+        <v>-0.029</v>
       </c>
       <c r="H2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="I2" t="n">
-        <v>2.87</v>
+        <v>2.99</v>
       </c>
       <c r="J2" t="n">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="K2" t="n">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="L2" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="M2" t="n">
-        <v>3.22</v>
+        <v>3.31</v>
       </c>
       <c r="N2" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.31</v>
+        <v>3.41</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,18 +692,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -716,55 +716,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="D3" t="n">
         <v>3.12</v>
       </c>
       <c r="E3" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.09</v>
+        <v>0.09</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.029</v>
+        <v>0.028</v>
       </c>
       <c r="H3" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="J3" t="n">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="K3" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="L3" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="M3" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="O3" t="n">
-        <v>3.41</v>
+        <v>3.48</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,19 +776,19 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -798,57 +802,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="C4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E4" t="n">
         <v>3.25</v>
       </c>
-      <c r="D4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.23</v>
-      </c>
       <c r="F4" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0062</v>
       </c>
       <c r="H4" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="K4" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="L4" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="M4" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N4" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>3.37</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,7 +863,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -880,78 +884,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C5" t="n">
         <v>3.28</v>
       </c>
-      <c r="C5" t="n">
-        <v>3.34</v>
-      </c>
       <c r="D5" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="E5" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0326</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="J5" t="n">
         <v>3.14</v>
       </c>
       <c r="K5" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="M5" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -964,77 +966,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="C6" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="D6" t="n">
         <v>3.14</v>
       </c>
       <c r="E6" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0235</v>
       </c>
       <c r="H6" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="J6" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N6" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1048,57 +1052,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="C7" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="D7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.14</v>
       </c>
-      <c r="E7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.98</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="L7" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="O7" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1109,93 +1113,97 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="C8" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="D8" t="n">
         <v>3.2</v>
       </c>
       <c r="E8" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="F8" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0379</v>
+        <v>-0.0335</v>
       </c>
       <c r="H8" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="I8" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="J8" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="K8" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L8" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="N8" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
@@ -1203,93 +1211,89 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="C9" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="E9" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0155</v>
       </c>
       <c r="H9" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="I9" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="J9" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="K9" t="n">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="L9" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="M9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.43</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.54</v>
-      </c>
       <c r="O9" t="n">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1304,57 +1308,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="C10" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="D10" t="n">
         <v>3.16</v>
       </c>
       <c r="E10" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0296</v>
       </c>
       <c r="H10" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I10" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="J10" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>3.11</v>
       </c>
       <c r="L10" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N10" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,21 +1366,23 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1388,57 +1394,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="C11" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D11" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="E11" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0296</v>
+        <v>-0.0168</v>
       </c>
       <c r="H11" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I11" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K11" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="L11" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="M11" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O11" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,23 +1452,21 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1474,57 +1478,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M12" t="n">
         <v>3.26</v>
       </c>
-      <c r="C12" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N12" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1537,7 +1541,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1558,58 +1562,58 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3.21</v>
       </c>
       <c r="C13" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D13" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J13" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K13" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L13" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M13" t="n">
         <v>3.23</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N13" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O13" t="n">
         <v>3.29</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
@@ -1618,17 +1622,19 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1640,59 +1646,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C14" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D14" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E14" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I14" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J14" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K14" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M14" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N14" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O14" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1705,7 +1707,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1731,50 +1733,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C15" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D15" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H15" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I15" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J15" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K15" t="n">
         <v>3.2</v>
       </c>
       <c r="L15" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M15" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N15" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O15" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1784,19 +1786,19 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1808,76 +1810,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C16" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E16" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H16" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I16" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J16" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L16" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M16" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.33</v>
       </c>
-      <c r="N16" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O16" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1885,81 +1893,73 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C17" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D17" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E17" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H17" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I17" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J17" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.14</v>
       </c>
-      <c r="L17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N17" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O17" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1983,50 +1983,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C18" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K18" t="n">
         <v>2.87</v>
       </c>
-      <c r="E18" t="n">
+      <c r="L18" t="n">
         <v>2.94</v>
       </c>
-      <c r="F18" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M18" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N18" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2039,7 +2039,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2063,14 +2063,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C19" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2.95</v>
       </c>
       <c r="D19" t="n">
         <v>2.85</v>
@@ -2079,34 +2079,34 @@
         <v>2.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H19" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I19" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J19" t="n">
         <v>2.79</v>
       </c>
       <c r="K19" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L19" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N19" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2114,14 +2114,12 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2138,55 +2136,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C20" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D20" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H20" t="n">
         <v>0.08</v>
       </c>
       <c r="I20" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J20" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K20" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L20" t="n">
         <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O20" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2194,16 +2196,20 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2218,63 +2224,65 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2.92</v>
       </c>
       <c r="C21" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D21" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E21" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I21" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J21" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K21" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M21" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N21" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O21" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
@@ -2283,12 +2291,12 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2304,81 +2312,77 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C22" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D22" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E22" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H22" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K22" t="n">
         <v>2.79</v>
       </c>
-      <c r="J22" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L22" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M22" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N22" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2392,76 +2396,78 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C23" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D23" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E23" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H23" t="n">
         <v>0.08</v>
       </c>
       <c r="I23" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J23" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K23" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L23" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M23" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O23" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2474,81 +2480,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C24" t="n">
         <v>2.91</v>
       </c>
       <c r="D24" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E24" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H24" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J24" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K24" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L24" t="n">
         <v>2.87</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2.9</v>
       </c>
-      <c r="M24" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N24" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O24" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2560,43 +2560,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C25" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D25" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E25" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I25" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J25" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K25" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L25" t="n">
         <v>2.87</v>
@@ -2608,7 +2612,7 @@
         <v>2.93</v>
       </c>
       <c r="O25" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2621,7 +2625,7 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2629,8 +2633,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2642,57 +2648,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C26" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D26" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E26" t="n">
         <v>2.92</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H26" t="n">
         <v>0.09</v>
       </c>
       <c r="I26" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J26" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K26" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L26" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N26" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O26" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2705,7 +2711,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2713,10 +2719,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2728,57 +2732,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C27" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D27" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E27" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H27" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I27" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J27" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K27" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L27" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M27" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N27" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O27" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2786,18 +2790,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2810,72 +2814,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C28" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D28" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E28" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H28" t="n">
         <v>0.1</v>
       </c>
       <c r="I28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K28" t="n">
         <v>2.82</v>
       </c>
-      <c r="J28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L28" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M28" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2899,67 +2903,65 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M29" t="n">
         <v>2.82</v>
       </c>
-      <c r="C29" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N29" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O29" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2983,75 +2985,75 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C30" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D30" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E30" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H30" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I30" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J30" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M30" t="n">
         <v>2.72</v>
       </c>
-      <c r="L30" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M30" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N30" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O30" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3060,55 +3062,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C31" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D31" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E31" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H31" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I31" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J31" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K31" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L31" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M31" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O31" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3119,7 +3125,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3129,10 +3135,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3144,57 +3148,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C32" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D32" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J32" t="n">
         <v>2.68</v>
       </c>
-      <c r="E32" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K32" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L32" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M32" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N32" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O32" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,15 +3209,13 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3228,57 +3230,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C33" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D33" t="n">
         <v>2.71</v>
       </c>
       <c r="E33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L33" t="n">
         <v>2.75</v>
       </c>
-      <c r="F33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L33" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M33" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N33" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O33" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3289,13 +3291,15 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3317,69 +3321,71 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C34" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D34" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E34" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I34" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J34" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K34" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L34" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M34" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N34" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O34" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3392,56 +3398,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C35" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D35" t="n">
         <v>2.66</v>
       </c>
       <c r="E35" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H35" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I35" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J35" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K35" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L35" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N35" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O35" t="n">
         <v>2.91</v>
@@ -3449,19 +3451,15 @@
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3478,68 +3476,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L36" t="n">
         <v>2.69</v>
       </c>
-      <c r="C36" t="n">
+      <c r="M36" t="n">
         <v>2.71</v>
       </c>
-      <c r="D36" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N36" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O36" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3556,81 +3562,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C37" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D37" t="n">
         <v>2.62</v>
       </c>
       <c r="E37" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H37" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J37" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K37" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L37" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M37" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N37" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O37" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3642,55 +3642,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K38" t="n">
         <v>2.63</v>
       </c>
-      <c r="C38" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E38" t="n">
+      <c r="L38" t="n">
         <v>2.66</v>
       </c>
-      <c r="F38" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M38" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N38" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O38" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3701,9 +3705,9 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3711,70 +3715,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W38" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J39" t="n">
         <v>2.71</v>
       </c>
-      <c r="C39" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K39" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L39" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M39" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N39" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O39" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3787,78 +3791,76 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C40" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D40" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E40" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J40" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K40" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L40" t="n">
         <v>2.77</v>
       </c>
       <c r="M40" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N40" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O40" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3871,11 +3873,13 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3888,78 +3892,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C41" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D41" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E41" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L41" t="n">
         <v>2.8</v>
       </c>
-      <c r="F41" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L41" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M41" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N41" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O41" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3967,9 +3969,9 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
@@ -3977,14 +3979,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C42" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D42" t="n">
         <v>2.71</v>
@@ -3993,56 +3995,54 @@
         <v>2.73</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H42" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J42" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K42" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N42" t="n">
         <v>2.8</v>
       </c>
-      <c r="M42" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>2.89</v>
       </c>
-      <c r="O42" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4054,43 +4054,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C43" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D43" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E43" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H43" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J43" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K43" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L43" t="n">
         <v>2.74</v>
@@ -4102,27 +4106,29 @@
         <v>2.8</v>
       </c>
       <c r="O43" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+      <c r="Q43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4134,90 +4140,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D44" t="n">
         <v>2.69</v>
       </c>
-      <c r="C44" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E44" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H44" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I44" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J44" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K44" t="n">
         <v>2.65</v>
       </c>
-      <c r="K44" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L44" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M44" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N44" t="n">
         <v>2.77</v>
       </c>
-      <c r="N44" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O44" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
@@ -4225,50 +4229,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C45" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D45" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J45" t="n">
         <v>2.69</v>
       </c>
-      <c r="E45" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K45" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L45" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M45" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N45" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O45" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4279,25 +4283,21 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
@@ -4309,69 +4309,71 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C46" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D46" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E46" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F46" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H46" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I46" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J46" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K46" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L46" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M46" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N46" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O46" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4384,77 +4386,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C47" t="n">
         <v>2.8</v>
       </c>
       <c r="D47" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E47" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H47" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I47" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J47" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K47" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L47" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M47" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N47" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O47" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4468,79 +4472,85 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C48" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M48" t="n">
         <v>2.8</v>
       </c>
-      <c r="D48" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N48" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O48" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4559,78 +4569,72 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2.75</v>
       </c>
       <c r="C49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M49" t="n">
         <v>2.84</v>
       </c>
-      <c r="D49" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N49" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O49" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4642,80 +4646,82 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C50" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D50" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E50" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H50" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I50" t="n">
         <v>2.59</v>
       </c>
       <c r="J50" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K50" t="n">
         <v>2.72</v>
       </c>
       <c r="L50" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M50" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N50" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O50" t="n">
         <v>2.91</v>
       </c>
-      <c r="O50" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
@@ -4724,59 +4730,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C51" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E51" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2.84</v>
       </c>
       <c r="F51" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H51" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I51" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J51" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K51" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L51" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M51" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N51" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O51" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4787,7 +4789,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4797,10 +4799,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4815,47 +4815,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K52" t="n">
         <v>2.86</v>
       </c>
-      <c r="C52" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L52" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M52" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N52" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O52" t="n">
         <v>3.04</v>
@@ -4866,18 +4866,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4890,55 +4890,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C53" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E53" t="n">
         <v>2.93</v>
       </c>
-      <c r="D53" t="n">
+      <c r="F53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K53" t="n">
         <v>2.84</v>
       </c>
-      <c r="E53" t="n">
+      <c r="L53" t="n">
         <v>2.89</v>
       </c>
-      <c r="F53" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M53" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N53" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O53" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4953,11 +4957,13 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4972,57 +4978,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C54" t="n">
         <v>2.95</v>
       </c>
       <c r="D54" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E54" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F54" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H54" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I54" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J54" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K54" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L54" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M54" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N54" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O54" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5037,13 +5043,11 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5065,47 +5069,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C55" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K55" t="n">
         <v>2.85</v>
       </c>
-      <c r="E55" t="n">
+      <c r="L55" t="n">
         <v>2.9</v>
       </c>
-      <c r="F55" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L55" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M55" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N55" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O55" t="n">
         <v>3.06</v>
@@ -5116,18 +5120,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5140,59 +5144,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C56" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M56" t="n">
         <v>3</v>
       </c>
-      <c r="D56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N56" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O56" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5200,17 +5200,19 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U56" s="8" t="n">
@@ -5224,55 +5226,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C57" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N57" t="n">
         <v>3.03</v>
       </c>
-      <c r="D57" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E57" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L57" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O57" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5280,21 +5286,19 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5308,76 +5312,78 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>2.93</v>
       </c>
       <c r="C58" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D58" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E58" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F58" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H58" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I58" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J58" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K58" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L58" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M58" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N58" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O58" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5392,72 +5398,70 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L59" t="n">
         <v>2.93</v>
       </c>
-      <c r="C59" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D59" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E59" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I59" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L59" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M59" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N59" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O59" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5478,57 +5482,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N60" t="n">
         <v>2.91</v>
       </c>
-      <c r="C60" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D60" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E60" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I60" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K60" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L60" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M60" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N60" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O60" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5538,12 +5542,12 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5562,203 +5566,119 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C61" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D61" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E61" t="n">
         <v>2.83</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H61" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J61" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K61" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L61" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M61" t="n">
         <v>2.88</v>
       </c>
       <c r="N61" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>明日預測</t>
+        </is>
+      </c>
+      <c r="I62" s="13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N62" s="13" t="n">
         <v>2.91</v>
       </c>
-      <c r="O61" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="C62" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="D62" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="L62" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="M62" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N62" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O62" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="O63" s="13" t="n">
+      <c r="O62" s="13" t="n">
         <v>2.92</v>
       </c>
     </row>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="D2" t="n">
         <v>3.12</v>
       </c>
       <c r="E2" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09</v>
+        <v>0.09</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.029</v>
+        <v>0.028</v>
       </c>
       <c r="H2" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="I2" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="J2" t="n">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="K2" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="L2" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="O2" t="n">
-        <v>3.41</v>
+        <v>3.48</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,19 +692,19 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -718,57 +718,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="C3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E3" t="n">
         <v>3.25</v>
       </c>
-      <c r="D3" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.23</v>
-      </c>
       <c r="F3" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0062</v>
       </c>
       <c r="H3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="K3" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="L3" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="M3" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N3" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.37</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,7 +779,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -800,78 +800,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C4" t="n">
         <v>3.28</v>
       </c>
-      <c r="C4" t="n">
-        <v>3.34</v>
-      </c>
       <c r="D4" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="E4" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0326</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="J4" t="n">
         <v>3.14</v>
       </c>
       <c r="K4" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="M4" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="O4" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -884,77 +882,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="C5" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="D5" t="n">
         <v>3.14</v>
       </c>
       <c r="E5" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0235</v>
       </c>
       <c r="H5" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="J5" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N5" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -968,57 +968,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="C6" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="D6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J6" t="n">
         <v>3.14</v>
       </c>
-      <c r="E6" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.98</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="L6" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="O6" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1029,93 +1029,97 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="C7" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="D7" t="n">
         <v>3.2</v>
       </c>
       <c r="E7" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="F7" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0379</v>
+        <v>-0.0335</v>
       </c>
       <c r="H7" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="I7" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="J7" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="K7" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L7" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="N7" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -1123,93 +1127,89 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="C8" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="E8" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0155</v>
       </c>
       <c r="H8" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="J8" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="K8" t="n">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="L8" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="M8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.43</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.54</v>
-      </c>
       <c r="O8" t="n">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1224,57 +1224,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="C9" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="D9" t="n">
         <v>3.16</v>
       </c>
       <c r="E9" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0296</v>
       </c>
       <c r="H9" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I9" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="J9" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>3.11</v>
       </c>
       <c r="L9" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N9" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1282,21 +1282,23 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1308,57 +1310,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="C10" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D10" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="E10" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0296</v>
+        <v>-0.0168</v>
       </c>
       <c r="H10" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K10" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="L10" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="M10" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O10" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1366,23 +1368,21 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1394,57 +1394,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M11" t="n">
         <v>3.26</v>
       </c>
-      <c r="C11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N11" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1457,7 +1457,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1478,58 +1478,58 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3.21</v>
       </c>
       <c r="C12" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D12" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J12" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K12" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L12" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M12" t="n">
         <v>3.23</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N12" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O12" t="n">
         <v>3.29</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
@@ -1538,17 +1538,19 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1560,59 +1562,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C13" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D13" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E13" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I13" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J13" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K13" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M13" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N13" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O13" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1625,7 +1623,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1651,50 +1649,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C14" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D14" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E14" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H14" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I14" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J14" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K14" t="n">
         <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M14" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N14" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1704,19 +1702,19 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1728,76 +1726,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C15" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E15" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H15" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I15" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J15" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L15" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.33</v>
       </c>
-      <c r="N15" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O15" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1805,81 +1809,73 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C16" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D16" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H16" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I16" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J16" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M16" t="n">
         <v>3.14</v>
       </c>
-      <c r="L16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N16" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O16" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1903,50 +1899,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C17" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K17" t="n">
         <v>2.87</v>
       </c>
-      <c r="E17" t="n">
+      <c r="L17" t="n">
         <v>2.94</v>
       </c>
-      <c r="F17" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M17" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N17" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1959,7 +1955,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1983,14 +1979,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C18" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2.95</v>
       </c>
       <c r="D18" t="n">
         <v>2.85</v>
@@ -1999,34 +1995,34 @@
         <v>2.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H18" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I18" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J18" t="n">
         <v>2.79</v>
       </c>
       <c r="K18" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L18" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2034,14 +2030,12 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2058,55 +2052,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C19" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D19" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H19" t="n">
         <v>0.08</v>
       </c>
       <c r="I19" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J19" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K19" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L19" t="n">
         <v>2.9</v>
       </c>
       <c r="M19" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O19" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2114,16 +2112,20 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2138,63 +2140,65 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2.92</v>
       </c>
       <c r="C20" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D20" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E20" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I20" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J20" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K20" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M20" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N20" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O20" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
@@ -2203,12 +2207,12 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U20" s="8" t="n">
@@ -2224,81 +2228,77 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C21" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D21" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E21" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H21" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K21" t="n">
         <v>2.79</v>
       </c>
-      <c r="J21" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L21" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M21" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N21" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O21" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2312,76 +2312,78 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C22" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D22" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E22" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
       </c>
       <c r="I22" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J22" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K22" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L22" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M22" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O22" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2394,81 +2396,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C23" t="n">
         <v>2.91</v>
       </c>
       <c r="D23" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E23" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H23" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J23" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K23" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L23" t="n">
         <v>2.87</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2.9</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N23" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O23" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2480,43 +2476,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C24" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D24" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E24" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I24" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J24" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K24" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L24" t="n">
         <v>2.87</v>
@@ -2528,7 +2528,7 @@
         <v>2.93</v>
       </c>
       <c r="O24" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2549,8 +2549,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2562,57 +2564,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C25" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D25" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E25" t="n">
         <v>2.92</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H25" t="n">
         <v>0.09</v>
       </c>
       <c r="I25" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J25" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K25" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L25" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N25" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O25" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2625,7 +2627,7 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2633,10 +2635,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2648,57 +2648,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C26" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D26" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E26" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H26" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J26" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K26" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L26" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M26" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N26" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O26" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2706,18 +2706,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2730,72 +2730,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C27" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D27" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E27" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H27" t="n">
         <v>0.1</v>
       </c>
       <c r="I27" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K27" t="n">
         <v>2.82</v>
       </c>
-      <c r="J27" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L27" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M27" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N27" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O27" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2819,67 +2819,65 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M28" t="n">
         <v>2.82</v>
       </c>
-      <c r="C28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N28" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O28" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2903,75 +2901,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C29" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D29" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E29" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H29" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I29" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J29" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M29" t="n">
         <v>2.72</v>
       </c>
-      <c r="L29" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N29" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O29" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2980,55 +2978,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C30" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D30" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E30" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F30" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H30" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I30" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J30" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L30" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M30" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N30" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O30" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3039,7 +3041,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3049,10 +3051,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3064,57 +3064,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C31" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D31" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J31" t="n">
         <v>2.68</v>
       </c>
-      <c r="E31" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K31" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L31" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M31" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N31" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O31" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3125,15 +3125,13 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3148,57 +3146,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C32" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D32" t="n">
         <v>2.71</v>
       </c>
       <c r="E32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L32" t="n">
         <v>2.75</v>
       </c>
-      <c r="F32" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L32" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M32" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N32" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O32" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,13 +3207,15 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3237,69 +3237,71 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C33" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D33" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E33" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I33" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J33" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K33" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L33" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M33" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N33" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O33" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3312,56 +3314,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C34" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D34" t="n">
         <v>2.66</v>
       </c>
       <c r="E34" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H34" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I34" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J34" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K34" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L34" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N34" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O34" t="n">
         <v>2.91</v>
@@ -3369,19 +3367,15 @@
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3398,68 +3392,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L35" t="n">
         <v>2.69</v>
       </c>
-      <c r="C35" t="n">
+      <c r="M35" t="n">
         <v>2.71</v>
       </c>
-      <c r="D35" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N35" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O35" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3476,81 +3478,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C36" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D36" t="n">
         <v>2.62</v>
       </c>
       <c r="E36" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H36" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J36" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K36" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L36" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M36" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N36" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O36" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3562,55 +3558,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K37" t="n">
         <v>2.63</v>
       </c>
-      <c r="C37" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="L37" t="n">
         <v>2.66</v>
       </c>
-      <c r="F37" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L37" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M37" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N37" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O37" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3621,9 +3621,9 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3631,70 +3631,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J38" t="n">
         <v>2.71</v>
       </c>
-      <c r="C38" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K38" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L38" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M38" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N38" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O38" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3707,78 +3707,76 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C39" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D39" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E39" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H39" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J39" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K39" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L39" t="n">
         <v>2.77</v>
       </c>
       <c r="M39" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N39" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O39" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3791,11 +3789,13 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3808,78 +3808,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C40" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D40" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E40" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L40" t="n">
         <v>2.8</v>
       </c>
-      <c r="F40" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M40" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N40" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O40" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3887,9 +3885,9 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -3897,14 +3895,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C41" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D41" t="n">
         <v>2.71</v>
@@ -3913,56 +3911,54 @@
         <v>2.73</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H41" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J41" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K41" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L41" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N41" t="n">
         <v>2.8</v>
       </c>
-      <c r="M41" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>2.89</v>
       </c>
-      <c r="O41" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3974,43 +3970,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C42" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D42" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E42" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H42" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J42" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K42" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L42" t="n">
         <v>2.74</v>
@@ -4022,27 +4022,29 @@
         <v>2.8</v>
       </c>
       <c r="O42" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4054,90 +4056,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D43" t="n">
         <v>2.69</v>
       </c>
-      <c r="C43" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E43" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H43" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I43" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K43" t="n">
         <v>2.65</v>
       </c>
-      <c r="K43" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L43" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M43" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N43" t="n">
         <v>2.77</v>
       </c>
-      <c r="N43" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O43" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
@@ -4145,50 +4145,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C44" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D44" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J44" t="n">
         <v>2.69</v>
       </c>
-      <c r="E44" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K44" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L44" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M44" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N44" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O44" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4199,25 +4199,21 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
@@ -4229,69 +4225,71 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C45" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D45" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E45" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F45" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H45" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I45" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J45" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K45" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L45" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M45" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N45" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O45" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4304,77 +4302,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C46" t="n">
         <v>2.8</v>
       </c>
       <c r="D46" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E46" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I46" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J46" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K46" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L46" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M46" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N46" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O46" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4388,79 +4388,85 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M47" t="n">
         <v>2.8</v>
       </c>
-      <c r="D47" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M47" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N47" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O47" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4479,78 +4485,72 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>2.75</v>
       </c>
       <c r="C48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M48" t="n">
         <v>2.84</v>
       </c>
-      <c r="D48" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N48" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O48" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4562,80 +4562,82 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C49" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D49" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E49" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H49" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I49" t="n">
         <v>2.59</v>
       </c>
       <c r="J49" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K49" t="n">
         <v>2.72</v>
       </c>
       <c r="L49" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M49" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N49" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O49" t="n">
         <v>2.91</v>
       </c>
-      <c r="O49" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4644,59 +4646,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C50" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E50" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2.84</v>
       </c>
       <c r="F50" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H50" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I50" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J50" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K50" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L50" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M50" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N50" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O50" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4707,7 +4705,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4717,10 +4715,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4735,47 +4731,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K51" t="n">
         <v>2.86</v>
       </c>
-      <c r="C51" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L51" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M51" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N51" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O51" t="n">
         <v>3.04</v>
@@ -4786,18 +4782,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4810,55 +4806,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C52" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E52" t="n">
         <v>2.93</v>
       </c>
-      <c r="D52" t="n">
+      <c r="F52" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K52" t="n">
         <v>2.84</v>
       </c>
-      <c r="E52" t="n">
+      <c r="L52" t="n">
         <v>2.89</v>
       </c>
-      <c r="F52" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M52" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N52" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O52" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4873,11 +4873,13 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4892,57 +4894,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C53" t="n">
         <v>2.95</v>
       </c>
       <c r="D53" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E53" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F53" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H53" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I53" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J53" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K53" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L53" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M53" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N53" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O53" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4957,13 +4959,11 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4985,47 +4985,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C54" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K54" t="n">
         <v>2.85</v>
       </c>
-      <c r="E54" t="n">
+      <c r="L54" t="n">
         <v>2.9</v>
       </c>
-      <c r="F54" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M54" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N54" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O54" t="n">
         <v>3.06</v>
@@ -5036,18 +5036,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5060,59 +5060,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C55" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M55" t="n">
         <v>3</v>
       </c>
-      <c r="D55" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E55" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L55" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N55" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O55" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5120,17 +5116,19 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U55" s="8" t="n">
@@ -5144,55 +5142,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C56" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N56" t="n">
         <v>3.03</v>
       </c>
-      <c r="D56" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M56" t="n">
-        <v>3</v>
-      </c>
-      <c r="N56" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O56" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5200,21 +5202,19 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5228,76 +5228,78 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>2.93</v>
       </c>
       <c r="C57" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D57" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E57" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F57" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H57" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I57" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J57" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K57" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L57" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M57" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N57" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O57" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5312,72 +5314,70 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L58" t="n">
         <v>2.93</v>
       </c>
-      <c r="C58" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M58" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N58" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O58" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5398,57 +5398,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N59" t="n">
         <v>2.91</v>
       </c>
-      <c r="C59" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D59" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E59" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I59" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L59" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M59" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N59" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O59" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5458,12 +5458,12 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5482,57 +5482,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C60" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D60" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E60" t="n">
         <v>2.83</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H60" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J60" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K60" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L60" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M60" t="n">
         <v>2.88</v>
       </c>
       <c r="N60" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O60" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5566,42 +5566,42 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C61" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D61" t="n">
         <v>2.85</v>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J61" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J61" t="n">
-        <v>2.76</v>
       </c>
       <c r="K61" t="n">
         <v>2.79</v>
@@ -5610,13 +5610,13 @@
         <v>2.82</v>
       </c>
       <c r="M61" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N61" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O61" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5624,18 +5624,18 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5648,11 +5648,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5661,25 +5657,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5577,25 +5577,25 @@
         </is>
       </c>
       <c r="B61" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="D61" t="n">
         <v>2.87</v>
       </c>
-      <c r="C61" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D61" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E61" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="F61" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0187</v>
+        <v>0.0145</v>
       </c>
       <c r="H61" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I61" t="n">
         <v>2.7</v>
@@ -5657,25 +5657,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L62" s="13" t="n">
         <v>2.88</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5586,13 +5586,13 @@
         <v>2.87</v>
       </c>
       <c r="E61" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="F61" t="n">
         <v>0.04</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0159</v>
       </c>
       <c r="H61" t="n">
         <v>0.02</v>
@@ -5663,13 +5663,13 @@
         <v>2.85</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="L62" s="13" t="n">
         <v>2.88</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="N62" s="13" t="n">
         <v>2.89</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5589,10 +5589,10 @@
         <v>2.88</v>
       </c>
       <c r="F61" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0173</v>
       </c>
       <c r="H61" t="n">
         <v>0.02</v>
@@ -5660,7 +5660,7 @@
         <v>2.85</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="K62" s="13" t="n">
         <v>2.87</v>
@@ -5672,7 +5672,7 @@
         <v>2.89</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>2.91</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5577,25 +5577,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="C61" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="D61" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="E61" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="F61" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0173</v>
+        <v>0.023</v>
       </c>
       <c r="H61" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="I61" t="n">
         <v>2.7</v>
@@ -5634,12 +5634,14 @@
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
@@ -5651,30 +5653,112 @@
       <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="O62" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
+      <c r="I63" s="13" t="n">
         <v>2.85</v>
       </c>
-      <c r="J62" s="13" t="n">
+      <c r="J63" s="13" t="n">
         <v>2.86</v>
       </c>
-      <c r="K62" s="13" t="n">
+      <c r="K63" s="13" t="n">
         <v>2.87</v>
       </c>
-      <c r="L62" s="13" t="n">
+      <c r="L63" s="13" t="n">
         <v>2.88</v>
       </c>
-      <c r="M62" s="13" t="n">
+      <c r="M63" s="13" t="n">
         <v>2.89</v>
       </c>
-      <c r="N62" s="13" t="n">
+      <c r="N63" s="13" t="n">
         <v>2.9</v>
       </c>
-      <c r="O62" s="13" t="n">
+      <c r="O63" s="13" t="n">
         <v>2.91</v>
       </c>
     </row>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="C2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E2" t="n">
         <v>3.25</v>
       </c>
-      <c r="D2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3.23</v>
-      </c>
       <c r="F2" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0062</v>
       </c>
       <c r="H2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="K2" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="L2" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="M2" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N2" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="O2" t="n">
-        <v>3.48</v>
+        <v>3.37</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -716,79 +716,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C3" t="n">
         <v>3.28</v>
       </c>
-      <c r="C3" t="n">
-        <v>3.34</v>
-      </c>
       <c r="D3" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="E3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0326</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="J3" t="n">
         <v>3.14</v>
       </c>
       <c r="K3" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="M3" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="O3" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -800,77 +798,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="C4" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="D4" t="n">
         <v>3.14</v>
       </c>
       <c r="E4" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0235</v>
       </c>
       <c r="H4" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="J4" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -884,57 +884,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="C5" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="D5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J5" t="n">
         <v>3.14</v>
       </c>
-      <c r="E5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.98</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="L5" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -952,86 +952,90 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="C6" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="D6" t="n">
         <v>3.2</v>
       </c>
       <c r="E6" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="F6" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0379</v>
+        <v>-0.0335</v>
       </c>
       <c r="H6" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="I6" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="J6" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="K6" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="N6" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="O6" t="n">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
@@ -1039,93 +1043,89 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="C7" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="E7" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0155</v>
       </c>
       <c r="H7" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="J7" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="K7" t="n">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="L7" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="M7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.43</v>
       </c>
-      <c r="N7" t="n">
-        <v>3.54</v>
-      </c>
       <c r="O7" t="n">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1140,57 +1140,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="C8" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="D8" t="n">
         <v>3.16</v>
       </c>
       <c r="E8" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0296</v>
       </c>
       <c r="H8" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I8" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="J8" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>3.11</v>
       </c>
       <c r="L8" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N8" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1198,21 +1198,23 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1224,57 +1226,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="C9" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D9" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="E9" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0296</v>
+        <v>-0.0168</v>
       </c>
       <c r="H9" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K9" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="L9" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="M9" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O9" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1282,23 +1284,21 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1310,57 +1310,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M10" t="n">
         <v>3.26</v>
       </c>
-      <c r="C10" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N10" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1394,58 +1394,58 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>3.21</v>
       </c>
       <c r="C11" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D11" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J11" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K11" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L11" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M11" t="n">
         <v>3.23</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N11" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O11" t="n">
         <v>3.29</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
@@ -1454,17 +1454,19 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1476,59 +1478,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C12" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D12" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E12" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J12" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K12" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N12" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O12" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1567,50 +1565,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C13" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D13" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E13" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H13" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I13" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J13" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M13" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N13" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O13" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1620,19 +1618,19 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1644,65 +1642,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C14" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E14" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H14" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I14" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J14" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L14" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M14" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N14" t="n">
         <v>3.33</v>
       </c>
-      <c r="N14" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O14" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
@@ -1710,10 +1716,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1721,78 +1725,70 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C15" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D15" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E15" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H15" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I15" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J15" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M15" t="n">
         <v>3.14</v>
       </c>
-      <c r="L15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N15" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O15" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
@@ -1819,50 +1815,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C16" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K16" t="n">
         <v>2.87</v>
       </c>
-      <c r="E16" t="n">
+      <c r="L16" t="n">
         <v>2.94</v>
       </c>
-      <c r="F16" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M16" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1899,14 +1895,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C17" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2.95</v>
       </c>
       <c r="D17" t="n">
         <v>2.85</v>
@@ -1915,34 +1911,34 @@
         <v>2.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H17" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I17" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J17" t="n">
         <v>2.79</v>
       </c>
       <c r="K17" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L17" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1950,14 +1946,12 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1974,55 +1968,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C18" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D18" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H18" t="n">
         <v>0.08</v>
       </c>
       <c r="I18" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J18" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K18" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L18" t="n">
         <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2030,16 +2028,20 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2054,77 +2056,79 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2.92</v>
       </c>
       <c r="C19" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D19" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E19" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I19" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J19" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K19" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M19" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N19" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O19" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U19" s="8" t="n">
@@ -2140,81 +2144,77 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C20" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D20" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E20" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H20" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K20" t="n">
         <v>2.79</v>
       </c>
-      <c r="J20" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L20" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M20" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N20" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O20" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2228,77 +2228,79 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C21" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D21" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E21" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H21" t="n">
         <v>0.08</v>
       </c>
       <c r="I21" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J21" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K21" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L21" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M21" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N21" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O21" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2310,81 +2312,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C22" t="n">
         <v>2.91</v>
       </c>
       <c r="D22" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E22" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H22" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J22" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L22" t="n">
         <v>2.87</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>2.9</v>
       </c>
-      <c r="M22" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N22" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O22" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2396,43 +2392,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C23" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D23" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E23" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I23" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J23" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K23" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L23" t="n">
         <v>2.87</v>
@@ -2444,7 +2444,7 @@
         <v>2.93</v>
       </c>
       <c r="O23" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2455,9 +2455,9 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2465,8 +2465,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2478,57 +2480,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C24" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D24" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E24" t="n">
         <v>2.92</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H24" t="n">
         <v>0.09</v>
       </c>
       <c r="I24" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J24" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K24" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L24" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N24" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O24" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2539,9 +2541,9 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2549,10 +2551,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2564,57 +2564,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C25" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D25" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E25" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H25" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I25" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J25" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K25" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L25" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M25" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N25" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O25" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2622,18 +2622,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2646,69 +2646,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C26" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D26" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E26" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H26" t="n">
         <v>0.1</v>
       </c>
       <c r="I26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K26" t="n">
         <v>2.82</v>
       </c>
-      <c r="J26" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L26" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M26" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N26" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
@@ -2735,59 +2735,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M27" t="n">
         <v>2.82</v>
       </c>
-      <c r="C27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N27" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O27" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -2819,75 +2817,75 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C28" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D28" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E28" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H28" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I28" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J28" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M28" t="n">
         <v>2.72</v>
       </c>
-      <c r="L28" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N28" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O28" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2896,55 +2894,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C29" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D29" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E29" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H29" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I29" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J29" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L29" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M29" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N29" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O29" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2965,10 +2967,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2980,57 +2980,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C30" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D30" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J30" t="n">
         <v>2.68</v>
       </c>
-      <c r="E30" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K30" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L30" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M30" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N30" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O30" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3043,13 +3043,11 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3064,57 +3062,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C31" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D31" t="n">
         <v>2.71</v>
       </c>
       <c r="E31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L31" t="n">
         <v>2.75</v>
       </c>
-      <c r="F31" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M31" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N31" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O31" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3127,11 +3125,13 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3153,70 +3153,72 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C32" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D32" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E32" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I32" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J32" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K32" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L32" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M32" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N32" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O32" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3228,56 +3230,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C33" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D33" t="n">
         <v>2.66</v>
       </c>
       <c r="E33" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H33" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I33" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J33" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K33" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L33" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M33" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N33" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O33" t="n">
         <v>2.91</v>
@@ -3285,19 +3283,15 @@
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3314,68 +3308,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L34" t="n">
         <v>2.69</v>
       </c>
-      <c r="C34" t="n">
+      <c r="M34" t="n">
         <v>2.71</v>
       </c>
-      <c r="D34" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N34" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3392,81 +3394,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C35" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D35" t="n">
         <v>2.62</v>
       </c>
       <c r="E35" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H35" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J35" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K35" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L35" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M35" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N35" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O35" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3478,55 +3474,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K36" t="n">
         <v>2.63</v>
       </c>
-      <c r="C36" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="L36" t="n">
         <v>2.66</v>
       </c>
-      <c r="F36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M36" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N36" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O36" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3547,70 +3547,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J37" t="n">
         <v>2.71</v>
       </c>
-      <c r="C37" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K37" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L37" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M37" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N37" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O37" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3621,80 +3621,78 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C38" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D38" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E38" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H38" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J38" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K38" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L38" t="n">
         <v>2.77</v>
       </c>
       <c r="M38" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N38" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O38" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3705,13 +3703,15 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3724,88 +3724,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C39" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D39" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L39" t="n">
         <v>2.8</v>
       </c>
-      <c r="F39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L39" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M39" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N39" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O39" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3813,14 +3811,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C40" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D40" t="n">
         <v>2.71</v>
@@ -3829,56 +3827,54 @@
         <v>2.73</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H40" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J40" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K40" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L40" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N40" t="n">
         <v>2.8</v>
       </c>
-      <c r="M40" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>2.89</v>
       </c>
-      <c r="O40" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3890,43 +3886,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C41" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D41" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E41" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H41" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J41" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K41" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L41" t="n">
         <v>2.74</v>
@@ -3938,26 +3938,28 @@
         <v>2.8</v>
       </c>
       <c r="O41" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3970,90 +3972,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D42" t="n">
         <v>2.69</v>
       </c>
-      <c r="C42" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E42" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I42" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K42" t="n">
         <v>2.65</v>
       </c>
-      <c r="K42" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L42" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M42" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N42" t="n">
         <v>2.77</v>
       </c>
-      <c r="N42" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O42" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
@@ -4061,50 +4061,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C43" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D43" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J43" t="n">
         <v>2.69</v>
       </c>
-      <c r="E43" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K43" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L43" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M43" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N43" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O43" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4122,18 +4122,14 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
@@ -4145,70 +4141,72 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C44" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D44" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E44" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F44" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H44" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I44" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J44" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K44" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L44" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M44" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N44" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O44" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4220,77 +4218,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C45" t="n">
         <v>2.8</v>
       </c>
       <c r="D45" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E45" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H45" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I45" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J45" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K45" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L45" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M45" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N45" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O45" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4304,79 +4304,85 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C46" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M46" t="n">
         <v>2.8</v>
       </c>
-      <c r="D46" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N46" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O46" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4395,78 +4401,72 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2.75</v>
       </c>
       <c r="C47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M47" t="n">
         <v>2.84</v>
       </c>
-      <c r="D47" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M47" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N47" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O47" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4478,80 +4478,82 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C48" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D48" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E48" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H48" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I48" t="n">
         <v>2.59</v>
       </c>
       <c r="J48" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K48" t="n">
         <v>2.72</v>
       </c>
       <c r="L48" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M48" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N48" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O48" t="n">
         <v>2.91</v>
       </c>
-      <c r="O48" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4560,59 +4562,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C49" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E49" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2.84</v>
       </c>
       <c r="F49" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H49" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I49" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J49" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K49" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L49" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M49" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N49" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O49" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4633,10 +4631,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4651,47 +4647,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K50" t="n">
         <v>2.86</v>
       </c>
-      <c r="C50" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L50" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M50" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O50" t="n">
         <v>3.04</v>
@@ -4702,18 +4698,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4726,55 +4722,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E51" t="n">
         <v>2.93</v>
       </c>
-      <c r="D51" t="n">
+      <c r="F51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K51" t="n">
         <v>2.84</v>
       </c>
-      <c r="E51" t="n">
+      <c r="L51" t="n">
         <v>2.89</v>
       </c>
-      <c r="F51" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M51" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N51" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O51" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4787,13 +4787,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4808,57 +4810,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C52" t="n">
         <v>2.95</v>
       </c>
       <c r="D52" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E52" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F52" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H52" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J52" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K52" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L52" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M52" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N52" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O52" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4871,15 +4873,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4901,47 +4901,47 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C53" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K53" t="n">
         <v>2.85</v>
       </c>
-      <c r="E53" t="n">
+      <c r="L53" t="n">
         <v>2.9</v>
       </c>
-      <c r="F53" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M53" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N53" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O53" t="n">
         <v>3.06</v>
@@ -4952,18 +4952,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4976,59 +4976,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C54" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M54" t="n">
         <v>3</v>
       </c>
-      <c r="D54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M54" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N54" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O54" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5036,17 +5032,19 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U54" s="8" t="n">
@@ -5060,55 +5058,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C55" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N55" t="n">
         <v>3.03</v>
       </c>
-      <c r="D55" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E55" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L55" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O55" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5116,21 +5118,19 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5144,77 +5144,79 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2.93</v>
       </c>
       <c r="C56" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D56" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E56" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F56" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H56" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I56" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J56" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K56" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L56" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M56" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N56" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O56" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5228,71 +5230,69 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L57" t="n">
         <v>2.93</v>
       </c>
-      <c r="C57" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D57" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E57" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L57" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M57" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N57" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O57" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5314,57 +5314,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N58" t="n">
         <v>2.91</v>
       </c>
-      <c r="C58" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O58" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5374,12 +5374,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5398,57 +5398,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C59" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D59" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E59" t="n">
         <v>2.83</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J59" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K59" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L59" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M59" t="n">
         <v>2.88</v>
       </c>
       <c r="N59" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O59" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5461,9 +5461,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5482,42 +5482,42 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C60" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D60" t="n">
         <v>2.85</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J60" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E60" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I60" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2.76</v>
       </c>
       <c r="K60" t="n">
         <v>2.79</v>
@@ -5526,13 +5526,13 @@
         <v>2.82</v>
       </c>
       <c r="M60" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N60" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O60" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5540,21 +5540,23 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5564,202 +5566,114 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D61" t="n">
         <v>2.87</v>
       </c>
-      <c r="C61" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D61" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E61" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>明日預測</t>
+        </is>
+      </c>
+      <c r="I62" s="13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K62" s="13" t="n">
         <v>2.9</v>
       </c>
-      <c r="F61" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J61" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="K61" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="L61" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="M61" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N61" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="O61" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="C62" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="D62" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L62" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M62" t="n">
+      <c r="L62" s="13" t="n">
         <v>2.93</v>
       </c>
-      <c r="N62" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O62" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>2.91</v>
+      <c r="M62" s="13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>3.03</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5575,25 +5575,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="C61" t="n">
         <v>2.95</v>
       </c>
       <c r="D61" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="E61" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="F61" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0135</v>
       </c>
       <c r="H61" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="I61" t="n">
         <v>2.79</v>
@@ -5655,25 +5655,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5575,25 +5575,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="C61" t="n">
         <v>2.95</v>
       </c>
       <c r="D61" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="E61" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="F61" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0135</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="I61" t="n">
         <v>2.79</v>
@@ -5649,31 +5649,113 @@
       <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3</v>
+      </c>
+      <c r="O62" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K62" s="13" t="n">
+      <c r="I63" s="13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L63" s="13" t="n">
         <v>2.93</v>
       </c>
-      <c r="L62" s="13" t="n">
+      <c r="M63" s="13" t="n">
         <v>2.94</v>
       </c>
-      <c r="M62" s="13" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N62" s="13" t="n">
+      <c r="N63" s="13" t="n">
         <v>2.95</v>
       </c>
-      <c r="O62" s="13" t="n">
-        <v>2.96</v>
+      <c r="O63" s="13" t="n">
+        <v>2.98</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5661,19 +5661,19 @@
         <v>2.95</v>
       </c>
       <c r="D62" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="E62" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0045</v>
       </c>
       <c r="H62" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I62" t="n">
         <v>2.79</v>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="K63" s="13" t="n">
         <v>2.91</v>
@@ -5749,13 +5749,13 @@
         <v>2.93</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5664,13 +5664,13 @@
         <v>2.9</v>
       </c>
       <c r="E62" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0075</v>
       </c>
       <c r="H62" t="n">
         <v>0.05</v>
@@ -5707,11 +5707,13 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5740,7 +5742,7 @@
         <v>2.84</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K63" s="13" t="n">
         <v>2.91</v>
@@ -5749,10 +5751,10 @@
         <v>2.93</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>3</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5658,22 +5658,22 @@
         <v>2.94</v>
       </c>
       <c r="C62" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="D62" t="n">
         <v>2.9</v>
       </c>
       <c r="E62" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="F62" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0075</v>
+        <v>0.0144</v>
       </c>
       <c r="H62" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I62" t="n">
         <v>2.79</v>
@@ -5726,11 +5726,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -5739,25 +5735,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,69 +641,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C2" t="n">
         <v>3.28</v>
       </c>
-      <c r="C2" t="n">
-        <v>3.34</v>
-      </c>
       <c r="D2" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="E2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0326</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="J2" t="n">
         <v>3.14</v>
       </c>
       <c r="K2" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="L2" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="M2" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="O2" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -716,77 +718,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="C3" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="D3" t="n">
         <v>3.14</v>
       </c>
       <c r="E3" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0235</v>
       </c>
       <c r="H3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="J3" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N3" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -800,57 +804,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="C4" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="D4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.14</v>
       </c>
-      <c r="E4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.98</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="L4" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="O4" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -861,93 +865,97 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="D5" t="n">
         <v>3.2</v>
       </c>
       <c r="E5" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0379</v>
+        <v>-0.0335</v>
       </c>
       <c r="H5" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="I5" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="J5" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="K5" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="M5" t="n">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="N5" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="O5" t="n">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -955,93 +963,89 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="C6" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="E6" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0155</v>
       </c>
       <c r="H6" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="I6" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="J6" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="K6" t="n">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="L6" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="M6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.43</v>
       </c>
-      <c r="N6" t="n">
-        <v>3.54</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1056,57 +1060,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="C7" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="D7" t="n">
         <v>3.16</v>
       </c>
       <c r="E7" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0296</v>
       </c>
       <c r="H7" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I7" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="J7" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>3.11</v>
       </c>
       <c r="L7" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N7" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1114,21 +1118,23 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1140,57 +1146,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="C8" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D8" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="E8" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0296</v>
+        <v>-0.0168</v>
       </c>
       <c r="H8" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K8" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="L8" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="M8" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O8" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1198,23 +1204,21 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1226,57 +1230,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M9" t="n">
         <v>3.26</v>
       </c>
-      <c r="C9" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N9" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1289,7 +1293,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1310,58 +1314,58 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3.21</v>
       </c>
       <c r="C10" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D10" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J10" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K10" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L10" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M10" t="n">
         <v>3.23</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O10" t="n">
         <v>3.29</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
@@ -1370,17 +1374,19 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1392,59 +1398,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C11" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D11" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E11" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I11" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J11" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K11" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N11" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O11" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1457,7 +1459,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1483,50 +1485,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C12" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D12" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E12" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I12" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J12" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M12" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N12" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1536,19 +1538,19 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1560,76 +1562,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C13" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E13" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H13" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L13" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M13" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N13" t="n">
         <v>3.33</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O13" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1637,81 +1645,73 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C14" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D14" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E14" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H14" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I14" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J14" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M14" t="n">
         <v>3.14</v>
       </c>
-      <c r="L14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N14" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O14" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1735,50 +1735,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C15" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K15" t="n">
         <v>2.87</v>
       </c>
-      <c r="E15" t="n">
+      <c r="L15" t="n">
         <v>2.94</v>
       </c>
-      <c r="F15" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M15" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1791,7 +1791,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1815,14 +1815,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C16" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2.95</v>
       </c>
       <c r="D16" t="n">
         <v>2.85</v>
@@ -1831,34 +1831,34 @@
         <v>2.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H16" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I16" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J16" t="n">
         <v>2.79</v>
       </c>
       <c r="K16" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L16" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1866,14 +1866,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1890,55 +1888,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C17" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D17" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H17" t="n">
         <v>0.08</v>
       </c>
       <c r="I17" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J17" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K17" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L17" t="n">
         <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1946,16 +1948,20 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1970,63 +1976,65 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2.92</v>
       </c>
       <c r="C18" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D18" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E18" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H18" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I18" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J18" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K18" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M18" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N18" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O18" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
@@ -2035,12 +2043,12 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U18" s="8" t="n">
@@ -2056,81 +2064,77 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C19" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D19" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E19" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.79</v>
       </c>
-      <c r="J19" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L19" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M19" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N19" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O19" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2144,76 +2148,78 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C20" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D20" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E20" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H20" t="n">
         <v>0.08</v>
       </c>
       <c r="I20" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J20" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K20" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L20" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N20" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O20" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2226,81 +2232,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C21" t="n">
         <v>2.91</v>
       </c>
       <c r="D21" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E21" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J21" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L21" t="n">
         <v>2.87</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2.9</v>
       </c>
-      <c r="M21" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N21" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O21" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2312,43 +2312,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C22" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D22" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E22" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I22" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J22" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K22" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L22" t="n">
         <v>2.87</v>
@@ -2360,7 +2364,7 @@
         <v>2.93</v>
       </c>
       <c r="O22" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2373,7 +2377,7 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2381,8 +2385,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2394,57 +2400,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C23" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D23" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E23" t="n">
         <v>2.92</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H23" t="n">
         <v>0.09</v>
       </c>
       <c r="I23" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J23" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K23" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L23" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N23" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2457,7 +2463,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2465,10 +2471,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2480,57 +2484,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C24" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D24" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E24" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H24" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I24" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J24" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K24" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L24" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M24" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2538,18 +2542,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2562,72 +2566,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C25" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D25" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E25" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H25" t="n">
         <v>0.1</v>
       </c>
       <c r="I25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K25" t="n">
         <v>2.82</v>
       </c>
-      <c r="J25" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L25" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M25" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N25" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2651,67 +2655,65 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M26" t="n">
         <v>2.82</v>
       </c>
-      <c r="C26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O26" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2735,75 +2737,75 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C27" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D27" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E27" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H27" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I27" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J27" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M27" t="n">
         <v>2.72</v>
       </c>
-      <c r="L27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N27" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O27" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2812,55 +2814,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C28" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D28" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E28" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H28" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I28" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J28" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L28" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M28" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N28" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O28" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2871,7 +2877,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2881,10 +2887,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2896,57 +2900,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C29" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D29" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J29" t="n">
         <v>2.68</v>
       </c>
-      <c r="E29" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K29" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L29" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M29" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N29" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O29" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2957,15 +2961,13 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2980,57 +2982,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C30" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D30" t="n">
         <v>2.71</v>
       </c>
       <c r="E30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L30" t="n">
         <v>2.75</v>
       </c>
-      <c r="F30" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M30" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N30" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O30" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3041,13 +3043,15 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3069,69 +3073,71 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C31" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D31" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E31" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I31" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J31" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K31" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L31" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M31" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N31" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O31" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3144,56 +3150,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C32" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D32" t="n">
         <v>2.66</v>
       </c>
       <c r="E32" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H32" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I32" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J32" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K32" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L32" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M32" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N32" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O32" t="n">
         <v>2.91</v>
@@ -3201,19 +3203,15 @@
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3230,68 +3228,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L33" t="n">
         <v>2.69</v>
       </c>
-      <c r="C33" t="n">
+      <c r="M33" t="n">
         <v>2.71</v>
       </c>
-      <c r="D33" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M33" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N33" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O33" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3308,81 +3314,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C34" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D34" t="n">
         <v>2.62</v>
       </c>
       <c r="E34" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J34" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K34" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L34" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M34" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N34" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3394,55 +3394,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K35" t="n">
         <v>2.63</v>
       </c>
-      <c r="C35" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E35" t="n">
+      <c r="L35" t="n">
         <v>2.66</v>
       </c>
-      <c r="F35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M35" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N35" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O35" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3453,9 +3457,9 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3463,70 +3467,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J36" t="n">
         <v>2.71</v>
       </c>
-      <c r="C36" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K36" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L36" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M36" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N36" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O36" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3539,78 +3543,76 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C37" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D37" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E37" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H37" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J37" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K37" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L37" t="n">
         <v>2.77</v>
       </c>
       <c r="M37" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N37" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O37" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3623,11 +3625,13 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3640,78 +3644,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C38" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D38" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E38" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L38" t="n">
         <v>2.8</v>
       </c>
-      <c r="F38" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M38" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N38" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O38" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3719,9 +3721,9 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3729,14 +3731,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C39" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D39" t="n">
         <v>2.71</v>
@@ -3745,56 +3747,54 @@
         <v>2.73</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H39" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J39" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K39" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L39" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N39" t="n">
         <v>2.8</v>
       </c>
-      <c r="M39" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>2.89</v>
       </c>
-      <c r="O39" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3806,43 +3806,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C40" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D40" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E40" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H40" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J40" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K40" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L40" t="n">
         <v>2.74</v>
@@ -3854,27 +3858,29 @@
         <v>2.8</v>
       </c>
       <c r="O40" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3886,90 +3892,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D41" t="n">
         <v>2.69</v>
       </c>
-      <c r="C41" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D41" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E41" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H41" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I41" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K41" t="n">
         <v>2.65</v>
       </c>
-      <c r="K41" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L41" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M41" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N41" t="n">
         <v>2.77</v>
       </c>
-      <c r="N41" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O41" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W41" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
@@ -3977,50 +3981,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C42" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D42" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J42" t="n">
         <v>2.69</v>
       </c>
-      <c r="E42" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K42" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L42" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M42" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N42" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O42" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4031,25 +4035,21 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
@@ -4061,69 +4061,71 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C43" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D43" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E43" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F43" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H43" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I43" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J43" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K43" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L43" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M43" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N43" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O43" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4136,77 +4138,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C44" t="n">
         <v>2.8</v>
       </c>
       <c r="D44" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E44" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H44" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I44" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J44" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K44" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L44" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M44" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N44" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O44" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4220,79 +4224,85 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C45" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M45" t="n">
         <v>2.8</v>
       </c>
-      <c r="D45" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L45" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N45" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O45" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4311,78 +4321,72 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2.75</v>
       </c>
       <c r="C46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M46" t="n">
         <v>2.84</v>
       </c>
-      <c r="D46" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N46" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O46" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4394,80 +4398,82 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C47" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D47" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E47" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H47" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I47" t="n">
         <v>2.59</v>
       </c>
       <c r="J47" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K47" t="n">
         <v>2.72</v>
       </c>
       <c r="L47" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M47" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N47" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O47" t="n">
         <v>2.91</v>
       </c>
-      <c r="O47" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4476,59 +4482,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C48" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E48" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.84</v>
       </c>
       <c r="F48" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H48" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I48" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J48" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K48" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L48" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N48" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O48" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4539,7 +4541,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4549,10 +4551,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4567,47 +4567,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K49" t="n">
         <v>2.86</v>
       </c>
-      <c r="C49" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L49" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M49" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N49" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O49" t="n">
         <v>3.04</v>
@@ -4618,18 +4618,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4642,55 +4642,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E50" t="n">
         <v>2.93</v>
       </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K50" t="n">
         <v>2.84</v>
       </c>
-      <c r="E50" t="n">
+      <c r="L50" t="n">
         <v>2.89</v>
       </c>
-      <c r="F50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L50" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M50" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N50" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O50" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4705,11 +4709,13 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4724,57 +4730,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C51" t="n">
         <v>2.95</v>
       </c>
       <c r="D51" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E51" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F51" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H51" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I51" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J51" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K51" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L51" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M51" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N51" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O51" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4789,13 +4795,11 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4817,47 +4821,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C52" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K52" t="n">
         <v>2.85</v>
       </c>
-      <c r="E52" t="n">
+      <c r="L52" t="n">
         <v>2.9</v>
       </c>
-      <c r="F52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M52" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N52" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O52" t="n">
         <v>3.06</v>
@@ -4868,18 +4872,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4892,59 +4896,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M53" t="n">
         <v>3</v>
       </c>
-      <c r="D53" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N53" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O53" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4952,17 +4952,19 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U53" s="8" t="n">
@@ -4976,55 +4978,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C54" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N54" t="n">
         <v>3.03</v>
       </c>
-      <c r="D54" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M54" t="n">
-        <v>3</v>
-      </c>
-      <c r="N54" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O54" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5032,21 +5038,19 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5060,76 +5064,78 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>2.93</v>
       </c>
       <c r="C55" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D55" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E55" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F55" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H55" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I55" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J55" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K55" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L55" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M55" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N55" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O55" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5144,72 +5150,70 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L56" t="n">
         <v>2.93</v>
       </c>
-      <c r="C56" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M56" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N56" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O56" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5230,57 +5234,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N57" t="n">
         <v>2.91</v>
       </c>
-      <c r="C57" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D57" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E57" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L57" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O57" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5290,12 +5294,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5314,57 +5318,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C58" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D58" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E58" t="n">
         <v>2.83</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H58" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J58" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K58" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L58" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M58" t="n">
         <v>2.88</v>
       </c>
       <c r="N58" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O58" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5379,7 +5383,7 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5398,42 +5402,42 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C59" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D59" t="n">
         <v>2.85</v>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J59" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E59" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I59" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2.76</v>
       </c>
       <c r="K59" t="n">
         <v>2.79</v>
@@ -5442,13 +5446,13 @@
         <v>2.82</v>
       </c>
       <c r="M59" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N59" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O59" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5456,21 +5460,23 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5480,59 +5486,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D60" t="n">
         <v>2.87</v>
       </c>
-      <c r="C60" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D60" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E60" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F60" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I60" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J60" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K60" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L60" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M60" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N60" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O60" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5543,20 +5545,18 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5571,29 +5571,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="C61" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="D61" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="E61" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F61" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0089</v>
       </c>
       <c r="H61" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="I61" t="n">
         <v>2.79</v>
@@ -5602,158 +5602,82 @@
         <v>2.84</v>
       </c>
       <c r="K61" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L61" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3</v>
+      </c>
+      <c r="O61" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>明日預測</t>
+        </is>
+      </c>
+      <c r="I62" s="13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K62" s="13" t="n">
         <v>2.89</v>
       </c>
-      <c r="M61" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="N61" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O61" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="C62" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="D62" t="n">
+      <c r="L62" s="13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M62" s="13" t="n">
         <v>2.9</v>
       </c>
-      <c r="E62" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0144</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L62" t="n">
+      <c r="N62" s="13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O62" s="13" t="n">
         <v>2.91</v>
-      </c>
-      <c r="M62" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N62" t="n">
-        <v>3</v>
-      </c>
-      <c r="O62" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>3.03</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5590,7 +5590,7 @@
         <v>-0.03</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0089</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H61" t="n">
         <v>0.01</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C61" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="D61" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="E61" t="n">
         <v>2.89</v>
@@ -5593,7 +5593,7 @@
         <v>-0.009599999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="I61" t="n">
         <v>2.79</v>
@@ -5632,8 +5632,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5648,36 +5650,120 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="O62" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
+      <c r="I63" s="13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O63" s="13" t="n">
         <v>2.88</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>2.91</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5667,16 +5667,16 @@
         <v>2.87</v>
       </c>
       <c r="D62" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="E62" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0076</v>
+        <v>-0.0097</v>
       </c>
       <c r="H62" t="n">
         <v>0.01</v>
@@ -5745,13 +5745,13 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K63" s="13" t="n">
         <v>2.86</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>2.87</v>
       </c>
       <c r="L63" s="13" t="n">
         <v>2.87</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5667,19 +5660,19 @@
         <v>2.87</v>
       </c>
       <c r="D62" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E62" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0097</v>
+        <v>-0.0128</v>
       </c>
       <c r="H62" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I62" t="n">
         <v>2.78</v>
@@ -5736,34 +5729,6 @@
         <is>
           <t>強警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>2.88</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5669,7 +5669,7 @@
         <v>-0.04</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0128</v>
+        <v>-0.0131</v>
       </c>
       <c r="H62" t="n">
         <v>0.02</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,72 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="C2" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="D2" t="n">
         <v>3.14</v>
       </c>
       <c r="E2" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0326</v>
+        <v>0.0235</v>
       </c>
       <c r="H2" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="J2" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N2" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -713,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="C3" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="D3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J3" t="n">
         <v>3.14</v>
       </c>
-      <c r="E3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.98</v>
-      </c>
       <c r="K3" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="L3" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="O3" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,93 +772,97 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="D4" t="n">
         <v>3.2</v>
       </c>
       <c r="E4" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="F4" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0379</v>
+        <v>-0.0335</v>
       </c>
       <c r="H4" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="I4" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="J4" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="K4" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="M4" t="n">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="N4" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -868,93 +870,89 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="C5" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="E5" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0155</v>
       </c>
       <c r="H5" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="J5" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="K5" t="n">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="L5" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="M5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.43</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.54</v>
-      </c>
       <c r="O5" t="n">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -969,57 +967,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="C6" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="D6" t="n">
         <v>3.16</v>
       </c>
       <c r="E6" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0296</v>
       </c>
       <c r="H6" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I6" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="J6" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>3.11</v>
       </c>
       <c r="L6" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N6" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1027,21 +1025,23 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1053,57 +1053,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="C7" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D7" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="E7" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0296</v>
+        <v>-0.0168</v>
       </c>
       <c r="H7" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K7" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="L7" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="M7" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O7" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,23 +1111,21 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1139,57 +1137,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M8" t="n">
         <v>3.26</v>
       </c>
-      <c r="C8" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N8" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1202,7 +1200,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1223,58 +1221,58 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>3.21</v>
       </c>
       <c r="C9" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D9" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K9" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L9" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M9" t="n">
         <v>3.23</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N9" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O9" t="n">
         <v>3.29</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
@@ -1283,17 +1281,19 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1305,59 +1305,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C10" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D10" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E10" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I10" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J10" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K10" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N10" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O10" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1370,7 +1366,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1396,50 +1392,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C11" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D11" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E11" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H11" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J11" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K11" t="n">
         <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M11" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N11" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O11" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1449,19 +1445,19 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1473,76 +1469,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C12" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D12" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E12" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H12" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I12" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L12" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M12" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.33</v>
       </c>
-      <c r="N12" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O12" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1550,81 +1552,73 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C13" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D13" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E13" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H13" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I13" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J13" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M13" t="n">
         <v>3.14</v>
       </c>
-      <c r="L13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N13" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O13" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1648,50 +1642,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C14" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.87</v>
       </c>
-      <c r="E14" t="n">
+      <c r="L14" t="n">
         <v>2.94</v>
       </c>
-      <c r="F14" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M14" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1704,7 +1698,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1728,14 +1722,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C15" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.95</v>
       </c>
       <c r="D15" t="n">
         <v>2.85</v>
@@ -1744,34 +1738,34 @@
         <v>2.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H15" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I15" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J15" t="n">
         <v>2.79</v>
       </c>
       <c r="K15" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L15" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1779,14 +1773,12 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1803,55 +1795,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C16" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D16" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H16" t="n">
         <v>0.08</v>
       </c>
       <c r="I16" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J16" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K16" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L16" t="n">
         <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O16" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1859,16 +1855,20 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1883,63 +1883,65 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2.92</v>
       </c>
       <c r="C17" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D17" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E17" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H17" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I17" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J17" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K17" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M17" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O17" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
@@ -1948,12 +1950,12 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U17" s="8" t="n">
@@ -1969,81 +1971,77 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C18" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D18" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E18" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H18" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K18" t="n">
         <v>2.79</v>
       </c>
-      <c r="J18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L18" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M18" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O18" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2057,76 +2055,78 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C19" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D19" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E19" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H19" t="n">
         <v>0.08</v>
       </c>
       <c r="I19" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J19" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K19" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L19" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N19" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O19" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2139,81 +2139,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C20" t="n">
         <v>2.91</v>
       </c>
       <c r="D20" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E20" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J20" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L20" t="n">
         <v>2.87</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2.9</v>
       </c>
-      <c r="M20" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N20" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O20" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2225,43 +2219,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C21" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D21" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E21" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I21" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J21" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K21" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L21" t="n">
         <v>2.87</v>
@@ -2273,7 +2271,7 @@
         <v>2.93</v>
       </c>
       <c r="O21" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2286,7 +2284,7 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2294,8 +2292,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2307,57 +2307,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C22" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D22" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E22" t="n">
         <v>2.92</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H22" t="n">
         <v>0.09</v>
       </c>
       <c r="I22" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J22" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K22" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L22" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O22" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2378,10 +2378,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2393,57 +2391,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C23" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D23" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E23" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H23" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I23" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J23" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K23" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L23" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N23" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2451,18 +2449,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2475,72 +2473,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C24" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D24" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E24" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H24" t="n">
         <v>0.1</v>
       </c>
       <c r="I24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K24" t="n">
         <v>2.82</v>
       </c>
-      <c r="J24" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L24" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2564,67 +2562,65 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M25" t="n">
         <v>2.82</v>
       </c>
-      <c r="C25" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O25" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2648,75 +2644,75 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C26" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D26" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E26" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H26" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I26" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J26" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M26" t="n">
         <v>2.72</v>
       </c>
-      <c r="L26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N26" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O26" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2725,55 +2721,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C27" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D27" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E27" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H27" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I27" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J27" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L27" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M27" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O27" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2784,7 +2784,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2794,10 +2794,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2809,57 +2807,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C28" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D28" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J28" t="n">
         <v>2.68</v>
       </c>
-      <c r="E28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K28" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L28" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M28" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N28" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O28" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2870,15 +2868,13 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2893,57 +2889,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C29" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D29" t="n">
         <v>2.71</v>
       </c>
       <c r="E29" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L29" t="n">
         <v>2.75</v>
       </c>
-      <c r="F29" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M29" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N29" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2954,13 +2950,15 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2982,69 +2980,71 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C30" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D30" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E30" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I30" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J30" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K30" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L30" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M30" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O30" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3057,56 +3057,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C31" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D31" t="n">
         <v>2.66</v>
       </c>
       <c r="E31" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H31" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I31" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J31" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K31" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L31" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M31" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N31" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O31" t="n">
         <v>2.91</v>
@@ -3114,19 +3110,15 @@
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3143,68 +3135,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L32" t="n">
         <v>2.69</v>
       </c>
-      <c r="C32" t="n">
+      <c r="M32" t="n">
         <v>2.71</v>
       </c>
-      <c r="D32" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N32" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O32" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3221,81 +3221,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C33" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D33" t="n">
         <v>2.62</v>
       </c>
       <c r="E33" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H33" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J33" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K33" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L33" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N33" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O33" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3307,55 +3301,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K34" t="n">
         <v>2.63</v>
       </c>
-      <c r="C34" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E34" t="n">
+      <c r="L34" t="n">
         <v>2.66</v>
       </c>
-      <c r="F34" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M34" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3366,9 +3364,9 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3376,70 +3374,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J35" t="n">
         <v>2.71</v>
       </c>
-      <c r="C35" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K35" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L35" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M35" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N35" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O35" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3452,78 +3450,76 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C36" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D36" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E36" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I36" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J36" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K36" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L36" t="n">
         <v>2.77</v>
       </c>
       <c r="M36" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N36" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O36" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3536,11 +3532,13 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3553,78 +3551,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C37" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D37" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E37" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L37" t="n">
         <v>2.8</v>
       </c>
-      <c r="F37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L37" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M37" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N37" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3632,9 +3628,9 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3642,14 +3638,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C38" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D38" t="n">
         <v>2.71</v>
@@ -3658,56 +3654,54 @@
         <v>2.73</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H38" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J38" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K38" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N38" t="n">
         <v>2.8</v>
       </c>
-      <c r="M38" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>2.89</v>
       </c>
-      <c r="O38" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3719,43 +3713,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C39" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D39" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E39" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H39" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J39" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K39" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L39" t="n">
         <v>2.74</v>
@@ -3767,27 +3765,29 @@
         <v>2.8</v>
       </c>
       <c r="O39" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3799,90 +3799,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D40" t="n">
         <v>2.69</v>
       </c>
-      <c r="C40" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D40" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E40" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I40" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K40" t="n">
         <v>2.65</v>
       </c>
-      <c r="K40" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L40" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M40" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N40" t="n">
         <v>2.77</v>
       </c>
-      <c r="N40" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O40" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -3890,50 +3888,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C41" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D41" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J41" t="n">
         <v>2.69</v>
       </c>
-      <c r="E41" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K41" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L41" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M41" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N41" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O41" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3944,25 +3942,21 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
@@ -3974,69 +3968,71 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C42" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D42" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E42" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F42" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H42" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I42" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J42" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K42" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L42" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M42" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N42" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O42" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4049,77 +4045,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C43" t="n">
         <v>2.8</v>
       </c>
       <c r="D43" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E43" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H43" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I43" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J43" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K43" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L43" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M43" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N43" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O43" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4133,79 +4131,85 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C44" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M44" t="n">
         <v>2.8</v>
       </c>
-      <c r="D44" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E44" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N44" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O44" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4224,78 +4228,72 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2.75</v>
       </c>
       <c r="C45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M45" t="n">
         <v>2.84</v>
       </c>
-      <c r="D45" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L45" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N45" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O45" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4307,80 +4305,82 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C46" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D46" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E46" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H46" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I46" t="n">
         <v>2.59</v>
       </c>
       <c r="J46" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K46" t="n">
         <v>2.72</v>
       </c>
       <c r="L46" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M46" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N46" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O46" t="n">
         <v>2.91</v>
       </c>
-      <c r="O46" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4389,59 +4389,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C47" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E47" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2.84</v>
       </c>
       <c r="F47" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H47" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I47" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J47" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K47" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L47" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M47" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O47" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4452,7 +4448,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4462,10 +4458,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4480,47 +4474,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K48" t="n">
         <v>2.86</v>
       </c>
-      <c r="C48" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L48" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M48" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N48" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O48" t="n">
         <v>3.04</v>
@@ -4531,18 +4525,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4555,55 +4549,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C49" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E49" t="n">
         <v>2.93</v>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K49" t="n">
         <v>2.84</v>
       </c>
-      <c r="E49" t="n">
+      <c r="L49" t="n">
         <v>2.89</v>
       </c>
-      <c r="F49" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M49" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N49" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O49" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4618,11 +4616,13 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4637,57 +4637,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C50" t="n">
         <v>2.95</v>
       </c>
       <c r="D50" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E50" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F50" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H50" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I50" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J50" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K50" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L50" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M50" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N50" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O50" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4702,13 +4702,11 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4730,47 +4728,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C51" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K51" t="n">
         <v>2.85</v>
       </c>
-      <c r="E51" t="n">
+      <c r="L51" t="n">
         <v>2.9</v>
       </c>
-      <c r="F51" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M51" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N51" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O51" t="n">
         <v>3.06</v>
@@ -4781,18 +4779,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4805,59 +4803,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M52" t="n">
         <v>3</v>
       </c>
-      <c r="D52" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N52" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O52" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4865,17 +4859,19 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U52" s="8" t="n">
@@ -4889,55 +4885,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C53" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N53" t="n">
         <v>3.03</v>
       </c>
-      <c r="D53" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M53" t="n">
-        <v>3</v>
-      </c>
-      <c r="N53" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O53" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4945,21 +4945,19 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4973,76 +4971,78 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2.93</v>
       </c>
       <c r="C54" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D54" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E54" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H54" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I54" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J54" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K54" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L54" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M54" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N54" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O54" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5057,72 +5057,70 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L55" t="n">
         <v>2.93</v>
       </c>
-      <c r="C55" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D55" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E55" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L55" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M55" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N55" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O55" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5143,57 +5141,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N56" t="n">
         <v>2.91</v>
       </c>
-      <c r="C56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N56" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O56" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5203,12 +5201,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5227,57 +5225,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C57" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D57" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E57" t="n">
         <v>2.83</v>
       </c>
       <c r="F57" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H57" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J57" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K57" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L57" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M57" t="n">
         <v>2.88</v>
       </c>
       <c r="N57" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O57" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5292,7 +5290,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5311,42 +5309,42 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C58" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D58" t="n">
         <v>2.85</v>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J58" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.76</v>
       </c>
       <c r="K58" t="n">
         <v>2.79</v>
@@ -5355,13 +5353,13 @@
         <v>2.82</v>
       </c>
       <c r="M58" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N58" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O58" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5369,21 +5367,23 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5393,59 +5393,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D59" t="n">
         <v>2.87</v>
       </c>
-      <c r="C59" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D59" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E59" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F59" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J59" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K59" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L59" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M59" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N59" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O59" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5456,20 +5452,18 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5484,29 +5478,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D60" t="n">
         <v>2.88</v>
       </c>
-      <c r="C60" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="D60" t="n">
-        <v>2.87</v>
-      </c>
       <c r="E60" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F60" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I60" t="n">
         <v>2.79</v>
@@ -5515,19 +5509,19 @@
         <v>2.84</v>
       </c>
       <c r="K60" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L60" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M60" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="N60" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5535,17 +5529,19 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U60" s="8" t="n">
@@ -5559,55 +5555,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="C61" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="D61" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E61" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H61" t="n">
         <v>0.1</v>
       </c>
       <c r="I61" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J61" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K61" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K61" t="n">
-        <v>2.88</v>
       </c>
       <c r="L61" t="n">
         <v>2.91</v>
       </c>
       <c r="M61" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O61" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5615,14 +5615,12 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
@@ -5643,57 +5641,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>2.87</v>
       </c>
       <c r="C62" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="D62" t="n">
         <v>2.85</v>
       </c>
       <c r="E62" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K62" t="n">
         <v>2.85</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.0131</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2.84</v>
       </c>
       <c r="L62" t="n">
         <v>2.91</v>
       </c>
       <c r="M62" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N62" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O62" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5703,12 +5701,12 @@
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5727,7 +5725,89 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="C2" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="D2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.14</v>
       </c>
-      <c r="E2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.98</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="L2" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="O2" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,86 +695,90 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="D3" t="n">
         <v>3.2</v>
       </c>
       <c r="E3" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="F3" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0379</v>
+        <v>-0.0335</v>
       </c>
       <c r="H3" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="I3" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="J3" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="K3" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="M3" t="n">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="N3" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="O3" t="n">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -782,93 +786,89 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="C4" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="E4" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0155</v>
       </c>
       <c r="H4" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="I4" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="J4" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="K4" t="n">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="L4" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="M4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N4" t="n">
         <v>3.43</v>
       </c>
-      <c r="N4" t="n">
-        <v>3.54</v>
-      </c>
       <c r="O4" t="n">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -883,57 +883,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="C5" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="D5" t="n">
         <v>3.16</v>
       </c>
       <c r="E5" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0296</v>
       </c>
       <c r="H5" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I5" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="J5" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>3.11</v>
       </c>
       <c r="L5" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N5" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -941,21 +941,23 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -967,57 +969,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="C6" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D6" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="E6" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0296</v>
+        <v>-0.0168</v>
       </c>
       <c r="H6" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K6" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="L6" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="M6" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O6" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,23 +1027,21 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1053,57 +1053,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M7" t="n">
         <v>3.26</v>
       </c>
-      <c r="C7" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N7" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1137,58 +1137,58 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3.21</v>
       </c>
       <c r="C8" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D8" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K8" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L8" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M8" t="n">
         <v>3.23</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N8" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O8" t="n">
         <v>3.29</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
@@ -1197,17 +1197,19 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1219,59 +1221,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C9" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D9" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E9" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I9" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J9" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K9" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N9" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1310,50 +1308,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C10" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D10" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E10" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H10" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I10" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J10" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K10" t="n">
         <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M10" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N10" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O10" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1363,19 +1361,19 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1387,65 +1385,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C11" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D11" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E11" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H11" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I11" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J11" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L11" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M11" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.33</v>
       </c>
-      <c r="N11" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O11" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
@@ -1453,10 +1459,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1464,78 +1468,70 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C12" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D12" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E12" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H12" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J12" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M12" t="n">
         <v>3.14</v>
       </c>
-      <c r="L12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N12" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O12" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
@@ -1562,50 +1558,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C13" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.87</v>
       </c>
-      <c r="E13" t="n">
+      <c r="L13" t="n">
         <v>2.94</v>
       </c>
-      <c r="F13" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M13" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1642,14 +1638,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C14" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2.95</v>
       </c>
       <c r="D14" t="n">
         <v>2.85</v>
@@ -1658,34 +1654,34 @@
         <v>2.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H14" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I14" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J14" t="n">
         <v>2.79</v>
       </c>
       <c r="K14" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L14" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,14 +1689,12 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1717,55 +1711,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C15" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D15" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H15" t="n">
         <v>0.08</v>
       </c>
       <c r="I15" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J15" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K15" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L15" t="n">
         <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O15" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,16 +1771,20 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1797,77 +1799,79 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2.92</v>
       </c>
       <c r="C16" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D16" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E16" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H16" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I16" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J16" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K16" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M16" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N16" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O16" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U16" s="8" t="n">
@@ -1883,81 +1887,77 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C17" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D17" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E17" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H17" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K17" t="n">
         <v>2.79</v>
       </c>
-      <c r="J17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L17" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N17" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O17" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1971,77 +1971,79 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C18" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D18" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E18" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H18" t="n">
         <v>0.08</v>
       </c>
       <c r="I18" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J18" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K18" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L18" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O18" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2053,81 +2055,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C19" t="n">
         <v>2.91</v>
       </c>
       <c r="D19" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E19" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J19" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L19" t="n">
         <v>2.87</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2.9</v>
       </c>
-      <c r="M19" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N19" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O19" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2139,43 +2135,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C20" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D20" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E20" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I20" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J20" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K20" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L20" t="n">
         <v>2.87</v>
@@ -2187,7 +2187,7 @@
         <v>2.93</v>
       </c>
       <c r="O20" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2198,9 +2198,9 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2208,8 +2208,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2221,57 +2223,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C21" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D21" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E21" t="n">
         <v>2.92</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H21" t="n">
         <v>0.09</v>
       </c>
       <c r="I21" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J21" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K21" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L21" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N21" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O21" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2282,9 +2284,9 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2292,10 +2294,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2307,57 +2307,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C22" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D22" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E22" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I22" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J22" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K22" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L22" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N22" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2365,18 +2365,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2389,69 +2389,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C23" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D23" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E23" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H23" t="n">
         <v>0.1</v>
       </c>
       <c r="I23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K23" t="n">
         <v>2.82</v>
       </c>
-      <c r="J23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L23" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M23" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
@@ -2478,59 +2478,57 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M24" t="n">
         <v>2.82</v>
       </c>
-      <c r="C24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N24" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O24" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -2562,75 +2560,75 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C25" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D25" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E25" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H25" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I25" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J25" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M25" t="n">
         <v>2.72</v>
       </c>
-      <c r="L25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N25" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O25" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2639,55 +2637,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C26" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D26" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E26" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H26" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J26" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M26" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O26" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2708,10 +2710,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2723,57 +2723,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C27" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D27" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J27" t="n">
         <v>2.68</v>
       </c>
-      <c r="E27" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K27" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L27" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M27" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N27" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O27" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2786,13 +2786,11 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2807,57 +2805,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C28" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D28" t="n">
         <v>2.71</v>
       </c>
       <c r="E28" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L28" t="n">
         <v>2.75</v>
       </c>
-      <c r="F28" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M28" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N28" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2870,11 +2868,13 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2896,70 +2896,72 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C29" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D29" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E29" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I29" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J29" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K29" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L29" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M29" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O29" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
+      <c r="Q29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2971,56 +2973,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C30" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D30" t="n">
         <v>2.66</v>
       </c>
       <c r="E30" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H30" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I30" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J30" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K30" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L30" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N30" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O30" t="n">
         <v>2.91</v>
@@ -3028,19 +3026,15 @@
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3057,68 +3051,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L31" t="n">
         <v>2.69</v>
       </c>
-      <c r="C31" t="n">
+      <c r="M31" t="n">
         <v>2.71</v>
       </c>
-      <c r="D31" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N31" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O31" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3135,81 +3137,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C32" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D32" t="n">
         <v>2.62</v>
       </c>
       <c r="E32" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H32" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J32" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K32" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L32" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N32" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O32" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3221,55 +3217,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K33" t="n">
         <v>2.63</v>
       </c>
-      <c r="C33" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="L33" t="n">
         <v>2.66</v>
       </c>
-      <c r="F33" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L33" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M33" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N33" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O33" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3290,70 +3290,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J34" t="n">
         <v>2.71</v>
       </c>
-      <c r="C34" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K34" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L34" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M34" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N34" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O34" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3364,80 +3364,78 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C35" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D35" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E35" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H35" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I35" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J35" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K35" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L35" t="n">
         <v>2.77</v>
       </c>
       <c r="M35" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N35" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O35" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3448,13 +3446,15 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3467,88 +3467,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C36" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D36" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E36" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L36" t="n">
         <v>2.8</v>
       </c>
-      <c r="F36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M36" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N36" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3556,14 +3554,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C37" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D37" t="n">
         <v>2.71</v>
@@ -3572,56 +3570,54 @@
         <v>2.73</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H37" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J37" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K37" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L37" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N37" t="n">
         <v>2.8</v>
       </c>
-      <c r="M37" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>2.89</v>
       </c>
-      <c r="O37" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3633,43 +3629,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C38" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D38" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E38" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H38" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J38" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K38" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L38" t="n">
         <v>2.74</v>
@@ -3681,26 +3681,28 @@
         <v>2.8</v>
       </c>
       <c r="O38" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3713,90 +3715,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D39" t="n">
         <v>2.69</v>
       </c>
-      <c r="C39" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E39" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H39" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I39" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K39" t="n">
         <v>2.65</v>
       </c>
-      <c r="K39" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L39" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N39" t="n">
         <v>2.77</v>
       </c>
-      <c r="N39" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O39" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W39" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W39" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3804,50 +3804,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C40" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J40" t="n">
         <v>2.69</v>
       </c>
-      <c r="E40" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K40" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L40" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M40" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N40" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O40" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3865,18 +3865,14 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
@@ -3888,70 +3884,72 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C41" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D41" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E41" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F41" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H41" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I41" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J41" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K41" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L41" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M41" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N41" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O41" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3963,77 +3961,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C42" t="n">
         <v>2.8</v>
       </c>
       <c r="D42" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E42" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H42" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I42" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J42" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K42" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L42" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N42" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O42" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4047,79 +4047,85 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C43" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M43" t="n">
         <v>2.8</v>
       </c>
-      <c r="D43" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N43" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O43" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4138,78 +4144,72 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2.75</v>
       </c>
       <c r="C44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M44" t="n">
         <v>2.84</v>
       </c>
-      <c r="D44" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E44" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L44" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N44" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O44" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4221,80 +4221,82 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C45" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D45" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E45" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H45" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I45" t="n">
         <v>2.59</v>
       </c>
       <c r="J45" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K45" t="n">
         <v>2.72</v>
       </c>
       <c r="L45" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M45" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N45" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O45" t="n">
         <v>2.91</v>
       </c>
-      <c r="O45" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4303,59 +4305,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C46" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E46" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2.84</v>
       </c>
       <c r="F46" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H46" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I46" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J46" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K46" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L46" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M46" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N46" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O46" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4376,10 +4374,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4394,47 +4390,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K47" t="n">
         <v>2.86</v>
       </c>
-      <c r="C47" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L47" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M47" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N47" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O47" t="n">
         <v>3.04</v>
@@ -4445,18 +4441,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4469,55 +4465,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C48" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E48" t="n">
         <v>2.93</v>
       </c>
-      <c r="D48" t="n">
+      <c r="F48" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K48" t="n">
         <v>2.84</v>
       </c>
-      <c r="E48" t="n">
+      <c r="L48" t="n">
         <v>2.89</v>
       </c>
-      <c r="F48" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M48" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N48" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O48" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4530,13 +4530,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4551,57 +4553,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C49" t="n">
         <v>2.95</v>
       </c>
       <c r="D49" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E49" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F49" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H49" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I49" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J49" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K49" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L49" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M49" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N49" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O49" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4614,15 +4616,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4644,47 +4644,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C50" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K50" t="n">
         <v>2.85</v>
       </c>
-      <c r="E50" t="n">
+      <c r="L50" t="n">
         <v>2.9</v>
       </c>
-      <c r="F50" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L50" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M50" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N50" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O50" t="n">
         <v>3.06</v>
@@ -4695,18 +4695,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4719,59 +4719,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C51" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M51" t="n">
         <v>3</v>
       </c>
-      <c r="D51" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N51" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O51" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4779,17 +4775,19 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U51" s="8" t="n">
@@ -4803,55 +4801,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C52" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N52" t="n">
         <v>3.03</v>
       </c>
-      <c r="D52" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O52" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4859,21 +4861,19 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4887,77 +4887,79 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>2.93</v>
       </c>
       <c r="C53" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D53" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E53" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I53" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J53" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K53" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L53" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M53" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N53" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O53" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4971,71 +4973,69 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L54" t="n">
         <v>2.93</v>
       </c>
-      <c r="C54" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M54" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N54" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O54" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5057,57 +5057,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N55" t="n">
         <v>2.91</v>
       </c>
-      <c r="C55" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D55" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E55" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L55" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O55" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5117,12 +5117,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5141,57 +5141,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C56" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D56" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E56" t="n">
         <v>2.83</v>
       </c>
       <c r="F56" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H56" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J56" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K56" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L56" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M56" t="n">
         <v>2.88</v>
       </c>
       <c r="N56" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O56" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5204,9 +5204,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5225,42 +5225,42 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C57" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D57" t="n">
         <v>2.85</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J57" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E57" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2.76</v>
       </c>
       <c r="K57" t="n">
         <v>2.79</v>
@@ -5269,13 +5269,13 @@
         <v>2.82</v>
       </c>
       <c r="M57" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N57" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O57" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5283,21 +5283,23 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5307,59 +5309,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D58" t="n">
         <v>2.87</v>
       </c>
-      <c r="C58" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E58" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F58" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I58" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J58" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K58" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L58" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M58" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N58" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O58" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5377,13 +5375,11 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5398,29 +5394,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D59" t="n">
         <v>2.88</v>
       </c>
-      <c r="C59" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="D59" t="n">
-        <v>2.87</v>
-      </c>
       <c r="E59" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F59" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I59" t="n">
         <v>2.79</v>
@@ -5429,19 +5425,19 @@
         <v>2.84</v>
       </c>
       <c r="K59" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L59" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M59" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="N59" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O59" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5449,17 +5445,19 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U59" s="8" t="n">
@@ -5473,55 +5471,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="C60" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="D60" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E60" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H60" t="n">
         <v>0.1</v>
       </c>
       <c r="I60" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J60" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K60" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K60" t="n">
-        <v>2.88</v>
       </c>
       <c r="L60" t="n">
         <v>2.91</v>
       </c>
       <c r="M60" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O60" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5529,14 +5531,12 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
@@ -5557,57 +5557,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="C61" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="D61" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E61" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F61" t="n">
         <v>0.01</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="H61" t="n">
         <v>0.1</v>
       </c>
       <c r="I61" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J61" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="K61" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="L61" t="n">
         <v>2.91</v>
       </c>
       <c r="M61" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N61" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O61" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5615,18 +5615,18 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5648,65 +5648,67 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="C62" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="D62" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="E62" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0288</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J62" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K62" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L62" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="M62" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="O62" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5725,89 +5727,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C63" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E63" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L63" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M63" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N63" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="O63" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5652,25 +5652,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="C62" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="D62" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="E62" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="F62" t="n">
         <v>-0.08</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0261</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I62" t="n">
         <v>2.75</v>
@@ -5730,6 +5730,90 @@
           <t>強警訊</t>
         </is>
       </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5741,22 +5741,22 @@
         <v>2.83</v>
       </c>
       <c r="C63" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="D63" t="n">
         <v>2.98</v>
       </c>
       <c r="E63" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0712</v>
+        <v>0.0878</v>
       </c>
       <c r="H63" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I63" t="n">
         <v>2.73</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,63 +634,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="C2" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="D2" t="n">
         <v>3.2</v>
       </c>
       <c r="E2" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="F2" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0379</v>
+        <v>-0.0335</v>
       </c>
       <c r="H2" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="I2" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="J2" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="K2" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="M2" t="n">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="N2" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="O2" t="n">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -698,93 +702,89 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="C3" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="E3" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0155</v>
       </c>
       <c r="H3" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="I3" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="J3" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="K3" t="n">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="L3" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="M3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N3" t="n">
         <v>3.43</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.54</v>
-      </c>
       <c r="O3" t="n">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -799,57 +799,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="C4" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="D4" t="n">
         <v>3.16</v>
       </c>
       <c r="E4" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0296</v>
       </c>
       <c r="H4" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I4" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="J4" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>3.11</v>
       </c>
       <c r="L4" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N4" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,21 +857,23 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -883,57 +885,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="C5" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D5" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="E5" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0296</v>
+        <v>-0.0168</v>
       </c>
       <c r="H5" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K5" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="L5" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="M5" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O5" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -941,23 +943,21 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -969,57 +969,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M6" t="n">
         <v>3.26</v>
       </c>
-      <c r="C6" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N6" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1032,7 +1032,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1053,58 +1053,58 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3.21</v>
       </c>
       <c r="C7" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D7" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K7" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L7" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M7" t="n">
         <v>3.23</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N7" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O7" t="n">
         <v>3.29</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
@@ -1113,17 +1113,19 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1135,59 +1137,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C8" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D8" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E8" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I8" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J8" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K8" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L8" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M8" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N8" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1200,7 +1198,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1226,50 +1224,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C9" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D9" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E9" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H9" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I9" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J9" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K9" t="n">
         <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M9" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N9" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O9" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1279,19 +1277,19 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1303,76 +1301,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C10" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E10" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H10" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I10" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L10" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.33</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O10" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1380,81 +1384,73 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C11" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D11" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E11" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H11" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J11" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M11" t="n">
         <v>3.14</v>
       </c>
-      <c r="L11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N11" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O11" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1478,50 +1474,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C12" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.87</v>
       </c>
-      <c r="E12" t="n">
+      <c r="L12" t="n">
         <v>2.94</v>
       </c>
-      <c r="F12" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M12" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N12" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1534,7 +1530,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1558,14 +1554,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C13" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.95</v>
       </c>
       <c r="D13" t="n">
         <v>2.85</v>
@@ -1574,34 +1570,34 @@
         <v>2.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H13" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I13" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J13" t="n">
         <v>2.79</v>
       </c>
       <c r="K13" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L13" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,14 +1605,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1633,55 +1627,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C14" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D14" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H14" t="n">
         <v>0.08</v>
       </c>
       <c r="I14" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J14" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K14" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L14" t="n">
         <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,16 +1687,20 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1713,63 +1715,65 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2.92</v>
       </c>
       <c r="C15" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D15" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E15" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H15" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I15" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J15" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N15" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O15" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
@@ -1778,12 +1782,12 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U15" s="8" t="n">
@@ -1799,81 +1803,77 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C16" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D16" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E16" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H16" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K16" t="n">
         <v>2.79</v>
       </c>
-      <c r="J16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L16" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M16" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N16" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1887,76 +1887,78 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C17" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D17" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E17" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H17" t="n">
         <v>0.08</v>
       </c>
       <c r="I17" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J17" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K17" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L17" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O17" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1969,81 +1971,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C18" t="n">
         <v>2.91</v>
       </c>
       <c r="D18" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E18" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J18" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L18" t="n">
         <v>2.87</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2.9</v>
       </c>
-      <c r="M18" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N18" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O18" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2055,43 +2051,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C19" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D19" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E19" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I19" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J19" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K19" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L19" t="n">
         <v>2.87</v>
@@ -2103,7 +2103,7 @@
         <v>2.93</v>
       </c>
       <c r="O19" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2124,8 +2124,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2137,57 +2139,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C20" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D20" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E20" t="n">
         <v>2.92</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H20" t="n">
         <v>0.09</v>
       </c>
       <c r="I20" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J20" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K20" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L20" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N20" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O20" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2200,7 +2202,7 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2208,10 +2210,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2223,57 +2223,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C21" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D21" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E21" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H21" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I21" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J21" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K21" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L21" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M21" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N21" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O21" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2281,18 +2281,18 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2305,72 +2305,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C22" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D22" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E22" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H22" t="n">
         <v>0.1</v>
       </c>
       <c r="I22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K22" t="n">
         <v>2.82</v>
       </c>
-      <c r="J22" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L22" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M22" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2394,67 +2394,65 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M23" t="n">
         <v>2.82</v>
       </c>
-      <c r="C23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N23" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O23" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2478,75 +2476,75 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C24" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D24" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E24" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H24" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I24" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J24" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M24" t="n">
         <v>2.72</v>
       </c>
-      <c r="L24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N24" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O24" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2555,55 +2553,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C25" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D25" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E25" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H25" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I25" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J25" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M25" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O25" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2614,7 +2616,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2624,10 +2626,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2639,57 +2639,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C26" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D26" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J26" t="n">
         <v>2.68</v>
       </c>
-      <c r="E26" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K26" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L26" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M26" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N26" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O26" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2700,15 +2700,13 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2723,57 +2721,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C27" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D27" t="n">
         <v>2.71</v>
       </c>
       <c r="E27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L27" t="n">
         <v>2.75</v>
       </c>
-      <c r="F27" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M27" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N27" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O27" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2784,13 +2782,15 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2812,69 +2812,71 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C28" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D28" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E28" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F28" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I28" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J28" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L28" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M28" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O28" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2887,56 +2889,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C29" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D29" t="n">
         <v>2.66</v>
       </c>
       <c r="E29" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H29" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I29" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J29" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K29" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L29" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M29" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N29" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O29" t="n">
         <v>2.91</v>
@@ -2944,19 +2942,15 @@
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2973,68 +2967,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L30" t="n">
         <v>2.69</v>
       </c>
-      <c r="C30" t="n">
+      <c r="M30" t="n">
         <v>2.71</v>
       </c>
-      <c r="D30" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M30" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N30" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O30" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3051,81 +3053,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C31" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D31" t="n">
         <v>2.62</v>
       </c>
       <c r="E31" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H31" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J31" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K31" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L31" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N31" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O31" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3137,55 +3133,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K32" t="n">
         <v>2.63</v>
       </c>
-      <c r="C32" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="L32" t="n">
         <v>2.66</v>
       </c>
-      <c r="F32" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L32" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M32" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N32" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O32" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3196,9 +3196,9 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3206,70 +3206,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J33" t="n">
         <v>2.71</v>
       </c>
-      <c r="C33" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K33" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L33" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M33" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N33" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O33" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3282,78 +3282,76 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C34" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D34" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E34" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H34" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J34" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K34" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L34" t="n">
         <v>2.77</v>
       </c>
       <c r="M34" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O34" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3366,11 +3364,13 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3383,78 +3383,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C35" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D35" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E35" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L35" t="n">
         <v>2.8</v>
       </c>
-      <c r="F35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M35" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N35" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O35" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3462,9 +3460,9 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3472,14 +3470,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C36" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D36" t="n">
         <v>2.71</v>
@@ -3488,56 +3486,54 @@
         <v>2.73</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H36" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J36" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K36" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N36" t="n">
         <v>2.8</v>
       </c>
-      <c r="M36" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>2.89</v>
       </c>
-      <c r="O36" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3549,43 +3545,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C37" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D37" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E37" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H37" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J37" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K37" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L37" t="n">
         <v>2.74</v>
@@ -3597,27 +3597,29 @@
         <v>2.8</v>
       </c>
       <c r="O37" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="Q37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3629,90 +3631,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D38" t="n">
         <v>2.69</v>
       </c>
-      <c r="C38" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E38" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H38" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I38" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K38" t="n">
         <v>2.65</v>
       </c>
-      <c r="K38" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L38" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M38" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N38" t="n">
         <v>2.77</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O38" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W38" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3720,50 +3720,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C39" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J39" t="n">
         <v>2.69</v>
       </c>
-      <c r="E39" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K39" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L39" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M39" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N39" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3774,25 +3774,21 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
@@ -3804,69 +3800,71 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C40" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D40" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E40" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F40" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H40" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I40" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J40" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K40" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L40" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M40" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N40" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O40" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3879,77 +3877,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C41" t="n">
         <v>2.8</v>
       </c>
       <c r="D41" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E41" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H41" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I41" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J41" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K41" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L41" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M41" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N41" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O41" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3963,79 +3963,85 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C42" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M42" t="n">
         <v>2.8</v>
       </c>
-      <c r="D42" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M42" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N42" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O42" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4054,78 +4060,72 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2.75</v>
       </c>
       <c r="C43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M43" t="n">
         <v>2.84</v>
       </c>
-      <c r="D43" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N43" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O43" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4137,80 +4137,82 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C44" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D44" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E44" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H44" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I44" t="n">
         <v>2.59</v>
       </c>
       <c r="J44" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K44" t="n">
         <v>2.72</v>
       </c>
       <c r="L44" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M44" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N44" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O44" t="n">
         <v>2.91</v>
       </c>
-      <c r="O44" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4219,59 +4221,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C45" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E45" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2.84</v>
       </c>
       <c r="F45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H45" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I45" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J45" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K45" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L45" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M45" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N45" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O45" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4282,7 +4280,7 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4292,10 +4290,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4310,47 +4306,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K46" t="n">
         <v>2.86</v>
       </c>
-      <c r="C46" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L46" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N46" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O46" t="n">
         <v>3.04</v>
@@ -4361,18 +4357,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4385,55 +4381,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C47" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E47" t="n">
         <v>2.93</v>
       </c>
-      <c r="D47" t="n">
+      <c r="F47" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K47" t="n">
         <v>2.84</v>
       </c>
-      <c r="E47" t="n">
+      <c r="L47" t="n">
         <v>2.89</v>
       </c>
-      <c r="F47" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M47" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N47" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O47" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4448,11 +4448,13 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4467,57 +4469,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C48" t="n">
         <v>2.95</v>
       </c>
       <c r="D48" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E48" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F48" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H48" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I48" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J48" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K48" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L48" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M48" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N48" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O48" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4532,13 +4534,11 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4560,47 +4560,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C49" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K49" t="n">
         <v>2.85</v>
       </c>
-      <c r="E49" t="n">
+      <c r="L49" t="n">
         <v>2.9</v>
       </c>
-      <c r="F49" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M49" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N49" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O49" t="n">
         <v>3.06</v>
@@ -4611,18 +4611,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4635,59 +4635,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M50" t="n">
         <v>3</v>
       </c>
-      <c r="D50" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L50" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N50" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4695,17 +4691,19 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U50" s="8" t="n">
@@ -4719,55 +4717,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C51" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N51" t="n">
         <v>3.03</v>
       </c>
-      <c r="D51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O51" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4775,21 +4777,19 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4803,76 +4803,78 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>2.93</v>
       </c>
       <c r="C52" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D52" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E52" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F52" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H52" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I52" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J52" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K52" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L52" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M52" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N52" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O52" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4887,72 +4889,70 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L53" t="n">
         <v>2.93</v>
       </c>
-      <c r="C53" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M53" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N53" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O53" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4973,57 +4973,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N54" t="n">
         <v>2.91</v>
       </c>
-      <c r="C54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M54" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N54" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O54" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5033,12 +5033,12 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5057,57 +5057,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C55" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D55" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E55" t="n">
         <v>2.83</v>
       </c>
       <c r="F55" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H55" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J55" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K55" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L55" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M55" t="n">
         <v>2.88</v>
       </c>
       <c r="N55" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O55" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5141,42 +5141,42 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D56" t="n">
         <v>2.85</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J56" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.76</v>
       </c>
       <c r="K56" t="n">
         <v>2.79</v>
@@ -5185,13 +5185,13 @@
         <v>2.82</v>
       </c>
       <c r="M56" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N56" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O56" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5199,21 +5199,23 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5223,59 +5225,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D57" t="n">
         <v>2.87</v>
       </c>
-      <c r="C57" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D57" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E57" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F57" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I57" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J57" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K57" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L57" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M57" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N57" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O57" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5286,20 +5284,18 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5314,29 +5310,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D58" t="n">
         <v>2.88</v>
       </c>
-      <c r="C58" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2.87</v>
-      </c>
       <c r="E58" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F58" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I58" t="n">
         <v>2.79</v>
@@ -5345,19 +5341,19 @@
         <v>2.84</v>
       </c>
       <c r="K58" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L58" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M58" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="N58" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5365,17 +5361,19 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5389,55 +5387,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="C59" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="D59" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E59" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H59" t="n">
         <v>0.1</v>
       </c>
       <c r="I59" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J59" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K59" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2.88</v>
       </c>
       <c r="L59" t="n">
         <v>2.91</v>
       </c>
       <c r="M59" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="N59" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O59" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5445,14 +5447,12 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
@@ -5473,57 +5473,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="C60" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="D60" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E60" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F60" t="n">
         <v>0.01</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="H60" t="n">
         <v>0.1</v>
       </c>
       <c r="I60" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J60" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="K60" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="L60" t="n">
         <v>2.91</v>
       </c>
       <c r="M60" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N60" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5531,18 +5531,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5564,56 +5564,58 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C61" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="D61" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="E61" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0261</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I61" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J61" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K61" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L61" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="M61" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="O61" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
@@ -5622,7 +5624,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5641,179 +5643,93 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="C62" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N62" t="n">
         <v>2.91</v>
       </c>
-      <c r="D62" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.0261</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L62" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M62" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N62" t="n">
-        <v>3.02</v>
-      </c>
       <c r="O62" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="C63" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E63" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0878</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="L63" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="M63" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N63" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="O63" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5657,22 +5657,22 @@
         <v>3.16</v>
       </c>
       <c r="C62" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="D62" t="n">
         <v>3.16</v>
       </c>
       <c r="E62" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="F62" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.116</v>
+        <v>0.1195</v>
       </c>
       <c r="H62" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I62" t="n">
         <v>2.73</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5669,7 +5669,7 @@
         <v>0.34</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.1195</v>
+        <v>0.1188</v>
       </c>
       <c r="H62" t="n">
         <v>0.04</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5666,10 +5666,10 @@
         <v>3.17</v>
       </c>
       <c r="F62" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.1188</v>
+        <v>0.1164</v>
       </c>
       <c r="H62" t="n">
         <v>0.04</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -5663,13 +5663,13 @@
         <v>3.16</v>
       </c>
       <c r="E62" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="F62" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.1164</v>
+        <v>0.1142</v>
       </c>
       <c r="H62" t="n">
         <v>0.04</v>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5654,25 +5654,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3.16</v>
+        <v>2.83</v>
       </c>
       <c r="C62" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="D62" t="n">
-        <v>3.16</v>
+        <v>2.82</v>
       </c>
       <c r="E62" t="n">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="F62" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.1142</v>
+        <v>0.0455</v>
       </c>
       <c r="H62" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="I62" t="n">
         <v>2.73</v>
@@ -5729,7 +5729,93 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,73 +634,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="C2" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="E2" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0155</v>
       </c>
       <c r="H2" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="J2" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="K2" t="n">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="L2" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="M2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N2" t="n">
         <v>3.43</v>
       </c>
-      <c r="N2" t="n">
-        <v>3.54</v>
-      </c>
       <c r="O2" t="n">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -715,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="C3" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="D3" t="n">
         <v>3.16</v>
       </c>
       <c r="E3" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0296</v>
       </c>
       <c r="H3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="J3" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3.11</v>
       </c>
       <c r="L3" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N3" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,21 +769,23 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -799,57 +797,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="C4" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D4" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="E4" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0296</v>
+        <v>-0.0168</v>
       </c>
       <c r="H4" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K4" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="L4" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="M4" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O4" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,23 +855,21 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -885,57 +881,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M5" t="n">
         <v>3.26</v>
       </c>
-      <c r="C5" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N5" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -969,58 +965,58 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>3.21</v>
       </c>
       <c r="C6" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D6" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K6" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L6" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M6" t="n">
         <v>3.23</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N6" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O6" t="n">
         <v>3.29</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
@@ -1029,17 +1025,19 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1051,59 +1049,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C7" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D7" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E7" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I7" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K7" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N7" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O7" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1142,50 +1136,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C8" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D8" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E8" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H8" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J8" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K8" t="n">
         <v>3.2</v>
       </c>
       <c r="L8" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M8" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N8" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1195,19 +1189,19 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1219,65 +1213,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C9" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E9" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H9" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I9" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L9" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M9" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.33</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O9" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
@@ -1285,10 +1287,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1296,78 +1296,70 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C10" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D10" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E10" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H10" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J10" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M10" t="n">
         <v>3.14</v>
       </c>
-      <c r="L10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N10" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
@@ -1394,50 +1386,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C11" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.87</v>
       </c>
-      <c r="E11" t="n">
+      <c r="L11" t="n">
         <v>2.94</v>
       </c>
-      <c r="F11" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M11" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1474,14 +1466,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C12" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.95</v>
       </c>
       <c r="D12" t="n">
         <v>2.85</v>
@@ -1490,34 +1482,34 @@
         <v>2.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H12" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I12" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J12" t="n">
         <v>2.79</v>
       </c>
       <c r="K12" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L12" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,14 +1517,12 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1549,55 +1539,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C13" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D13" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H13" t="n">
         <v>0.08</v>
       </c>
       <c r="I13" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J13" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K13" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L13" t="n">
         <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1605,16 +1599,20 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1629,77 +1627,79 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2.92</v>
       </c>
       <c r="C14" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D14" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E14" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H14" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I14" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J14" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K14" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M14" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N14" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O14" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U14" s="8" t="n">
@@ -1715,81 +1715,77 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C15" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D15" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E15" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H15" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K15" t="n">
         <v>2.79</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L15" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N15" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O15" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1803,77 +1799,79 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C16" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D16" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E16" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H16" t="n">
         <v>0.08</v>
       </c>
       <c r="I16" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J16" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K16" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O16" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1885,81 +1883,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C17" t="n">
         <v>2.91</v>
       </c>
       <c r="D17" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E17" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J17" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L17" t="n">
         <v>2.87</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2.9</v>
       </c>
-      <c r="M17" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N17" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O17" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1971,43 +1963,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C18" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D18" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E18" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I18" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J18" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K18" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L18" t="n">
         <v>2.87</v>
@@ -2019,7 +2015,7 @@
         <v>2.93</v>
       </c>
       <c r="O18" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2030,9 +2026,9 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2040,8 +2036,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2053,57 +2051,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C19" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D19" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E19" t="n">
         <v>2.92</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H19" t="n">
         <v>0.09</v>
       </c>
       <c r="I19" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J19" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K19" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L19" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N19" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O19" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2114,9 +2112,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2124,10 +2122,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2139,57 +2135,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C20" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D20" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E20" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I20" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J20" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K20" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L20" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M20" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N20" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O20" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2197,18 +2193,18 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2221,69 +2217,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C21" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D21" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E21" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H21" t="n">
         <v>0.1</v>
       </c>
       <c r="I21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K21" t="n">
         <v>2.82</v>
       </c>
-      <c r="J21" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L21" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M21" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N21" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
@@ -2310,59 +2306,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M22" t="n">
         <v>2.82</v>
       </c>
-      <c r="C22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O22" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -2394,75 +2388,75 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C23" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D23" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E23" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H23" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I23" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J23" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M23" t="n">
         <v>2.72</v>
       </c>
-      <c r="L23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N23" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O23" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2471,55 +2465,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C24" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D24" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E24" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H24" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I24" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J24" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L24" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M24" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O24" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2540,10 +2538,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2555,57 +2551,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C25" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D25" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J25" t="n">
         <v>2.68</v>
       </c>
-      <c r="E25" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K25" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L25" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N25" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O25" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2618,13 +2614,11 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2639,57 +2633,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C26" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D26" t="n">
         <v>2.71</v>
       </c>
       <c r="E26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L26" t="n">
         <v>2.75</v>
       </c>
-      <c r="F26" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M26" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N26" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O26" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2702,11 +2696,13 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2728,70 +2724,72 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C27" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D27" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E27" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F27" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I27" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J27" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L27" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M27" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O27" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2803,56 +2801,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C28" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D28" t="n">
         <v>2.66</v>
       </c>
       <c r="E28" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H28" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I28" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J28" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K28" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L28" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N28" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O28" t="n">
         <v>2.91</v>
@@ -2860,19 +2854,15 @@
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2889,68 +2879,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L29" t="n">
         <v>2.69</v>
       </c>
-      <c r="C29" t="n">
+      <c r="M29" t="n">
         <v>2.71</v>
       </c>
-      <c r="D29" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N29" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O29" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2967,81 +2965,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C30" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D30" t="n">
         <v>2.62</v>
       </c>
       <c r="E30" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H30" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J30" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K30" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L30" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M30" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N30" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O30" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3053,55 +3045,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K31" t="n">
         <v>2.63</v>
       </c>
-      <c r="C31" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="L31" t="n">
         <v>2.66</v>
       </c>
-      <c r="F31" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M31" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N31" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O31" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3114,7 +3110,7 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3122,70 +3118,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J32" t="n">
         <v>2.71</v>
       </c>
-      <c r="C32" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K32" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L32" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M32" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N32" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O32" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3196,80 +3192,78 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C33" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D33" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E33" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J33" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K33" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L33" t="n">
         <v>2.77</v>
       </c>
       <c r="M33" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N33" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O33" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,13 +3274,15 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3299,88 +3295,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C34" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D34" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L34" t="n">
         <v>2.8</v>
       </c>
-      <c r="F34" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M34" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N34" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O34" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3388,14 +3382,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C35" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D35" t="n">
         <v>2.71</v>
@@ -3404,56 +3398,54 @@
         <v>2.73</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H35" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J35" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K35" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L35" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N35" t="n">
         <v>2.8</v>
       </c>
-      <c r="M35" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>2.89</v>
       </c>
-      <c r="O35" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3465,43 +3457,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C36" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D36" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E36" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H36" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J36" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K36" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L36" t="n">
         <v>2.74</v>
@@ -3513,26 +3509,28 @@
         <v>2.8</v>
       </c>
       <c r="O36" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3545,90 +3543,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D37" t="n">
         <v>2.69</v>
       </c>
-      <c r="C37" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E37" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H37" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I37" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J37" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K37" t="n">
         <v>2.65</v>
       </c>
-      <c r="K37" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L37" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M37" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N37" t="n">
         <v>2.77</v>
       </c>
-      <c r="N37" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O37" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3636,50 +3632,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C38" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D38" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J38" t="n">
         <v>2.69</v>
       </c>
-      <c r="E38" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K38" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L38" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M38" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N38" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O38" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3697,18 +3693,14 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3720,70 +3712,72 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C39" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D39" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E39" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F39" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H39" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I39" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J39" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K39" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L39" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M39" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O39" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3795,77 +3789,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C40" t="n">
         <v>2.8</v>
       </c>
       <c r="D40" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E40" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H40" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I40" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J40" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K40" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L40" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N40" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O40" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3879,79 +3875,85 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C41" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M41" t="n">
         <v>2.8</v>
       </c>
-      <c r="D41" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L41" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M41" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N41" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O41" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3970,78 +3972,72 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2.75</v>
       </c>
       <c r="C42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M42" t="n">
         <v>2.84</v>
       </c>
-      <c r="D42" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L42" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M42" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N42" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O42" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4053,80 +4049,82 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C43" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D43" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E43" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H43" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I43" t="n">
         <v>2.59</v>
       </c>
       <c r="J43" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K43" t="n">
         <v>2.72</v>
       </c>
       <c r="L43" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M43" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N43" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O43" t="n">
         <v>2.91</v>
       </c>
-      <c r="O43" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
@@ -4135,59 +4133,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C44" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E44" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E44" t="n">
-        <v>2.84</v>
       </c>
       <c r="F44" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H44" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I44" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J44" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K44" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L44" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M44" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N44" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O44" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4208,10 +4202,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4226,47 +4218,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K45" t="n">
         <v>2.86</v>
       </c>
-      <c r="C45" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L45" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M45" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N45" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O45" t="n">
         <v>3.04</v>
@@ -4277,18 +4269,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4301,55 +4293,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C46" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E46" t="n">
         <v>2.93</v>
       </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K46" t="n">
         <v>2.84</v>
       </c>
-      <c r="E46" t="n">
+      <c r="L46" t="n">
         <v>2.89</v>
       </c>
-      <c r="F46" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M46" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N46" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O46" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4362,13 +4358,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4383,57 +4381,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C47" t="n">
         <v>2.95</v>
       </c>
       <c r="D47" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E47" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F47" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H47" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I47" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J47" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K47" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L47" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M47" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N47" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O47" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4446,15 +4444,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4476,47 +4472,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C48" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K48" t="n">
         <v>2.85</v>
       </c>
-      <c r="E48" t="n">
+      <c r="L48" t="n">
         <v>2.9</v>
       </c>
-      <c r="F48" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M48" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N48" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O48" t="n">
         <v>3.06</v>
@@ -4527,18 +4523,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4551,59 +4547,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M49" t="n">
         <v>3</v>
       </c>
-      <c r="D49" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N49" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4611,17 +4603,19 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U49" s="8" t="n">
@@ -4635,55 +4629,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C50" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N50" t="n">
         <v>3.03</v>
       </c>
-      <c r="D50" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L50" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O50" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4691,21 +4689,19 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4719,77 +4715,79 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2.93</v>
       </c>
       <c r="C51" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D51" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E51" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F51" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H51" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I51" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J51" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K51" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L51" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M51" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N51" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O51" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4803,71 +4801,69 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L52" t="n">
         <v>2.93</v>
       </c>
-      <c r="C52" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M52" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N52" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O52" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4889,57 +4885,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N53" t="n">
         <v>2.91</v>
       </c>
-      <c r="C53" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N53" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O53" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4949,12 +4945,12 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4973,57 +4969,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C54" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D54" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E54" t="n">
         <v>2.83</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H54" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J54" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K54" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L54" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M54" t="n">
         <v>2.88</v>
       </c>
       <c r="N54" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O54" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5036,9 +5032,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5057,42 +5053,42 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C55" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D55" t="n">
         <v>2.85</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J55" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E55" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.76</v>
       </c>
       <c r="K55" t="n">
         <v>2.79</v>
@@ -5101,13 +5097,13 @@
         <v>2.82</v>
       </c>
       <c r="M55" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N55" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O55" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5115,21 +5111,23 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5139,59 +5137,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D56" t="n">
         <v>2.87</v>
       </c>
-      <c r="C56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E56" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F56" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I56" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J56" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K56" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L56" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M56" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N56" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O56" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5209,13 +5203,11 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5230,29 +5222,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D57" t="n">
         <v>2.88</v>
       </c>
-      <c r="C57" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="D57" t="n">
-        <v>2.87</v>
-      </c>
       <c r="E57" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F57" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I57" t="n">
         <v>2.79</v>
@@ -5261,19 +5253,19 @@
         <v>2.84</v>
       </c>
       <c r="K57" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L57" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M57" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="N57" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5281,17 +5273,19 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">
@@ -5305,55 +5299,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="C58" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="D58" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E58" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H58" t="n">
         <v>0.1</v>
       </c>
       <c r="I58" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J58" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K58" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2.88</v>
       </c>
       <c r="L58" t="n">
         <v>2.91</v>
       </c>
       <c r="M58" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O58" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5361,14 +5359,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5389,57 +5385,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="C59" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="D59" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E59" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F59" t="n">
         <v>0.01</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="H59" t="n">
         <v>0.1</v>
       </c>
       <c r="I59" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J59" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="K59" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="L59" t="n">
         <v>2.91</v>
       </c>
       <c r="M59" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N59" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O59" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5447,18 +5443,18 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5480,65 +5476,67 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C60" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="D60" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="E60" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0261</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I60" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J60" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K60" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L60" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="M60" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="O60" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5557,85 +5555,87 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="C61" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="D61" t="n">
         <v>2.82</v>
       </c>
       <c r="E61" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.08</v>
+        <v>0.13</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0455</v>
       </c>
       <c r="H61" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I61" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="J61" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K61" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="L61" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M61" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="N61" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="O61" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -5643,57 +5643,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="C62" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="D62" t="n">
-        <v>2.82</v>
+        <v>3.17</v>
       </c>
       <c r="E62" t="n">
-        <v>2.96</v>
+        <v>3.17</v>
       </c>
       <c r="F62" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0455</v>
+        <v>0.0688</v>
       </c>
       <c r="H62" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="I62" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="J62" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K62" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L62" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="M62" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="N62" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="O62" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5716,106 +5716,18 @@
       </c>
       <c r="U62" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="D63" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="E63" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0712</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L63" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="M63" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="N63" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="O63" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="C2" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="D2" t="n">
         <v>3.16</v>
       </c>
       <c r="E2" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0296</v>
       </c>
       <c r="H2" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I2" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="J2" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>3.11</v>
       </c>
       <c r="L2" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="M2" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N2" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,21 +685,23 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -711,57 +713,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="C3" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D3" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="E3" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0296</v>
+        <v>-0.0168</v>
       </c>
       <c r="H3" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K3" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="L3" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="M3" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O3" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,23 +771,21 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -797,57 +797,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M4" t="n">
         <v>3.26</v>
       </c>
-      <c r="C4" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N4" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,7 +860,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -881,58 +881,58 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3.21</v>
       </c>
       <c r="C5" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D5" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K5" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L5" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M5" t="n">
         <v>3.23</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O5" t="n">
         <v>3.29</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
@@ -941,17 +941,19 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -963,59 +965,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C6" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D6" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E6" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I6" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K6" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N6" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O6" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1028,7 +1026,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1054,50 +1052,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C7" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D7" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E7" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H7" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J7" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K7" t="n">
         <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M7" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N7" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,19 +1105,19 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1131,76 +1129,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C8" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E8" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H8" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L8" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M8" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.33</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O8" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1208,81 +1212,73 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C9" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D9" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E9" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H9" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I9" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J9" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M9" t="n">
         <v>3.14</v>
       </c>
-      <c r="L9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N9" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O9" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1306,50 +1302,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C10" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.87</v>
       </c>
-      <c r="E10" t="n">
+      <c r="L10" t="n">
         <v>2.94</v>
       </c>
-      <c r="F10" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M10" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,7 +1358,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1386,14 +1382,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C11" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.95</v>
       </c>
       <c r="D11" t="n">
         <v>2.85</v>
@@ -1402,34 +1398,34 @@
         <v>2.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H11" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I11" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J11" t="n">
         <v>2.79</v>
       </c>
       <c r="K11" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L11" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1437,14 +1433,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1461,55 +1455,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C12" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D12" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H12" t="n">
         <v>0.08</v>
       </c>
       <c r="I12" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J12" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K12" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L12" t="n">
         <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O12" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1517,16 +1515,20 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1541,63 +1543,65 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2.92</v>
       </c>
       <c r="C13" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D13" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E13" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I13" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J13" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K13" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O13" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
@@ -1606,12 +1610,12 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1627,81 +1631,77 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C14" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D14" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E14" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H14" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.79</v>
       </c>
-      <c r="J14" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M14" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N14" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O14" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1715,76 +1715,78 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C15" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D15" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E15" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H15" t="n">
         <v>0.08</v>
       </c>
       <c r="I15" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J15" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K15" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O15" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1797,81 +1799,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C16" t="n">
         <v>2.91</v>
       </c>
       <c r="D16" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E16" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J16" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L16" t="n">
         <v>2.87</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2.9</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N16" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O16" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1883,43 +1879,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C17" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D17" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E17" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J17" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K17" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L17" t="n">
         <v>2.87</v>
@@ -1931,7 +1931,7 @@
         <v>2.93</v>
       </c>
       <c r="O17" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1952,8 +1952,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1965,57 +1967,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C18" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D18" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E18" t="n">
         <v>2.92</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H18" t="n">
         <v>0.09</v>
       </c>
       <c r="I18" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J18" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K18" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L18" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N18" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O18" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2028,7 +2030,7 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2036,10 +2038,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2051,57 +2051,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C19" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D19" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E19" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I19" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J19" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K19" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L19" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M19" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N19" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O19" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2109,18 +2109,18 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2133,72 +2133,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C20" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D20" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E20" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H20" t="n">
         <v>0.1</v>
       </c>
       <c r="I20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K20" t="n">
         <v>2.82</v>
       </c>
-      <c r="J20" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L20" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M20" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N20" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2222,67 +2222,65 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M21" t="n">
         <v>2.82</v>
       </c>
-      <c r="C21" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O21" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2306,75 +2304,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C22" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D22" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E22" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H22" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I22" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J22" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M22" t="n">
         <v>2.72</v>
       </c>
-      <c r="L22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N22" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O22" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2383,55 +2381,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C23" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D23" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E23" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H23" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I23" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J23" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L23" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M23" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O23" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2442,7 +2444,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2452,10 +2454,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2467,57 +2467,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C24" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D24" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J24" t="n">
         <v>2.68</v>
       </c>
-      <c r="E24" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K24" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L24" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N24" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O24" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2528,15 +2528,13 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2551,57 +2549,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C25" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D25" t="n">
         <v>2.71</v>
       </c>
       <c r="E25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L25" t="n">
         <v>2.75</v>
       </c>
-      <c r="F25" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M25" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N25" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O25" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2612,13 +2610,15 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2640,69 +2640,71 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C26" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D26" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E26" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F26" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I26" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J26" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L26" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M26" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N26" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O26" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2715,56 +2717,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C27" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D27" t="n">
         <v>2.66</v>
       </c>
       <c r="E27" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H27" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I27" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J27" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K27" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L27" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N27" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O27" t="n">
         <v>2.91</v>
@@ -2772,19 +2770,15 @@
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2801,68 +2795,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L28" t="n">
         <v>2.69</v>
       </c>
-      <c r="C28" t="n">
+      <c r="M28" t="n">
         <v>2.71</v>
       </c>
-      <c r="D28" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N28" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O28" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2879,81 +2881,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C29" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D29" t="n">
         <v>2.62</v>
       </c>
       <c r="E29" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J29" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K29" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L29" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N29" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O29" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2965,55 +2961,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K30" t="n">
         <v>2.63</v>
       </c>
-      <c r="C30" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="L30" t="n">
         <v>2.66</v>
       </c>
-      <c r="F30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M30" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N30" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O30" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3024,9 +3024,9 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3034,70 +3034,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J31" t="n">
         <v>2.71</v>
       </c>
-      <c r="C31" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K31" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L31" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M31" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N31" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O31" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3110,78 +3110,76 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C32" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D32" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E32" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J32" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K32" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L32" t="n">
         <v>2.77</v>
       </c>
       <c r="M32" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N32" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O32" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3194,11 +3192,13 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3211,78 +3211,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C33" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D33" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L33" t="n">
         <v>2.8</v>
       </c>
-      <c r="F33" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L33" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M33" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N33" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O33" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3290,9 +3288,9 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3300,14 +3298,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C34" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D34" t="n">
         <v>2.71</v>
@@ -3316,56 +3314,54 @@
         <v>2.73</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J34" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K34" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L34" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N34" t="n">
         <v>2.8</v>
       </c>
-      <c r="M34" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>2.89</v>
       </c>
-      <c r="O34" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3377,43 +3373,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C35" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D35" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E35" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H35" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J35" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K35" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L35" t="n">
         <v>2.74</v>
@@ -3425,27 +3425,29 @@
         <v>2.8</v>
       </c>
       <c r="O35" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3457,90 +3459,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D36" t="n">
         <v>2.69</v>
       </c>
-      <c r="C36" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E36" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I36" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K36" t="n">
         <v>2.65</v>
       </c>
-      <c r="K36" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L36" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M36" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N36" t="n">
         <v>2.77</v>
       </c>
-      <c r="N36" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O36" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3548,50 +3548,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C37" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D37" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J37" t="n">
         <v>2.69</v>
       </c>
-      <c r="E37" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K37" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L37" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M37" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N37" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3602,25 +3602,21 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3632,69 +3628,71 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C38" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D38" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E38" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F38" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H38" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I38" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J38" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K38" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L38" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M38" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N38" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O38" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3707,77 +3705,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C39" t="n">
         <v>2.8</v>
       </c>
       <c r="D39" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E39" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H39" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I39" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J39" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K39" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L39" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M39" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N39" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O39" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3791,79 +3791,85 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C40" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M40" t="n">
         <v>2.8</v>
       </c>
-      <c r="D40" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M40" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N40" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O40" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3882,78 +3888,72 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2.75</v>
       </c>
       <c r="C41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M41" t="n">
         <v>2.84</v>
       </c>
-      <c r="D41" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L41" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M41" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N41" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O41" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3965,80 +3965,82 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C42" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D42" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E42" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H42" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I42" t="n">
         <v>2.59</v>
       </c>
       <c r="J42" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K42" t="n">
         <v>2.72</v>
       </c>
       <c r="L42" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M42" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N42" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O42" t="n">
         <v>2.91</v>
       </c>
-      <c r="O42" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4047,59 +4049,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C43" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E43" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2.84</v>
       </c>
       <c r="F43" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H43" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I43" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J43" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K43" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L43" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M43" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N43" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O43" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4110,7 +4108,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4120,10 +4118,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4138,47 +4134,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K44" t="n">
         <v>2.86</v>
       </c>
-      <c r="C44" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E44" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L44" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M44" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O44" t="n">
         <v>3.04</v>
@@ -4189,18 +4185,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4213,55 +4209,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C45" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E45" t="n">
         <v>2.93</v>
       </c>
-      <c r="D45" t="n">
+      <c r="F45" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K45" t="n">
         <v>2.84</v>
       </c>
-      <c r="E45" t="n">
+      <c r="L45" t="n">
         <v>2.89</v>
       </c>
-      <c r="F45" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L45" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N45" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O45" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4276,11 +4276,13 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4295,57 +4297,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C46" t="n">
         <v>2.95</v>
       </c>
       <c r="D46" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E46" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F46" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H46" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I46" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J46" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K46" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L46" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M46" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N46" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O46" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4360,13 +4362,11 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4388,47 +4388,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C47" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K47" t="n">
         <v>2.85</v>
       </c>
-      <c r="E47" t="n">
+      <c r="L47" t="n">
         <v>2.9</v>
       </c>
-      <c r="F47" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M47" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N47" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O47" t="n">
         <v>3.06</v>
@@ -4439,18 +4439,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4463,59 +4463,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M48" t="n">
         <v>3</v>
       </c>
-      <c r="D48" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N48" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O48" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4523,17 +4519,19 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U48" s="8" t="n">
@@ -4547,55 +4545,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C49" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N49" t="n">
         <v>3.03</v>
       </c>
-      <c r="D49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M49" t="n">
-        <v>3</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O49" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4603,21 +4605,19 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4631,76 +4631,78 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>2.93</v>
       </c>
       <c r="C50" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D50" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E50" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F50" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H50" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I50" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J50" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K50" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L50" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M50" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N50" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O50" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4715,72 +4717,70 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L51" t="n">
         <v>2.93</v>
       </c>
-      <c r="C51" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M51" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N51" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O51" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4801,57 +4801,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N52" t="n">
         <v>2.91</v>
       </c>
-      <c r="C52" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O52" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4885,57 +4885,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C53" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D53" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E53" t="n">
         <v>2.83</v>
       </c>
       <c r="F53" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H53" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J53" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K53" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L53" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M53" t="n">
         <v>2.88</v>
       </c>
       <c r="N53" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O53" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4969,42 +4969,42 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C54" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D54" t="n">
         <v>2.85</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J54" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.76</v>
       </c>
       <c r="K54" t="n">
         <v>2.79</v>
@@ -5013,13 +5013,13 @@
         <v>2.82</v>
       </c>
       <c r="M54" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N54" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O54" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5027,21 +5027,23 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5051,59 +5053,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D55" t="n">
         <v>2.87</v>
       </c>
-      <c r="C55" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D55" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E55" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F55" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J55" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K55" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L55" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M55" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N55" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O55" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5114,20 +5112,18 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5142,29 +5138,29 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D56" t="n">
         <v>2.88</v>
       </c>
-      <c r="C56" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2.87</v>
-      </c>
       <c r="E56" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F56" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I56" t="n">
         <v>2.79</v>
@@ -5173,19 +5169,19 @@
         <v>2.84</v>
       </c>
       <c r="K56" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L56" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M56" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="N56" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5193,17 +5189,19 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U56" s="8" t="n">
@@ -5217,55 +5215,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="C57" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="D57" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E57" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H57" t="n">
         <v>0.1</v>
       </c>
       <c r="I57" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J57" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K57" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.88</v>
       </c>
       <c r="L57" t="n">
         <v>2.91</v>
       </c>
       <c r="M57" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O57" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5273,14 +5275,12 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
@@ -5301,57 +5301,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="C58" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="D58" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E58" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F58" t="n">
         <v>0.01</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="H58" t="n">
         <v>0.1</v>
       </c>
       <c r="I58" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J58" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="K58" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="L58" t="n">
         <v>2.91</v>
       </c>
       <c r="M58" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N58" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5359,18 +5359,18 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5392,56 +5392,58 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C59" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="D59" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="E59" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0261</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I59" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J59" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K59" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L59" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="M59" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="N59" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="O59" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
@@ -5450,7 +5452,7 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5469,85 +5471,87 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="C60" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="D60" t="n">
         <v>2.82</v>
       </c>
       <c r="E60" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.08</v>
+        <v>0.13</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0455</v>
       </c>
       <c r="H60" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I60" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="J60" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K60" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="L60" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M60" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="N60" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="O60" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
-      </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -5555,57 +5559,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="C61" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E61" t="n">
         <v>3.02</v>
       </c>
-      <c r="D61" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2.96</v>
-      </c>
       <c r="F61" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0455</v>
+        <v>0.0196</v>
       </c>
       <c r="H61" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="I61" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="J61" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K61" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L61" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="M61" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="N61" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="O61" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5616,85 +5620,77 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L62" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O62" t="n">
         <v>3.17</v>
       </c>
-      <c r="C62" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="D62" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="E62" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0688</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L62" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="M62" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="N62" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="O62" t="n">
-        <v>3.23</v>
-      </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
@@ -5704,7 +5700,7 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5716,11 +5712,13 @@
       </c>
       <c r="U62" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="C2" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D2" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="E2" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0296</v>
+        <v>-0.0168</v>
       </c>
       <c r="H2" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K2" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="L2" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="M2" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O2" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,23 +685,21 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -713,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M3" t="n">
         <v>3.26</v>
       </c>
-      <c r="C3" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N3" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -776,7 +774,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -797,58 +795,58 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3.21</v>
       </c>
       <c r="C4" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D4" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K4" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L4" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M4" t="n">
         <v>3.23</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O4" t="n">
         <v>3.29</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
@@ -857,17 +855,19 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -879,59 +879,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C5" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D5" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E5" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I5" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K5" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N5" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O5" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -944,7 +940,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -970,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C6" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D6" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E6" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H6" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I6" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J6" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K6" t="n">
         <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M6" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N6" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,19 +1019,19 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1047,76 +1043,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C7" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E7" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H7" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L7" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M7" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.33</v>
       </c>
-      <c r="N7" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O7" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1124,81 +1126,73 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C8" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D8" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E8" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J8" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K8" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M8" t="n">
         <v>3.14</v>
       </c>
-      <c r="L8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N8" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O8" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1222,50 +1216,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C9" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.87</v>
       </c>
-      <c r="E9" t="n">
+      <c r="L9" t="n">
         <v>2.94</v>
       </c>
-      <c r="F9" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M9" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1278,7 +1272,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1302,14 +1296,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C10" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2.95</v>
       </c>
       <c r="D10" t="n">
         <v>2.85</v>
@@ -1318,34 +1312,34 @@
         <v>2.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H10" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J10" t="n">
         <v>2.79</v>
       </c>
       <c r="K10" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L10" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,14 +1347,12 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1377,55 +1369,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C11" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D11" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H11" t="n">
         <v>0.08</v>
       </c>
       <c r="I11" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J11" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K11" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L11" t="n">
         <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O11" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1433,16 +1429,20 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1457,63 +1457,65 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2.92</v>
       </c>
       <c r="C12" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D12" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E12" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J12" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K12" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M12" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N12" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
@@ -1522,12 +1524,12 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1543,81 +1545,77 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C13" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D13" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E13" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H13" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.79</v>
       </c>
-      <c r="J13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L13" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N13" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1631,76 +1629,78 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C14" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D14" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E14" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H14" t="n">
         <v>0.08</v>
       </c>
       <c r="I14" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J14" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K14" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L14" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O14" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1713,81 +1713,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C15" t="n">
         <v>2.91</v>
       </c>
       <c r="D15" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E15" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J15" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L15" t="n">
         <v>2.87</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2.9</v>
       </c>
-      <c r="M15" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N15" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O15" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1799,43 +1793,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C16" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D16" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E16" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I16" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J16" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K16" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L16" t="n">
         <v>2.87</v>
@@ -1847,7 +1845,7 @@
         <v>2.93</v>
       </c>
       <c r="O16" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,7 +1858,7 @@
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1868,8 +1866,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1881,57 +1881,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C17" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D17" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E17" t="n">
         <v>2.92</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H17" t="n">
         <v>0.09</v>
       </c>
       <c r="I17" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J17" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K17" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L17" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N17" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O17" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1952,10 +1952,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1967,57 +1965,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C18" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D18" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E18" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H18" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J18" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K18" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L18" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M18" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N18" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O18" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2025,18 +2023,18 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2049,72 +2047,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C19" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D19" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E19" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H19" t="n">
         <v>0.1</v>
       </c>
       <c r="I19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.82</v>
       </c>
-      <c r="J19" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L19" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M19" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N19" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2138,67 +2136,65 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M20" t="n">
         <v>2.82</v>
       </c>
-      <c r="C20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2222,75 +2218,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C21" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D21" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E21" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H21" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I21" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J21" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M21" t="n">
         <v>2.72</v>
       </c>
-      <c r="L21" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N21" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O21" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2299,55 +2295,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C22" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D22" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E22" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H22" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I22" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J22" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L22" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M22" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O22" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,7 +2358,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2368,10 +2368,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2383,57 +2381,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D23" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J23" t="n">
         <v>2.68</v>
       </c>
-      <c r="E23" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K23" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L23" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N23" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O23" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2444,15 +2442,13 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2467,57 +2463,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C24" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D24" t="n">
         <v>2.71</v>
       </c>
       <c r="E24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L24" t="n">
         <v>2.75</v>
       </c>
-      <c r="F24" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M24" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N24" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O24" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2528,13 +2524,15 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2556,69 +2554,71 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C25" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D25" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E25" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I25" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J25" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M25" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N25" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O25" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2631,56 +2631,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C26" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D26" t="n">
         <v>2.66</v>
       </c>
       <c r="E26" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H26" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I26" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J26" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K26" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L26" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N26" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O26" t="n">
         <v>2.91</v>
@@ -2688,19 +2684,15 @@
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2717,68 +2709,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L27" t="n">
         <v>2.69</v>
       </c>
-      <c r="C27" t="n">
+      <c r="M27" t="n">
         <v>2.71</v>
       </c>
-      <c r="D27" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N27" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O27" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2795,81 +2795,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C28" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D28" t="n">
         <v>2.62</v>
       </c>
       <c r="E28" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J28" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K28" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L28" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M28" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N28" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O28" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2881,55 +2875,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K29" t="n">
         <v>2.63</v>
       </c>
-      <c r="C29" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="L29" t="n">
         <v>2.66</v>
       </c>
-      <c r="F29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M29" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N29" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O29" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,9 +2938,9 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2950,70 +2948,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J30" t="n">
         <v>2.71</v>
       </c>
-      <c r="C30" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K30" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L30" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M30" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N30" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O30" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3026,78 +3024,76 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C31" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D31" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E31" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I31" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J31" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K31" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L31" t="n">
         <v>2.77</v>
       </c>
       <c r="M31" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O31" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3110,11 +3106,13 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3127,78 +3125,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C32" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D32" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E32" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L32" t="n">
         <v>2.8</v>
       </c>
-      <c r="F32" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L32" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M32" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N32" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O32" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3206,9 +3202,9 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3216,14 +3212,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C33" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D33" t="n">
         <v>2.71</v>
@@ -3232,56 +3228,54 @@
         <v>2.73</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H33" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J33" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K33" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L33" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N33" t="n">
         <v>2.8</v>
       </c>
-      <c r="M33" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>2.89</v>
       </c>
-      <c r="O33" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3293,43 +3287,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C34" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D34" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E34" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H34" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J34" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K34" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L34" t="n">
         <v>2.74</v>
@@ -3341,27 +3339,29 @@
         <v>2.8</v>
       </c>
       <c r="O34" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3373,90 +3373,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D35" t="n">
         <v>2.69</v>
       </c>
-      <c r="C35" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E35" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H35" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I35" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K35" t="n">
         <v>2.65</v>
       </c>
-      <c r="K35" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L35" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M35" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N35" t="n">
         <v>2.77</v>
       </c>
-      <c r="N35" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O35" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3464,50 +3462,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C36" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D36" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J36" t="n">
         <v>2.69</v>
       </c>
-      <c r="E36" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K36" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L36" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M36" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N36" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O36" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3518,25 +3516,21 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3548,69 +3542,71 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C37" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D37" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E37" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F37" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H37" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I37" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J37" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K37" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L37" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M37" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O37" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3623,77 +3619,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C38" t="n">
         <v>2.8</v>
       </c>
       <c r="D38" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E38" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H38" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I38" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J38" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K38" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L38" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M38" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N38" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O38" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3707,79 +3705,85 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C39" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M39" t="n">
         <v>2.8</v>
       </c>
-      <c r="D39" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M39" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N39" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O39" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3798,78 +3802,72 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2.75</v>
       </c>
       <c r="C40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M40" t="n">
         <v>2.84</v>
       </c>
-      <c r="D40" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M40" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N40" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O40" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3881,80 +3879,82 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C41" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D41" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E41" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H41" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I41" t="n">
         <v>2.59</v>
       </c>
       <c r="J41" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K41" t="n">
         <v>2.72</v>
       </c>
       <c r="L41" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M41" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N41" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O41" t="n">
         <v>2.91</v>
       </c>
-      <c r="O41" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3963,59 +3963,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C42" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E42" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2.84</v>
       </c>
       <c r="F42" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H42" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I42" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J42" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K42" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L42" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M42" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N42" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O42" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4026,7 +4022,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4036,10 +4032,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4054,47 +4048,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K43" t="n">
         <v>2.86</v>
       </c>
-      <c r="C43" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L43" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M43" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N43" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O43" t="n">
         <v>3.04</v>
@@ -4105,18 +4099,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4129,55 +4123,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C44" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E44" t="n">
         <v>2.93</v>
       </c>
-      <c r="D44" t="n">
+      <c r="F44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K44" t="n">
         <v>2.84</v>
       </c>
-      <c r="E44" t="n">
+      <c r="L44" t="n">
         <v>2.89</v>
       </c>
-      <c r="F44" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L44" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N44" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O44" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4192,11 +4190,13 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4211,57 +4211,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C45" t="n">
         <v>2.95</v>
       </c>
       <c r="D45" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E45" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F45" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H45" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I45" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J45" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K45" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L45" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M45" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N45" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O45" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4276,13 +4276,11 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4304,47 +4302,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C46" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K46" t="n">
         <v>2.85</v>
       </c>
-      <c r="E46" t="n">
+      <c r="L46" t="n">
         <v>2.9</v>
       </c>
-      <c r="F46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M46" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N46" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O46" t="n">
         <v>3.06</v>
@@ -4355,18 +4353,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4379,59 +4377,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C47" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M47" t="n">
         <v>3</v>
       </c>
-      <c r="D47" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M47" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N47" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O47" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4439,17 +4433,19 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U47" s="8" t="n">
@@ -4463,55 +4459,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C48" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N48" t="n">
         <v>3.03</v>
       </c>
-      <c r="D48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3</v>
-      </c>
-      <c r="N48" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O48" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4519,21 +4519,19 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4547,76 +4545,78 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2.93</v>
       </c>
       <c r="C49" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D49" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E49" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F49" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H49" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I49" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J49" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K49" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L49" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M49" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N49" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O49" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4631,72 +4631,70 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L50" t="n">
         <v>2.93</v>
       </c>
-      <c r="C50" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L50" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M50" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N50" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O50" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4717,57 +4715,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N51" t="n">
         <v>2.91</v>
       </c>
-      <c r="C51" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N51" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O51" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4777,12 +4775,12 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4801,57 +4799,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C52" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D52" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E52" t="n">
         <v>2.83</v>
       </c>
       <c r="F52" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H52" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J52" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K52" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L52" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M52" t="n">
         <v>2.88</v>
       </c>
       <c r="N52" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O52" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4866,7 +4864,7 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4885,42 +4883,42 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C53" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D53" t="n">
         <v>2.85</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J53" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.76</v>
       </c>
       <c r="K53" t="n">
         <v>2.79</v>
@@ -4929,13 +4927,13 @@
         <v>2.82</v>
       </c>
       <c r="M53" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N53" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O53" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4943,21 +4941,23 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4967,59 +4967,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D54" t="n">
         <v>2.87</v>
       </c>
-      <c r="C54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E54" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I54" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J54" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K54" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L54" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M54" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N54" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O54" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5030,20 +5026,18 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5058,29 +5052,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D55" t="n">
         <v>2.88</v>
       </c>
-      <c r="C55" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="D55" t="n">
-        <v>2.87</v>
-      </c>
       <c r="E55" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F55" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I55" t="n">
         <v>2.79</v>
@@ -5089,19 +5083,19 @@
         <v>2.84</v>
       </c>
       <c r="K55" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L55" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M55" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="N55" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5109,17 +5103,19 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U55" s="8" t="n">
@@ -5133,55 +5129,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="C56" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="D56" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E56" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H56" t="n">
         <v>0.1</v>
       </c>
       <c r="I56" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J56" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K56" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2.88</v>
       </c>
       <c r="L56" t="n">
         <v>2.91</v>
       </c>
       <c r="M56" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O56" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5189,14 +5189,12 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
@@ -5217,57 +5215,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="C57" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="D57" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E57" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F57" t="n">
         <v>0.01</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="H57" t="n">
         <v>0.1</v>
       </c>
       <c r="I57" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J57" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="K57" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="L57" t="n">
         <v>2.91</v>
       </c>
       <c r="M57" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N57" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5275,18 +5273,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5308,56 +5306,58 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C58" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="D58" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="E58" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0261</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I58" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J58" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K58" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L58" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="M58" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="O58" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5385,85 +5385,87 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="C59" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="D59" t="n">
         <v>2.82</v>
       </c>
       <c r="E59" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.08</v>
+        <v>0.13</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0455</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I59" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="J59" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K59" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="L59" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M59" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="N59" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="O59" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -5471,57 +5473,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="C60" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E60" t="n">
         <v>3.02</v>
       </c>
-      <c r="D60" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E60" t="n">
-        <v>2.96</v>
-      </c>
       <c r="F60" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0455</v>
+        <v>0.0196</v>
       </c>
       <c r="H60" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="I60" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="J60" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K60" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L60" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="M60" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="N60" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="O60" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5532,84 +5534,76 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
+      </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="C61" t="n">
-        <v>3.07</v>
+        <v>3.32</v>
       </c>
       <c r="D61" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="E61" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L61" t="n">
         <v>3.02</v>
       </c>
-      <c r="F61" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J61" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K61" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L61" t="n">
-        <v>2.94</v>
-      </c>
       <c r="M61" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="N61" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O61" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5620,21 +5614,25 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
@@ -5646,50 +5644,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="C62" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="D62" t="n">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="E62" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="F62" t="n">
-        <v>0.26</v>
+        <v>-0.1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.0306</v>
       </c>
       <c r="H62" t="n">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="I62" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="J62" t="n">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="K62" t="n">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="L62" t="n">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
       <c r="M62" t="n">
-        <v>3.08</v>
+        <v>3.47</v>
       </c>
       <c r="N62" t="n">
-        <v>3.14</v>
+        <v>3.71</v>
       </c>
       <c r="O62" t="n">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5697,35 +5695,121 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M2" t="n">
         <v>3.26</v>
       </c>
-      <c r="C2" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.36</v>
-      </c>
       <c r="N2" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -711,58 +711,58 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>3.21</v>
       </c>
       <c r="C3" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D3" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K3" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L3" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M3" t="n">
         <v>3.23</v>
       </c>
-      <c r="M3" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O3" t="n">
         <v>3.29</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
@@ -771,17 +771,19 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -793,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C4" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D4" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E4" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I4" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J4" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K4" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M4" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N4" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O4" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -884,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C5" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D5" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E5" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H5" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J5" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K5" t="n">
         <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M5" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N5" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,19 +935,19 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -961,65 +959,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C6" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E6" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H6" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L6" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M6" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.33</v>
       </c>
-      <c r="N6" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
@@ -1027,10 +1033,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1038,78 +1042,70 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C7" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D7" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E7" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H7" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J7" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M7" t="n">
         <v>3.14</v>
       </c>
-      <c r="L7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N7" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O7" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
@@ -1136,50 +1132,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C8" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K8" t="n">
         <v>2.87</v>
       </c>
-      <c r="E8" t="n">
+      <c r="L8" t="n">
         <v>2.94</v>
       </c>
-      <c r="F8" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M8" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1216,14 +1212,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C9" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.95</v>
       </c>
       <c r="D9" t="n">
         <v>2.85</v>
@@ -1232,34 +1228,34 @@
         <v>2.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H9" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J9" t="n">
         <v>2.79</v>
       </c>
       <c r="K9" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L9" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M9" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1267,14 +1263,12 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1291,55 +1285,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C10" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D10" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H10" t="n">
         <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J10" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K10" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L10" t="n">
         <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O10" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1347,16 +1345,20 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1371,77 +1373,79 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2.92</v>
       </c>
       <c r="C11" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D11" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E11" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I11" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J11" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K11" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N11" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O11" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U11" s="8" t="n">
@@ -1457,81 +1461,77 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C12" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E12" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H12" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.79</v>
       </c>
-      <c r="J12" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L12" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M12" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N12" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1545,77 +1545,79 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C13" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D13" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E13" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H13" t="n">
         <v>0.08</v>
       </c>
       <c r="I13" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J13" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K13" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O13" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1627,81 +1629,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C14" t="n">
         <v>2.91</v>
       </c>
       <c r="D14" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E14" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J14" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L14" t="n">
         <v>2.87</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2.9</v>
       </c>
-      <c r="M14" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N14" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O14" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1713,43 +1709,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C15" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D15" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E15" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I15" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J15" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K15" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L15" t="n">
         <v>2.87</v>
@@ -1761,7 +1761,7 @@
         <v>2.93</v>
       </c>
       <c r="O15" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1772,9 +1772,9 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1782,8 +1782,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1795,57 +1797,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C16" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D16" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E16" t="n">
         <v>2.92</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H16" t="n">
         <v>0.09</v>
       </c>
       <c r="I16" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J16" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K16" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L16" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N16" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O16" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1856,9 +1858,9 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1866,10 +1868,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1881,57 +1881,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C17" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D17" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E17" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J17" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K17" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L17" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M17" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N17" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O17" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1939,18 +1939,18 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1963,69 +1963,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C18" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D18" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E18" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H18" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K18" t="n">
         <v>2.82</v>
       </c>
-      <c r="J18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L18" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M18" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N18" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
@@ -2052,59 +2052,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M19" t="n">
         <v>2.82</v>
       </c>
-      <c r="C19" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -2136,75 +2134,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C20" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D20" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E20" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H20" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I20" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J20" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M20" t="n">
         <v>2.72</v>
       </c>
-      <c r="L20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O20" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2213,55 +2211,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C21" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D21" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E21" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H21" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I21" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J21" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L21" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M21" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O21" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2282,10 +2284,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2297,57 +2297,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C22" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D22" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J22" t="n">
         <v>2.68</v>
       </c>
-      <c r="E22" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K22" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L22" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N22" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O22" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2360,13 +2360,11 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2381,57 +2379,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C23" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D23" t="n">
         <v>2.71</v>
       </c>
       <c r="E23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L23" t="n">
         <v>2.75</v>
       </c>
-      <c r="F23" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M23" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N23" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O23" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2444,11 +2442,13 @@
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2470,70 +2470,72 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C24" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D24" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E24" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I24" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J24" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M24" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N24" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O24" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2545,56 +2547,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C25" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D25" t="n">
         <v>2.66</v>
       </c>
       <c r="E25" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H25" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I25" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J25" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K25" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L25" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O25" t="n">
         <v>2.91</v>
@@ -2602,19 +2600,15 @@
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2631,68 +2625,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L26" t="n">
         <v>2.69</v>
       </c>
-      <c r="C26" t="n">
+      <c r="M26" t="n">
         <v>2.71</v>
       </c>
-      <c r="D26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N26" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O26" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2709,81 +2711,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C27" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D27" t="n">
         <v>2.62</v>
       </c>
       <c r="E27" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H27" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J27" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K27" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L27" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N27" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O27" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2795,55 +2791,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K28" t="n">
         <v>2.63</v>
       </c>
-      <c r="C28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="L28" t="n">
         <v>2.66</v>
       </c>
-      <c r="F28" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M28" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N28" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O28" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2864,70 +2864,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J29" t="n">
         <v>2.71</v>
       </c>
-      <c r="C29" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K29" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L29" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M29" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N29" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O29" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2938,80 +2938,78 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C30" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D30" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E30" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I30" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J30" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K30" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L30" t="n">
         <v>2.77</v>
       </c>
       <c r="M30" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N30" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O30" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3022,13 +3020,15 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3041,88 +3041,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C31" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D31" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L31" t="n">
         <v>2.8</v>
       </c>
-      <c r="F31" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M31" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N31" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O31" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="Q31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
@@ -3130,14 +3128,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C32" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D32" t="n">
         <v>2.71</v>
@@ -3146,56 +3144,54 @@
         <v>2.73</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H32" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J32" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K32" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L32" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N32" t="n">
         <v>2.8</v>
       </c>
-      <c r="M32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>2.89</v>
       </c>
-      <c r="O32" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3207,43 +3203,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C33" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D33" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E33" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H33" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J33" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K33" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L33" t="n">
         <v>2.74</v>
@@ -3255,26 +3255,28 @@
         <v>2.8</v>
       </c>
       <c r="O33" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3287,90 +3289,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D34" t="n">
         <v>2.69</v>
       </c>
-      <c r="C34" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E34" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H34" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I34" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K34" t="n">
         <v>2.65</v>
       </c>
-      <c r="K34" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L34" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N34" t="n">
         <v>2.77</v>
       </c>
-      <c r="N34" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O34" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3378,50 +3378,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C35" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J35" t="n">
         <v>2.69</v>
       </c>
-      <c r="E35" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K35" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L35" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M35" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N35" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3439,18 +3439,14 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3462,70 +3458,72 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C36" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D36" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E36" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F36" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H36" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I36" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J36" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K36" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L36" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M36" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N36" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O36" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3537,77 +3535,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C37" t="n">
         <v>2.8</v>
       </c>
       <c r="D37" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E37" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H37" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I37" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J37" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K37" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L37" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M37" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N37" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O37" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3621,79 +3621,85 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C38" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M38" t="n">
         <v>2.8</v>
       </c>
-      <c r="D38" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N38" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O38" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3712,78 +3718,72 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2.75</v>
       </c>
       <c r="C39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M39" t="n">
         <v>2.84</v>
       </c>
-      <c r="D39" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L39" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M39" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N39" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O39" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3795,80 +3795,82 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C40" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D40" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E40" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H40" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I40" t="n">
         <v>2.59</v>
       </c>
       <c r="J40" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K40" t="n">
         <v>2.72</v>
       </c>
       <c r="L40" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M40" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N40" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O40" t="n">
         <v>2.91</v>
       </c>
-      <c r="O40" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3877,59 +3879,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C41" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E41" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D41" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2.84</v>
       </c>
       <c r="F41" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H41" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I41" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J41" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K41" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L41" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M41" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N41" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O41" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3950,10 +3948,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3968,47 +3964,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K42" t="n">
         <v>2.86</v>
       </c>
-      <c r="C42" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L42" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M42" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N42" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O42" t="n">
         <v>3.04</v>
@@ -4019,18 +4015,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4043,55 +4039,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C43" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E43" t="n">
         <v>2.93</v>
       </c>
-      <c r="D43" t="n">
+      <c r="F43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K43" t="n">
         <v>2.84</v>
       </c>
-      <c r="E43" t="n">
+      <c r="L43" t="n">
         <v>2.89</v>
       </c>
-      <c r="F43" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M43" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N43" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O43" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4104,13 +4104,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4125,57 +4127,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C44" t="n">
         <v>2.95</v>
       </c>
       <c r="D44" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E44" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F44" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H44" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I44" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J44" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K44" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L44" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M44" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N44" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O44" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4188,15 +4190,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4218,47 +4218,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C45" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K45" t="n">
         <v>2.85</v>
       </c>
-      <c r="E45" t="n">
+      <c r="L45" t="n">
         <v>2.9</v>
       </c>
-      <c r="F45" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L45" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M45" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N45" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O45" t="n">
         <v>3.06</v>
@@ -4269,18 +4269,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4293,59 +4293,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M46" t="n">
         <v>3</v>
       </c>
-      <c r="D46" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N46" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O46" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4353,17 +4349,19 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U46" s="8" t="n">
@@ -4377,55 +4375,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C47" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N47" t="n">
         <v>3.03</v>
       </c>
-      <c r="D47" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3</v>
-      </c>
-      <c r="N47" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O47" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4433,21 +4435,19 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4461,77 +4461,79 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>2.93</v>
       </c>
       <c r="C48" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D48" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E48" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F48" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H48" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I48" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J48" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K48" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L48" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M48" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N48" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O48" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="Q48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4545,71 +4547,69 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L49" t="n">
         <v>2.93</v>
       </c>
-      <c r="C49" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M49" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N49" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O49" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4631,57 +4631,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N50" t="n">
         <v>2.91</v>
       </c>
-      <c r="C50" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L50" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O50" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4715,57 +4715,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C51" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D51" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E51" t="n">
         <v>2.83</v>
       </c>
       <c r="F51" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H51" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J51" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K51" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L51" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M51" t="n">
         <v>2.88</v>
       </c>
       <c r="N51" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O51" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4778,9 +4778,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4799,42 +4799,42 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C52" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D52" t="n">
         <v>2.85</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J52" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.76</v>
       </c>
       <c r="K52" t="n">
         <v>2.79</v>
@@ -4843,13 +4843,13 @@
         <v>2.82</v>
       </c>
       <c r="M52" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N52" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O52" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4857,21 +4857,23 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4881,59 +4883,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D53" t="n">
         <v>2.87</v>
       </c>
-      <c r="C53" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E53" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J53" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K53" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L53" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M53" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N53" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O53" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4951,13 +4949,11 @@
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4972,29 +4968,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D54" t="n">
         <v>2.88</v>
       </c>
-      <c r="C54" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2.87</v>
-      </c>
       <c r="E54" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F54" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I54" t="n">
         <v>2.79</v>
@@ -5003,19 +4999,19 @@
         <v>2.84</v>
       </c>
       <c r="K54" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L54" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M54" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="N54" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5023,17 +5019,19 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U54" s="8" t="n">
@@ -5047,55 +5045,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="C55" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="D55" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E55" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H55" t="n">
         <v>0.1</v>
       </c>
       <c r="I55" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J55" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K55" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.88</v>
       </c>
       <c r="L55" t="n">
         <v>2.91</v>
       </c>
       <c r="M55" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O55" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5103,14 +5105,12 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
@@ -5131,57 +5131,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="C56" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="D56" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E56" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F56" t="n">
         <v>0.01</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="H56" t="n">
         <v>0.1</v>
       </c>
       <c r="I56" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J56" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="K56" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="L56" t="n">
         <v>2.91</v>
       </c>
       <c r="M56" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N56" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5189,18 +5189,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5222,65 +5222,67 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C57" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="D57" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="E57" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="F57" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0261</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I57" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J57" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K57" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L57" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="M57" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="O57" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5299,85 +5301,87 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="C58" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="D58" t="n">
         <v>2.82</v>
       </c>
       <c r="E58" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.08</v>
+        <v>0.13</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0455</v>
       </c>
       <c r="H58" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I58" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="J58" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K58" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="L58" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M58" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="N58" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="O58" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -5385,57 +5389,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="C59" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E59" t="n">
         <v>3.02</v>
       </c>
-      <c r="D59" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E59" t="n">
-        <v>2.96</v>
-      </c>
       <c r="F59" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0455</v>
+        <v>0.0196</v>
       </c>
       <c r="H59" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="I59" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="J59" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K59" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L59" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="M59" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="N59" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="O59" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5453,77 +5457,69 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
+      </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="C60" t="n">
-        <v>3.07</v>
+        <v>3.32</v>
       </c>
       <c r="D60" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="E60" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L60" t="n">
         <v>3.02</v>
       </c>
-      <c r="F60" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I60" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K60" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L60" t="n">
-        <v>2.94</v>
-      </c>
       <c r="M60" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="N60" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O60" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5541,14 +5537,18 @@
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
@@ -5560,50 +5560,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="C61" t="n">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="D61" t="n">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="E61" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F61" t="n">
-        <v>0.27</v>
+        <v>-0.1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0906</v>
+        <v>-0.0306</v>
       </c>
       <c r="H61" t="n">
-        <v>0.34</v>
+        <v>0.14</v>
       </c>
       <c r="I61" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="J61" t="n">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="K61" t="n">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="L61" t="n">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
       <c r="M61" t="n">
-        <v>3.08</v>
+        <v>3.47</v>
       </c>
       <c r="N61" t="n">
-        <v>3.14</v>
+        <v>3.71</v>
       </c>
       <c r="O61" t="n">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5611,83 +5611,83 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="C62" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="D62" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="E62" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0306</v>
+        <v>-0.0153</v>
       </c>
       <c r="H62" t="n">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="I62" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="J62" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="K62" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="L62" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="M62" t="n">
-        <v>3.47</v>
+        <v>3.27</v>
       </c>
       <c r="N62" t="n">
-        <v>3.71</v>
+        <v>3.36</v>
       </c>
       <c r="O62" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5722,92 +5722,6 @@
       <c r="X62" t="inlineStr">
         <is>
           <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="C63" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="D63" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="E63" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0091</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="J63" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="K63" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L63" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="M63" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N63" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="O63" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,51 +634,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>3.21</v>
       </c>
       <c r="C2" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="D2" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0153</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="K2" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="L2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M2" t="n">
         <v>3.23</v>
       </c>
-      <c r="M2" t="n">
-        <v>3.26</v>
-      </c>
       <c r="N2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O2" t="n">
         <v>3.29</v>
       </c>
-      <c r="O2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
@@ -687,17 +687,19 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -709,59 +711,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C3" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D3" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E3" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I3" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J3" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K3" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M3" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N3" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O3" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,7 +772,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -800,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C4" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D4" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E4" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H4" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I4" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J4" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K4" t="n">
         <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M4" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N4" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,19 +851,19 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -877,76 +875,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C5" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E5" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H5" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I5" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L5" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.33</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O5" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -954,81 +958,73 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C6" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D6" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E6" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H6" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I6" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J6" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M6" t="n">
         <v>3.14</v>
       </c>
-      <c r="L6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N6" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O6" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1052,50 +1048,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C7" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K7" t="n">
         <v>2.87</v>
       </c>
-      <c r="E7" t="n">
+      <c r="L7" t="n">
         <v>2.94</v>
       </c>
-      <c r="F7" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M7" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,7 +1104,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1132,14 +1128,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C8" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2.95</v>
       </c>
       <c r="D8" t="n">
         <v>2.85</v>
@@ -1148,34 +1144,34 @@
         <v>2.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H8" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J8" t="n">
         <v>2.79</v>
       </c>
       <c r="K8" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L8" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1183,14 +1179,12 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1207,55 +1201,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C9" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D9" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H9" t="n">
         <v>0.08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J9" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K9" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L9" t="n">
         <v>2.9</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O9" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1263,16 +1261,20 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1287,63 +1289,65 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2.92</v>
       </c>
       <c r="C10" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D10" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E10" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I10" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J10" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K10" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N10" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O10" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
@@ -1352,12 +1356,12 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U10" s="8" t="n">
@@ -1373,81 +1377,77 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C11" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E11" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H11" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.79</v>
       </c>
-      <c r="J11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L11" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M11" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N11" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O11" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1461,76 +1461,78 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C12" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D12" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E12" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H12" t="n">
         <v>0.08</v>
       </c>
       <c r="I12" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J12" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1543,81 +1545,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C13" t="n">
         <v>2.91</v>
       </c>
       <c r="D13" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E13" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J13" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L13" t="n">
         <v>2.87</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2.9</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N13" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O13" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1629,43 +1625,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C14" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D14" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E14" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J14" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K14" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L14" t="n">
         <v>2.87</v>
@@ -1677,7 +1677,7 @@
         <v>2.93</v>
       </c>
       <c r="O14" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
@@ -1698,8 +1698,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1711,57 +1713,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C15" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D15" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E15" t="n">
         <v>2.92</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H15" t="n">
         <v>0.09</v>
       </c>
       <c r="I15" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J15" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K15" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L15" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O15" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1774,7 +1776,7 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1782,10 +1784,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1797,57 +1797,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C16" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D16" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E16" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H16" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J16" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K16" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L16" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M16" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N16" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1855,18 +1855,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1879,72 +1879,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C17" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D17" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E17" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H17" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K17" t="n">
         <v>2.82</v>
       </c>
-      <c r="J17" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L17" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M17" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N17" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1968,67 +1968,65 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M18" t="n">
         <v>2.82</v>
       </c>
-      <c r="C18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O18" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2052,75 +2050,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C19" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D19" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E19" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H19" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J19" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M19" t="n">
         <v>2.72</v>
       </c>
-      <c r="L19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O19" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2129,55 +2127,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C20" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D20" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E20" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H20" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I20" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J20" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L20" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M20" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,7 +2190,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2198,10 +2200,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2213,57 +2213,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C21" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D21" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J21" t="n">
         <v>2.68</v>
       </c>
-      <c r="E21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K21" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L21" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N21" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O21" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,15 +2274,13 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2297,57 +2295,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C22" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D22" t="n">
         <v>2.71</v>
       </c>
       <c r="E22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L22" t="n">
         <v>2.75</v>
       </c>
-      <c r="F22" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M22" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N22" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O22" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,13 +2356,15 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2386,69 +2386,71 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C23" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D23" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E23" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I23" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J23" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M23" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N23" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O23" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2461,56 +2463,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C24" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D24" t="n">
         <v>2.66</v>
       </c>
       <c r="E24" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H24" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I24" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J24" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K24" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L24" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O24" t="n">
         <v>2.91</v>
@@ -2518,19 +2516,15 @@
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2547,68 +2541,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L25" t="n">
         <v>2.69</v>
       </c>
-      <c r="C25" t="n">
+      <c r="M25" t="n">
         <v>2.71</v>
       </c>
-      <c r="D25" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N25" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O25" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2625,81 +2627,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C26" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D26" t="n">
         <v>2.62</v>
       </c>
       <c r="E26" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H26" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J26" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K26" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L26" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M26" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N26" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O26" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2711,55 +2707,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K27" t="n">
         <v>2.63</v>
       </c>
-      <c r="C27" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="L27" t="n">
         <v>2.66</v>
       </c>
-      <c r="F27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M27" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N27" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O27" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2770,9 +2770,9 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2780,70 +2780,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J28" t="n">
         <v>2.71</v>
       </c>
-      <c r="C28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K28" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L28" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M28" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N28" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O28" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2856,78 +2856,76 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C29" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D29" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E29" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H29" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J29" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K29" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L29" t="n">
         <v>2.77</v>
       </c>
       <c r="M29" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N29" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,11 +2938,13 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2957,78 +2957,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C30" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D30" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L30" t="n">
         <v>2.8</v>
       </c>
-      <c r="F30" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M30" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O30" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3036,9 +3034,9 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3046,14 +3044,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C31" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D31" t="n">
         <v>2.71</v>
@@ -3062,56 +3060,54 @@
         <v>2.73</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H31" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J31" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K31" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N31" t="n">
         <v>2.8</v>
       </c>
-      <c r="M31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>2.89</v>
       </c>
-      <c r="O31" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3123,43 +3119,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C32" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D32" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E32" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H32" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J32" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K32" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L32" t="n">
         <v>2.74</v>
@@ -3171,27 +3171,29 @@
         <v>2.8</v>
       </c>
       <c r="O32" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3203,90 +3205,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D33" t="n">
         <v>2.69</v>
       </c>
-      <c r="C33" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E33" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I33" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K33" t="n">
         <v>2.65</v>
       </c>
-      <c r="K33" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L33" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N33" t="n">
         <v>2.77</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O33" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3294,50 +3294,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C34" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D34" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J34" t="n">
         <v>2.69</v>
       </c>
-      <c r="E34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K34" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L34" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M34" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N34" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3348,25 +3348,21 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3378,69 +3374,71 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C35" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D35" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E35" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F35" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H35" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I35" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J35" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K35" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L35" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M35" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O35" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3453,77 +3451,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C36" t="n">
         <v>2.8</v>
       </c>
       <c r="D36" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E36" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H36" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I36" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J36" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K36" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L36" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M36" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N36" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O36" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3537,79 +3537,85 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C37" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M37" t="n">
         <v>2.8</v>
       </c>
-      <c r="D37" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N37" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O37" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3628,78 +3634,72 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>2.75</v>
       </c>
       <c r="C38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M38" t="n">
         <v>2.84</v>
       </c>
-      <c r="D38" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N38" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O38" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3711,80 +3711,82 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C39" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D39" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E39" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H39" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I39" t="n">
         <v>2.59</v>
       </c>
       <c r="J39" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K39" t="n">
         <v>2.72</v>
       </c>
       <c r="L39" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M39" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N39" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O39" t="n">
         <v>2.91</v>
       </c>
-      <c r="O39" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3793,59 +3795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C40" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E40" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D40" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2.84</v>
       </c>
       <c r="F40" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H40" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I40" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J40" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K40" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L40" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M40" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N40" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O40" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3856,7 +3854,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3866,10 +3864,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3884,47 +3880,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K41" t="n">
         <v>2.86</v>
       </c>
-      <c r="C41" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D41" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L41" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M41" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N41" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O41" t="n">
         <v>3.04</v>
@@ -3935,18 +3931,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3959,55 +3955,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C42" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E42" t="n">
         <v>2.93</v>
       </c>
-      <c r="D42" t="n">
+      <c r="F42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K42" t="n">
         <v>2.84</v>
       </c>
-      <c r="E42" t="n">
+      <c r="L42" t="n">
         <v>2.89</v>
       </c>
-      <c r="F42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L42" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M42" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N42" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O42" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4022,11 +4022,13 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4041,57 +4043,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C43" t="n">
         <v>2.95</v>
       </c>
       <c r="D43" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E43" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H43" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I43" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J43" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K43" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L43" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M43" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N43" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O43" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4106,13 +4108,11 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4134,47 +4134,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C44" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K44" t="n">
         <v>2.85</v>
       </c>
-      <c r="E44" t="n">
+      <c r="L44" t="n">
         <v>2.9</v>
       </c>
-      <c r="F44" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L44" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M44" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N44" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O44" t="n">
         <v>3.06</v>
@@ -4185,18 +4185,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4209,59 +4209,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M45" t="n">
         <v>3</v>
       </c>
-      <c r="D45" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N45" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O45" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4269,17 +4265,19 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U45" s="8" t="n">
@@ -4293,55 +4291,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C46" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N46" t="n">
         <v>3.03</v>
       </c>
-      <c r="D46" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O46" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4349,21 +4351,19 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4377,76 +4377,78 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2.93</v>
       </c>
       <c r="C47" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D47" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E47" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F47" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H47" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I47" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J47" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K47" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L47" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M47" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N47" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O47" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4461,72 +4463,70 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L48" t="n">
         <v>2.93</v>
       </c>
-      <c r="C48" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M48" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N48" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O48" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4547,57 +4547,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N49" t="n">
         <v>2.91</v>
       </c>
-      <c r="C49" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O49" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4631,57 +4631,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C50" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D50" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E50" t="n">
         <v>2.83</v>
       </c>
       <c r="F50" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H50" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J50" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K50" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L50" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M50" t="n">
         <v>2.88</v>
       </c>
       <c r="N50" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O50" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4715,42 +4715,42 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C51" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D51" t="n">
         <v>2.85</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J51" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.76</v>
       </c>
       <c r="K51" t="n">
         <v>2.79</v>
@@ -4759,13 +4759,13 @@
         <v>2.82</v>
       </c>
       <c r="M51" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N51" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O51" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4773,21 +4773,23 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4797,59 +4799,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D52" t="n">
         <v>2.87</v>
       </c>
-      <c r="C52" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E52" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F52" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J52" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K52" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L52" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M52" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N52" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O52" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4860,20 +4858,18 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4888,29 +4884,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D53" t="n">
         <v>2.88</v>
       </c>
-      <c r="C53" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2.87</v>
-      </c>
       <c r="E53" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F53" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I53" t="n">
         <v>2.79</v>
@@ -4919,19 +4915,19 @@
         <v>2.84</v>
       </c>
       <c r="K53" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L53" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M53" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="N53" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4939,17 +4935,19 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U53" s="8" t="n">
@@ -4963,55 +4961,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="C54" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="D54" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E54" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H54" t="n">
         <v>0.1</v>
       </c>
       <c r="I54" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J54" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K54" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.88</v>
       </c>
       <c r="L54" t="n">
         <v>2.91</v>
       </c>
       <c r="M54" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O54" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5019,14 +5021,12 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
@@ -5047,57 +5047,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="C55" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="D55" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E55" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F55" t="n">
         <v>0.01</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="H55" t="n">
         <v>0.1</v>
       </c>
       <c r="I55" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J55" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="K55" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="L55" t="n">
         <v>2.91</v>
       </c>
       <c r="M55" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N55" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5105,18 +5105,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5138,56 +5138,58 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C56" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="D56" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="E56" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="F56" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0261</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I56" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J56" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K56" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L56" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="M56" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="O56" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
@@ -5196,7 +5198,7 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5215,85 +5217,87 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="C57" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="D57" t="n">
         <v>2.82</v>
       </c>
       <c r="E57" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.08</v>
+        <v>0.13</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0455</v>
       </c>
       <c r="H57" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I57" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="J57" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K57" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="L57" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M57" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="N57" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="O57" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -5301,57 +5305,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="C58" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E58" t="n">
         <v>3.02</v>
       </c>
-      <c r="D58" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2.96</v>
-      </c>
       <c r="F58" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0455</v>
+        <v>0.0196</v>
       </c>
       <c r="H58" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="I58" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="J58" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K58" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L58" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="M58" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="N58" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="O58" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5362,84 +5366,76 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="C59" t="n">
-        <v>3.07</v>
+        <v>3.32</v>
       </c>
       <c r="D59" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="E59" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L59" t="n">
         <v>3.02</v>
       </c>
-      <c r="F59" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I59" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L59" t="n">
-        <v>2.94</v>
-      </c>
       <c r="M59" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="N59" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O59" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5450,21 +5446,25 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
@@ -5476,50 +5476,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="C60" t="n">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="D60" t="n">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="E60" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F60" t="n">
-        <v>0.27</v>
+        <v>-0.1</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0906</v>
+        <v>-0.0306</v>
       </c>
       <c r="H60" t="n">
-        <v>0.34</v>
+        <v>0.14</v>
       </c>
       <c r="I60" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="J60" t="n">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="K60" t="n">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="L60" t="n">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
       <c r="M60" t="n">
-        <v>3.08</v>
+        <v>3.47</v>
       </c>
       <c r="N60" t="n">
-        <v>3.14</v>
+        <v>3.71</v>
       </c>
       <c r="O60" t="n">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5527,98 +5527,102 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="C61" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="D61" t="n">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="E61" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0306</v>
+        <v>-0.0613</v>
       </c>
       <c r="H61" t="n">
         <v>0.14</v>
       </c>
       <c r="I61" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="J61" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="K61" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="L61" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="M61" t="n">
-        <v>3.47</v>
+        <v>3.27</v>
       </c>
       <c r="N61" t="n">
-        <v>3.71</v>
+        <v>3.36</v>
       </c>
       <c r="O61" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+        <v>3.38</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5630,64 +5634,60 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>3.15</v>
       </c>
       <c r="C62" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="D62" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="E62" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.005</v>
       </c>
       <c r="H62" t="n">
         <v>0.01</v>
       </c>
       <c r="I62" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="J62" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="L62" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M62" t="n">
         <v>3.07</v>
       </c>
-      <c r="K62" t="n">
+      <c r="N62" t="n">
         <v>3.12</v>
       </c>
-      <c r="L62" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="M62" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N62" t="n">
-        <v>3.36</v>
-      </c>
       <c r="O62" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5695,14 +5695,12 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5714,9 +5712,9 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="D2" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="E2" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0062</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I2" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="K2" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L2" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M2" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="N2" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="O2" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -716,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C3" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D3" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E3" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I3" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J3" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K3" t="n">
         <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M3" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N3" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,19 +769,19 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -793,65 +793,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C4" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E4" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H4" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L4" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N4" t="n">
         <v>3.33</v>
       </c>
-      <c r="N4" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O4" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
@@ -859,10 +867,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -870,78 +876,70 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C5" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D5" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E5" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H5" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M5" t="n">
         <v>3.14</v>
       </c>
-      <c r="L5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N5" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O5" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
@@ -968,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C6" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K6" t="n">
         <v>2.87</v>
       </c>
-      <c r="E6" t="n">
+      <c r="L6" t="n">
         <v>2.94</v>
       </c>
-      <c r="F6" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M6" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N6" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1048,14 +1046,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C7" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2.95</v>
       </c>
       <c r="D7" t="n">
         <v>2.85</v>
@@ -1064,34 +1062,34 @@
         <v>2.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H7" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J7" t="n">
         <v>2.79</v>
       </c>
       <c r="K7" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L7" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1099,14 +1097,12 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1123,55 +1119,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C8" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D8" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H8" t="n">
         <v>0.08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J8" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K8" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L8" t="n">
         <v>2.9</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O8" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1179,16 +1179,20 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1203,77 +1207,79 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2.92</v>
       </c>
       <c r="C9" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D9" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E9" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I9" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J9" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M9" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O9" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U9" s="8" t="n">
@@ -1289,81 +1295,77 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C10" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E10" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H10" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.79</v>
       </c>
-      <c r="J10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L10" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M10" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N10" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O10" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1377,77 +1379,79 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C11" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D11" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E11" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H11" t="n">
         <v>0.08</v>
       </c>
       <c r="I11" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J11" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O11" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1459,81 +1463,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C12" t="n">
         <v>2.91</v>
       </c>
       <c r="D12" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E12" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L12" t="n">
         <v>2.87</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2.9</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N12" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O12" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1545,43 +1543,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C13" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D13" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E13" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J13" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K13" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L13" t="n">
         <v>2.87</v>
@@ -1593,7 +1595,7 @@
         <v>2.93</v>
       </c>
       <c r="O13" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1604,9 +1606,9 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
@@ -1614,8 +1616,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1627,57 +1631,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C14" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D14" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E14" t="n">
         <v>2.92</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H14" t="n">
         <v>0.09</v>
       </c>
       <c r="I14" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J14" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K14" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L14" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O14" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1688,9 +1692,9 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
@@ -1698,10 +1702,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1713,57 +1715,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C15" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D15" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E15" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J15" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K15" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L15" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N15" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O15" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,18 +1773,18 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1795,69 +1797,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C16" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D16" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E16" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
       </c>
       <c r="I16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K16" t="n">
         <v>2.82</v>
       </c>
-      <c r="J16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L16" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M16" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N16" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O16" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
@@ -1884,59 +1886,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M17" t="n">
         <v>2.82</v>
       </c>
-      <c r="C17" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O17" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -1968,75 +1968,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C18" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D18" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E18" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H18" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I18" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J18" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M18" t="n">
         <v>2.72</v>
       </c>
-      <c r="L18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N18" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O18" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2045,55 +2045,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C19" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D19" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E19" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H19" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I19" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J19" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L19" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M19" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O19" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2114,10 +2118,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2129,57 +2131,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C20" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J20" t="n">
         <v>2.68</v>
       </c>
-      <c r="E20" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K20" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L20" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N20" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O20" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2192,13 +2194,11 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2213,57 +2213,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D21" t="n">
         <v>2.71</v>
       </c>
       <c r="E21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L21" t="n">
         <v>2.75</v>
       </c>
-      <c r="F21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M21" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N21" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O21" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,11 +2276,13 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2302,70 +2304,72 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C22" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D22" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E22" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F22" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I22" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J22" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M22" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N22" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O22" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2377,56 +2381,52 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C23" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D23" t="n">
         <v>2.66</v>
       </c>
       <c r="E23" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H23" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I23" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J23" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K23" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L23" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O23" t="n">
         <v>2.91</v>
@@ -2434,19 +2434,15 @@
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2463,68 +2459,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L24" t="n">
         <v>2.69</v>
       </c>
-      <c r="C24" t="n">
+      <c r="M24" t="n">
         <v>2.71</v>
       </c>
-      <c r="D24" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N24" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O24" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2541,81 +2545,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C25" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D25" t="n">
         <v>2.62</v>
       </c>
       <c r="E25" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H25" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J25" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K25" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L25" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N25" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O25" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2627,55 +2625,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K26" t="n">
         <v>2.63</v>
       </c>
-      <c r="C26" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="L26" t="n">
         <v>2.66</v>
       </c>
-      <c r="F26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M26" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N26" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O26" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2688,7 +2690,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2696,70 +2698,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J27" t="n">
         <v>2.71</v>
       </c>
-      <c r="C27" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K27" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L27" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M27" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N27" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O27" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2770,80 +2772,78 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C28" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D28" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E28" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J28" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K28" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L28" t="n">
         <v>2.77</v>
       </c>
       <c r="M28" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N28" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2854,13 +2854,15 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2873,88 +2875,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C29" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D29" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L29" t="n">
         <v>2.8</v>
       </c>
-      <c r="F29" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M29" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O29" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
+      <c r="Q29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2962,14 +2962,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C30" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D30" t="n">
         <v>2.71</v>
@@ -2978,56 +2978,54 @@
         <v>2.73</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H30" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J30" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K30" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N30" t="n">
         <v>2.8</v>
       </c>
-      <c r="M30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>2.89</v>
       </c>
-      <c r="O30" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3039,43 +3037,47 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C31" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D31" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E31" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H31" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J31" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K31" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L31" t="n">
         <v>2.74</v>
@@ -3087,26 +3089,28 @@
         <v>2.8</v>
       </c>
       <c r="O31" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3119,90 +3123,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D32" t="n">
         <v>2.69</v>
       </c>
-      <c r="C32" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E32" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I32" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K32" t="n">
         <v>2.65</v>
       </c>
-      <c r="K32" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L32" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M32" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N32" t="n">
         <v>2.77</v>
       </c>
-      <c r="N32" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O32" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3210,50 +3212,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C33" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D33" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J33" t="n">
         <v>2.69</v>
       </c>
-      <c r="E33" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K33" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L33" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M33" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N33" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3271,18 +3273,14 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3294,70 +3292,72 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C34" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D34" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E34" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F34" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H34" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I34" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J34" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K34" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L34" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M34" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N34" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O34" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3369,77 +3369,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C35" t="n">
         <v>2.8</v>
       </c>
       <c r="D35" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E35" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H35" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I35" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J35" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K35" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L35" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M35" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N35" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O35" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3453,79 +3455,85 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C36" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M36" t="n">
         <v>2.8</v>
       </c>
-      <c r="D36" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N36" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O36" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3544,78 +3552,72 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2.75</v>
       </c>
       <c r="C37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M37" t="n">
         <v>2.84</v>
       </c>
-      <c r="D37" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L37" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N37" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O37" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3627,80 +3629,82 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C38" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D38" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E38" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H38" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I38" t="n">
         <v>2.59</v>
       </c>
       <c r="J38" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K38" t="n">
         <v>2.72</v>
       </c>
       <c r="L38" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M38" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N38" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O38" t="n">
         <v>2.91</v>
       </c>
-      <c r="O38" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3709,59 +3713,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C39" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E39" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2.84</v>
       </c>
       <c r="F39" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H39" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I39" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J39" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K39" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L39" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M39" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O39" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3782,10 +3782,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3800,47 +3798,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K40" t="n">
         <v>2.86</v>
       </c>
-      <c r="C40" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D40" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L40" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N40" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O40" t="n">
         <v>3.04</v>
@@ -3851,18 +3849,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3875,55 +3873,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E41" t="n">
         <v>2.93</v>
       </c>
-      <c r="D41" t="n">
+      <c r="F41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K41" t="n">
         <v>2.84</v>
       </c>
-      <c r="E41" t="n">
+      <c r="L41" t="n">
         <v>2.89</v>
       </c>
-      <c r="F41" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L41" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M41" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N41" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O41" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3936,13 +3938,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3957,57 +3961,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C42" t="n">
         <v>2.95</v>
       </c>
       <c r="D42" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E42" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H42" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I42" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J42" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K42" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L42" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M42" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N42" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O42" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4020,15 +4024,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4050,47 +4052,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C43" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K43" t="n">
         <v>2.85</v>
       </c>
-      <c r="E43" t="n">
+      <c r="L43" t="n">
         <v>2.9</v>
       </c>
-      <c r="F43" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M43" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N43" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O43" t="n">
         <v>3.06</v>
@@ -4101,18 +4103,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4125,59 +4127,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M44" t="n">
         <v>3</v>
       </c>
-      <c r="D44" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E44" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N44" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4185,17 +4183,19 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U44" s="8" t="n">
@@ -4209,55 +4209,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C45" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N45" t="n">
         <v>3.03</v>
       </c>
-      <c r="D45" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L45" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O45" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4265,21 +4269,19 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4293,77 +4295,79 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2.93</v>
       </c>
       <c r="C46" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D46" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E46" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F46" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H46" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I46" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J46" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K46" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L46" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M46" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N46" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O46" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4377,71 +4381,69 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L47" t="n">
         <v>2.93</v>
       </c>
-      <c r="C47" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M47" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N47" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O47" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4463,57 +4465,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N48" t="n">
         <v>2.91</v>
       </c>
-      <c r="C48" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N48" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O48" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4523,12 +4525,12 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4547,57 +4549,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C49" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D49" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E49" t="n">
         <v>2.83</v>
       </c>
       <c r="F49" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H49" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J49" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K49" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L49" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M49" t="n">
         <v>2.88</v>
       </c>
       <c r="N49" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O49" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4610,9 +4612,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4631,42 +4633,42 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C50" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D50" t="n">
         <v>2.85</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J50" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.76</v>
       </c>
       <c r="K50" t="n">
         <v>2.79</v>
@@ -4675,13 +4677,13 @@
         <v>2.82</v>
       </c>
       <c r="M50" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N50" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O50" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4689,21 +4691,23 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4713,59 +4717,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D51" t="n">
         <v>2.87</v>
       </c>
-      <c r="C51" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E51" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F51" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J51" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K51" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L51" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M51" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N51" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O51" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4783,13 +4783,11 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4804,29 +4802,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D52" t="n">
         <v>2.88</v>
       </c>
-      <c r="C52" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.87</v>
-      </c>
       <c r="E52" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F52" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I52" t="n">
         <v>2.79</v>
@@ -4835,19 +4833,19 @@
         <v>2.84</v>
       </c>
       <c r="K52" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L52" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M52" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="N52" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4855,17 +4853,19 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U52" s="8" t="n">
@@ -4879,55 +4879,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="C53" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="D53" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E53" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H53" t="n">
         <v>0.1</v>
       </c>
       <c r="I53" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J53" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K53" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.88</v>
       </c>
       <c r="L53" t="n">
         <v>2.91</v>
       </c>
       <c r="M53" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="N53" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O53" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4935,14 +4939,12 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
@@ -4963,57 +4965,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="C54" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="D54" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E54" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F54" t="n">
         <v>0.01</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="H54" t="n">
         <v>0.1</v>
       </c>
       <c r="I54" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J54" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="K54" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="L54" t="n">
         <v>2.91</v>
       </c>
       <c r="M54" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5021,18 +5023,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5054,65 +5056,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C55" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="D55" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="E55" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="F55" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0261</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I55" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J55" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K55" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L55" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="M55" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="O55" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5131,85 +5135,87 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="C56" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="D56" t="n">
         <v>2.82</v>
       </c>
       <c r="E56" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.08</v>
+        <v>0.13</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0455</v>
       </c>
       <c r="H56" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I56" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="J56" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K56" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="L56" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M56" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="N56" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="O56" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -5217,57 +5223,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="C57" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E57" t="n">
         <v>3.02</v>
       </c>
-      <c r="D57" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E57" t="n">
-        <v>2.96</v>
-      </c>
       <c r="F57" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0455</v>
+        <v>0.0196</v>
       </c>
       <c r="H57" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="I57" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="J57" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K57" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L57" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="M57" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="N57" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="O57" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5285,77 +5291,69 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="C58" t="n">
-        <v>3.07</v>
+        <v>3.32</v>
       </c>
       <c r="D58" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="E58" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L58" t="n">
         <v>3.02</v>
       </c>
-      <c r="F58" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.94</v>
-      </c>
       <c r="M58" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="N58" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O58" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5373,14 +5371,18 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5392,50 +5394,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="C59" t="n">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="D59" t="n">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="E59" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F59" t="n">
-        <v>0.27</v>
+        <v>-0.1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0906</v>
+        <v>-0.0306</v>
       </c>
       <c r="H59" t="n">
-        <v>0.34</v>
+        <v>0.14</v>
       </c>
       <c r="I59" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="J59" t="n">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="K59" t="n">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="L59" t="n">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
       <c r="M59" t="n">
-        <v>3.08</v>
+        <v>3.47</v>
       </c>
       <c r="N59" t="n">
-        <v>3.14</v>
+        <v>3.71</v>
       </c>
       <c r="O59" t="n">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5443,89 +5445,93 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="C60" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="D60" t="n">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="E60" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0306</v>
+        <v>-0.0613</v>
       </c>
       <c r="H60" t="n">
         <v>0.14</v>
       </c>
       <c r="I60" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="J60" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="K60" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="L60" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="M60" t="n">
-        <v>3.47</v>
+        <v>3.27</v>
       </c>
       <c r="N60" t="n">
-        <v>3.71</v>
+        <v>3.36</v>
       </c>
       <c r="O60" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+        <v>3.38</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
@@ -5534,7 +5540,7 @@
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5546,91 +5552,85 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W60" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="C61" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="D61" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2</v>
+        <v>0.01</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0613</v>
+        <v>0.0037</v>
       </c>
       <c r="H61" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I61" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="J61" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="L61" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M61" t="n">
         <v>3.07</v>
       </c>
-      <c r="K61" t="n">
+      <c r="N61" t="n">
         <v>3.12</v>
       </c>
-      <c r="L61" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="M61" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N61" t="n">
-        <v>3.36</v>
-      </c>
       <c r="O61" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
+        <v>3.25</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
@@ -5639,55 +5639,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="C62" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="D62" t="n">
         <v>3.01</v>
       </c>
       <c r="E62" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.02</v>
+        <v>-0</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0007</v>
       </c>
       <c r="H62" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I62" t="n">
         <v>2.84</v>
       </c>
       <c r="J62" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K62" t="n">
         <v>2.93</v>
       </c>
       <c r="L62" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="M62" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="N62" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="O62" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5719,7 +5723,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5658,19 +5658,19 @@
         <v>3.06</v>
       </c>
       <c r="D62" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="E62" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="F62" t="n">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.005</v>
       </c>
       <c r="H62" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="I62" t="n">
         <v>2.84</v>
@@ -5726,6 +5726,88 @@
           <t>弱警訊</t>
         </is>
       </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="C2" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D2" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="E2" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H2" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="J2" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K2" t="n">
         <v>3.2</v>
       </c>
       <c r="L2" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="M2" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="N2" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -687,19 +687,19 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -711,76 +711,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C3" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E3" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H3" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I3" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L3" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N3" t="n">
         <v>3.33</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O3" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -788,81 +794,73 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C4" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D4" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E4" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H4" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J4" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M4" t="n">
         <v>3.14</v>
       </c>
-      <c r="L4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N4" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O4" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -876,7 +874,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -886,50 +884,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C5" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K5" t="n">
         <v>2.87</v>
       </c>
-      <c r="E5" t="n">
+      <c r="L5" t="n">
         <v>2.94</v>
       </c>
-      <c r="F5" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M5" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,7 +940,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -956,7 +954,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -966,14 +964,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C6" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2.95</v>
       </c>
       <c r="D6" t="n">
         <v>2.85</v>
@@ -982,34 +980,34 @@
         <v>2.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J6" t="n">
         <v>2.79</v>
       </c>
       <c r="K6" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L6" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,14 +1015,12 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1036,60 +1032,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C7" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D7" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H7" t="n">
         <v>0.08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J7" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K7" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L7" t="n">
         <v>2.9</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O7" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1097,16 +1097,20 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1114,70 +1118,72 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2.92</v>
       </c>
       <c r="C8" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D8" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E8" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I8" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J8" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K8" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M8" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N8" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O8" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
@@ -1186,12 +1192,12 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1200,171 +1206,169 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C9" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D9" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E9" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H9" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.79</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L9" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N9" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O9" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C10" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D10" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E10" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H10" t="n">
         <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J10" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L10" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O10" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1372,134 +1376,132 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C11" t="n">
         <v>2.91</v>
       </c>
       <c r="D11" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E11" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J11" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L11" t="n">
         <v>2.87</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2.9</v>
       </c>
-      <c r="M11" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N11" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O11" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C12" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D12" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E12" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I12" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J12" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K12" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L12" t="n">
         <v>2.87</v>
@@ -1511,7 +1513,7 @@
         <v>2.93</v>
       </c>
       <c r="O12" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1522,9 +1524,9 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
@@ -1532,70 +1534,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C13" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D13" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E13" t="n">
         <v>2.92</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H13" t="n">
         <v>0.09</v>
       </c>
       <c r="I13" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J13" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K13" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L13" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O13" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1608,7 +1612,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
@@ -1616,72 +1620,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C14" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D14" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E14" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H14" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J14" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K14" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L14" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N14" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O14" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,18 +1691,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1708,77 +1710,77 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C15" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D15" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E15" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
       </c>
       <c r="I15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K15" t="n">
         <v>2.82</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L15" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M15" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N15" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1792,7 +1794,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1802,67 +1804,65 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M16" t="n">
         <v>2.82</v>
       </c>
-      <c r="C16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N16" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1876,7 +1876,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1886,132 +1886,136 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C17" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D17" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E17" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H17" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I17" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J17" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M17" t="n">
         <v>2.72</v>
       </c>
-      <c r="L17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N17" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O17" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C18" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D18" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E18" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H18" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J18" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L18" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M18" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O18" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2022,7 +2026,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2032,72 +2036,70 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J19" t="n">
         <v>2.68</v>
       </c>
-      <c r="E19" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K19" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L19" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N19" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O19" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2108,15 +2110,13 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2124,64 +2124,64 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D20" t="n">
         <v>2.71</v>
       </c>
       <c r="E20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L20" t="n">
         <v>2.75</v>
       </c>
-      <c r="F20" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M20" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N20" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O20" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2192,13 +2192,15 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2206,7 +2208,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2220,69 +2222,71 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C21" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D21" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E21" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F21" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I21" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J21" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M21" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N21" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O21" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2290,61 +2294,57 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C22" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D22" t="n">
         <v>2.66</v>
       </c>
       <c r="E22" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H22" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I22" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J22" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K22" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L22" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M22" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O22" t="n">
         <v>2.91</v>
@@ -2352,19 +2352,15 @@
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2376,73 +2372,81 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L23" t="n">
         <v>2.69</v>
       </c>
-      <c r="C23" t="n">
+      <c r="M23" t="n">
         <v>2.71</v>
       </c>
-      <c r="D23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N23" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O23" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2454,146 +2458,144 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C24" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D24" t="n">
         <v>2.62</v>
       </c>
       <c r="E24" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H24" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J24" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K24" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L24" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M24" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N24" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O24" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K25" t="n">
         <v>2.63</v>
       </c>
-      <c r="C25" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="L25" t="n">
         <v>2.66</v>
       </c>
-      <c r="F25" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M25" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N25" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O25" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2604,9 +2606,9 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2614,70 +2616,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J26" t="n">
         <v>2.71</v>
       </c>
-      <c r="C26" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K26" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L26" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M26" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N26" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2690,78 +2692,76 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C27" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D27" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E27" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J27" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K27" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L27" t="n">
         <v>2.77</v>
       </c>
       <c r="M27" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O27" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2772,13 +2772,15 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="S27" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2791,78 +2793,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C28" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D28" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L28" t="n">
         <v>2.8</v>
       </c>
-      <c r="F28" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M28" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O28" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2870,9 +2870,9 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W28" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2880,14 +2880,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C29" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D29" t="n">
         <v>2.71</v>
@@ -2896,104 +2896,106 @@
         <v>2.73</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J29" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K29" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N29" t="n">
         <v>2.8</v>
       </c>
-      <c r="M29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>2.89</v>
       </c>
-      <c r="O29" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C30" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D30" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E30" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H30" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J30" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K30" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L30" t="n">
         <v>2.74</v>
@@ -3005,122 +3007,122 @@
         <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="Q30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D31" t="n">
         <v>2.69</v>
       </c>
-      <c r="C31" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E31" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I31" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K31" t="n">
         <v>2.65</v>
       </c>
-      <c r="K31" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L31" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N31" t="n">
         <v>2.77</v>
       </c>
-      <c r="N31" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O31" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
@@ -3128,50 +3130,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C32" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D32" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J32" t="n">
         <v>2.69</v>
       </c>
-      <c r="E32" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K32" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L32" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M32" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N32" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3182,25 +3184,21 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3212,69 +3210,71 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C33" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D33" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E33" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H33" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I33" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J33" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K33" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L33" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M33" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O33" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3287,77 +3287,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C34" t="n">
         <v>2.8</v>
       </c>
       <c r="D34" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E34" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I34" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J34" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K34" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L34" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M34" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N34" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O34" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3371,79 +3373,85 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C35" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M35" t="n">
         <v>2.8</v>
       </c>
-      <c r="D35" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N35" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O35" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3462,78 +3470,72 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>2.75</v>
       </c>
       <c r="C36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M36" t="n">
         <v>2.84</v>
       </c>
-      <c r="D36" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N36" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O36" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3545,80 +3547,82 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C37" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D37" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E37" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H37" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I37" t="n">
         <v>2.59</v>
       </c>
       <c r="J37" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K37" t="n">
         <v>2.72</v>
       </c>
       <c r="L37" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M37" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N37" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O37" t="n">
         <v>2.91</v>
       </c>
-      <c r="O37" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3627,59 +3631,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C38" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E38" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.84</v>
       </c>
       <c r="F38" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H38" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I38" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J38" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K38" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L38" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M38" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N38" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O38" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3690,7 +3690,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3700,10 +3700,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3718,47 +3716,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K39" t="n">
         <v>2.86</v>
       </c>
-      <c r="C39" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L39" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M39" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O39" t="n">
         <v>3.04</v>
@@ -3769,18 +3767,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3793,55 +3791,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E40" t="n">
         <v>2.93</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K40" t="n">
         <v>2.84</v>
       </c>
-      <c r="E40" t="n">
+      <c r="L40" t="n">
         <v>2.89</v>
       </c>
-      <c r="F40" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M40" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N40" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O40" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3854,13 +3856,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="S40" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3875,57 +3879,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C41" t="n">
         <v>2.95</v>
       </c>
       <c r="D41" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E41" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F41" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H41" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I41" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J41" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K41" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L41" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M41" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N41" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O41" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3940,13 +3944,11 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3968,47 +3970,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C42" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K42" t="n">
         <v>2.85</v>
       </c>
-      <c r="E42" t="n">
+      <c r="L42" t="n">
         <v>2.9</v>
       </c>
-      <c r="F42" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L42" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M42" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N42" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O42" t="n">
         <v>3.06</v>
@@ -4019,18 +4021,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4043,59 +4045,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M43" t="n">
         <v>3</v>
       </c>
-      <c r="D43" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N43" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O43" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4103,17 +4101,19 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U43" s="8" t="n">
@@ -4127,55 +4127,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C44" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N44" t="n">
         <v>3.03</v>
       </c>
-      <c r="D44" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E44" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L44" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3</v>
-      </c>
-      <c r="N44" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O44" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4183,21 +4187,19 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4211,76 +4213,78 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2.93</v>
       </c>
       <c r="C45" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D45" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E45" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F45" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H45" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I45" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J45" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K45" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L45" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M45" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N45" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O45" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4295,72 +4299,70 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L46" t="n">
         <v>2.93</v>
       </c>
-      <c r="C46" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>-0.0198</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2.96</v>
-      </c>
       <c r="M46" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N46" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O46" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4381,57 +4383,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N47" t="n">
         <v>2.91</v>
       </c>
-      <c r="C47" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>-0.0322</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M47" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N47" t="n">
-        <v>3.06</v>
-      </c>
       <c r="O47" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4441,12 +4443,12 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4465,57 +4467,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C48" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="D48" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="E48" t="n">
         <v>2.83</v>
       </c>
       <c r="F48" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0011</v>
       </c>
       <c r="H48" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J48" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K48" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="L48" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="M48" t="n">
         <v>2.88</v>
       </c>
       <c r="N48" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="O48" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4528,9 +4530,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S48" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4549,42 +4551,42 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="C49" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D49" t="n">
         <v>2.85</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J49" t="n">
         <v>2.77</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.76</v>
       </c>
       <c r="K49" t="n">
         <v>2.79</v>
@@ -4593,13 +4595,13 @@
         <v>2.82</v>
       </c>
       <c r="M49" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N49" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="O49" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4607,21 +4609,23 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4631,59 +4635,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D50" t="n">
         <v>2.87</v>
       </c>
-      <c r="C50" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2.85</v>
-      </c>
       <c r="E50" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F50" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.023</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="J50" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="K50" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L50" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="M50" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N50" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="O50" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4694,20 +4694,18 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4722,29 +4720,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D51" t="n">
         <v>2.88</v>
       </c>
-      <c r="C51" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2.87</v>
-      </c>
       <c r="E51" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="F51" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I51" t="n">
         <v>2.79</v>
@@ -4753,19 +4751,19 @@
         <v>2.84</v>
       </c>
       <c r="K51" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L51" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M51" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="N51" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4773,17 +4771,19 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U51" s="8" t="n">
@@ -4797,55 +4797,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="C52" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="D52" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="E52" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H52" t="n">
         <v>0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J52" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K52" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.88</v>
       </c>
       <c r="L52" t="n">
         <v>2.91</v>
       </c>
       <c r="M52" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O52" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4853,14 +4857,12 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4881,57 +4883,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="C53" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="D53" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E53" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F53" t="n">
         <v>0.01</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="H53" t="n">
         <v>0.1</v>
       </c>
       <c r="I53" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J53" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="K53" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="L53" t="n">
         <v>2.91</v>
       </c>
       <c r="M53" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N53" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4939,18 +4941,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="S53" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4972,56 +4974,58 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="C54" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="D54" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="E54" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0261</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I54" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J54" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K54" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L54" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="O54" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5030,7 +5034,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5049,85 +5053,87 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="C55" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="D55" t="n">
         <v>2.82</v>
       </c>
       <c r="E55" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.08</v>
+        <v>0.13</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0455</v>
       </c>
       <c r="H55" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I55" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="J55" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K55" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="L55" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M55" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="N55" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="O55" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -5135,57 +5141,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="C56" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E56" t="n">
         <v>3.02</v>
       </c>
-      <c r="D56" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2.96</v>
-      </c>
       <c r="F56" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0455</v>
+        <v>0.0196</v>
       </c>
       <c r="H56" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="I56" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="J56" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K56" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="L56" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="M56" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="N56" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="O56" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5196,84 +5202,76 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="C57" t="n">
-        <v>3.07</v>
+        <v>3.32</v>
       </c>
       <c r="D57" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="E57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L57" t="n">
         <v>3.02</v>
       </c>
-      <c r="F57" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L57" t="n">
-        <v>2.94</v>
-      </c>
       <c r="M57" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="N57" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O57" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5284,21 +5282,25 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5310,50 +5312,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="C58" t="n">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="D58" t="n">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="E58" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F58" t="n">
-        <v>0.27</v>
+        <v>-0.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0906</v>
+        <v>-0.0306</v>
       </c>
       <c r="H58" t="n">
-        <v>0.34</v>
+        <v>0.14</v>
       </c>
       <c r="I58" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="J58" t="n">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="K58" t="n">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="L58" t="n">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
       <c r="M58" t="n">
-        <v>3.08</v>
+        <v>3.47</v>
       </c>
       <c r="N58" t="n">
-        <v>3.14</v>
+        <v>3.71</v>
       </c>
       <c r="O58" t="n">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5361,98 +5363,102 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="C59" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="D59" t="n">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="E59" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0306</v>
+        <v>-0.0613</v>
       </c>
       <c r="H59" t="n">
         <v>0.14</v>
       </c>
       <c r="I59" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="J59" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="K59" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="L59" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="M59" t="n">
-        <v>3.47</v>
+        <v>3.27</v>
       </c>
       <c r="N59" t="n">
-        <v>3.71</v>
+        <v>3.36</v>
       </c>
       <c r="O59" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+        <v>3.38</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5464,148 +5470,146 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W59" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="C60" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="D60" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2</v>
+        <v>0.01</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0613</v>
+        <v>0.0037</v>
       </c>
       <c r="H60" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I60" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="J60" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="L60" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M60" t="n">
         <v>3.07</v>
       </c>
-      <c r="K60" t="n">
+      <c r="N60" t="n">
         <v>3.12</v>
       </c>
-      <c r="L60" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N60" t="n">
-        <v>3.36</v>
-      </c>
       <c r="O60" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
+        <v>3.25</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="C61" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="E61" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.005</v>
       </c>
       <c r="H61" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="I61" t="n">
         <v>2.84</v>
       </c>
       <c r="J61" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K61" t="n">
         <v>2.93</v>
       </c>
       <c r="L61" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="M61" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="N61" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="O61" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5616,82 +5620,78 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="C62" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="D62" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E62" t="n">
         <v>2.97</v>
       </c>
-      <c r="E62" t="n">
-        <v>3.03</v>
-      </c>
       <c r="F62" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0195</v>
       </c>
       <c r="H62" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="J62" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="K62" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="L62" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="M62" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="N62" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="O62" t="n">
-        <v>3.31</v>
+        <v>3.15</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5699,12 +5699,14 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5716,98 +5718,182 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W62" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2.95</v>
       </c>
       <c r="C63" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="D63" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="E63" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0248</v>
+        <v>0.0229</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="I63" t="n">
         <v>2.87</v>
       </c>
       <c r="J63" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="K63" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="L63" t="n">
         <v>2.98</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
+        <v>3</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
         <v>3.02</v>
       </c>
-      <c r="M63" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="N63" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="O63" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="C64" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L64" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NG_daily.xlsx
+++ b/three_gate/analysis/NG_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,60 +634,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="C2" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="E2" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0623</v>
       </c>
       <c r="H2" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I2" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="L2" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="M2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N2" t="n">
         <v>3.33</v>
       </c>
-      <c r="N2" t="n">
-        <v>3.41</v>
-      </c>
       <c r="O2" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>3.51</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -695,10 +699,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -708,78 +710,70 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="C3" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="D3" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="E3" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J3" t="n">
-        <v>3.03</v>
+        <v>2.71</v>
       </c>
       <c r="K3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M3" t="n">
         <v>3.14</v>
       </c>
-      <c r="L3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N3" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="O3" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -794,7 +788,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -804,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="C4" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="D4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K4" t="n">
         <v>2.87</v>
       </c>
-      <c r="E4" t="n">
+      <c r="L4" t="n">
         <v>2.94</v>
       </c>
-      <c r="F4" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3.06</v>
-      </c>
       <c r="M4" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -874,7 +868,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -884,14 +878,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C5" t="n">
         <v>2.93</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2.95</v>
       </c>
       <c r="D5" t="n">
         <v>2.85</v>
@@ -900,34 +894,34 @@
         <v>2.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0024</v>
       </c>
       <c r="H5" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="J5" t="n">
         <v>2.79</v>
       </c>
       <c r="K5" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L5" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,14 +929,12 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -954,60 +946,64 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="C6" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D6" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0069</v>
       </c>
       <c r="H6" t="n">
         <v>0.08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="J6" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="K6" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="L6" t="n">
         <v>2.9</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O6" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,16 +1011,20 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1032,84 +1032,86 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2.92</v>
       </c>
       <c r="C7" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="D7" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="E7" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0226</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I7" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="J7" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="M7" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="N7" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O7" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1118,306 +1120,302 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="C8" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="E8" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0185</v>
       </c>
       <c r="H8" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="I8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K8" t="n">
         <v>2.79</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.89</v>
-      </c>
       <c r="L8" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="M8" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="N8" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="O8" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="10" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="C9" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="D9" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="E9" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="H9" t="n">
         <v>0.08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J9" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="L9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M9" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="O9" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="C10" t="n">
         <v>2.91</v>
       </c>
       <c r="D10" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E10" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0017</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="J10" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L10" t="n">
         <v>2.87</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>2.9</v>
       </c>
-      <c r="M10" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N10" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="O10" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="C11" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="D11" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="E11" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0209</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I11" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="J11" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="K11" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L11" t="n">
         <v>2.87</v>
@@ -1429,7 +1427,7 @@
         <v>2.93</v>
       </c>
       <c r="O11" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,9 +1438,9 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
@@ -1450,70 +1448,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="C12" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="D12" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="E12" t="n">
         <v>2.92</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0031</v>
       </c>
       <c r="H12" t="n">
         <v>0.09</v>
       </c>
       <c r="I12" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J12" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="K12" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L12" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N12" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="O12" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1524,9 +1524,9 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
@@ -1534,72 +1534,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="C13" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D13" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="E13" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0154</v>
       </c>
       <c r="H13" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J13" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K13" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L13" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1607,18 +1605,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1626,74 +1624,74 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="C14" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="D14" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="E14" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0362</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>
       </c>
       <c r="I14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.82</v>
       </c>
-      <c r="J14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.87</v>
-      </c>
       <c r="L14" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="M14" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N14" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+        <v>3.06</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
@@ -1710,7 +1708,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="10" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1720,66 +1718,64 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M15" t="n">
         <v>2.82</v>
       </c>
-      <c r="C15" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2.92</v>
-      </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>2.94</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1794,7 +1790,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="10" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1804,132 +1800,136 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="C16" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D16" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E16" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H16" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I16" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="J16" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M16" t="n">
         <v>2.72</v>
       </c>
-      <c r="L16" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2.82</v>
-      </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O16" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="10" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="C17" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="D17" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E17" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.0121</v>
       </c>
       <c r="H17" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="J17" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L17" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M17" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="O17" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,7 +1940,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1950,72 +1950,70 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="10" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="C18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D18" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J18" t="n">
         <v>2.68</v>
       </c>
-      <c r="E18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K18" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="L18" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N18" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O18" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2026,15 +2024,13 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2042,64 +2038,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="10" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="D19" t="n">
         <v>2.71</v>
       </c>
       <c r="E19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L19" t="n">
         <v>2.75</v>
       </c>
-      <c r="F19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.74</v>
-      </c>
       <c r="M19" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="N19" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="O19" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2110,13 +2106,15 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2124,7 +2122,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="10" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2138,131 +2136,129 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="C20" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="D20" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="E20" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0356</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I20" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="J20" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="M20" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="N20" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="10" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="C21" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="D21" t="n">
         <v>2.66</v>
       </c>
       <c r="E21" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0356</v>
+        <v>0.0022</v>
       </c>
       <c r="H21" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I21" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J21" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="K21" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="L21" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="O21" t="n">
         <v>2.91</v>
@@ -2270,19 +2266,15 @@
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2294,73 +2286,81 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="10" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L22" t="n">
         <v>2.69</v>
       </c>
-      <c r="C22" t="n">
+      <c r="M22" t="n">
         <v>2.71</v>
       </c>
-      <c r="D22" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N22" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O22" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2372,146 +2372,144 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="10" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="C23" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D23" t="n">
         <v>2.62</v>
       </c>
       <c r="E23" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0083</v>
       </c>
       <c r="H23" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="J23" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="K23" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L23" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="M23" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N23" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O23" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="10" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K24" t="n">
         <v>2.63</v>
       </c>
-      <c r="C24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="L24" t="n">
         <v>2.66</v>
       </c>
-      <c r="F24" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M24" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O24" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2522,9 +2520,9 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2532,70 +2530,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J25" t="n">
         <v>2.71</v>
       </c>
-      <c r="C25" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.59</v>
-      </c>
       <c r="K25" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L25" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="M25" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N25" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O25" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2606,80 +2604,78 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="C26" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="D26" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E26" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0134</v>
       </c>
       <c r="H26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="J26" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="K26" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L26" t="n">
         <v>2.77</v>
       </c>
       <c r="M26" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="O26" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2690,13 +2686,15 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2704,84 +2702,82 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C27" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="D27" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="E27" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L27" t="n">
         <v>2.8</v>
       </c>
-      <c r="F27" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M27" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="O27" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2790,7 +2786,7 @@
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2798,14 +2794,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="C28" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D28" t="n">
         <v>2.71</v>
@@ -2814,104 +2810,106 @@
         <v>2.73</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0275</v>
+        <v>0.0022</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J28" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K28" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="L28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N28" t="n">
         <v>2.8</v>
       </c>
-      <c r="M28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>2.89</v>
       </c>
-      <c r="O28" t="n">
-        <v>2.91</v>
-      </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="10" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="C29" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="D29" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E29" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0157</v>
       </c>
       <c r="H29" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J29" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="K29" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L29" t="n">
         <v>2.74</v>
@@ -2923,26 +2921,28 @@
         <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2950,95 +2950,93 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="10" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D30" t="n">
         <v>2.69</v>
       </c>
-      <c r="C30" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2.64</v>
-      </c>
       <c r="E30" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0157</v>
+        <v>0.032</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I30" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="J30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K30" t="n">
         <v>2.65</v>
       </c>
-      <c r="K30" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L30" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="M30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N30" t="n">
         <v>2.77</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3046,50 +3044,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="C31" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="D31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J31" t="n">
         <v>2.69</v>
       </c>
-      <c r="E31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K31" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="L31" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="M31" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="N31" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3100,27 +3098,23 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="11" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3130,243 +3124,253 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="C32" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="D32" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="E32" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="F32" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0137</v>
+        <v>-0.0288</v>
       </c>
       <c r="H32" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I32" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J32" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="K32" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L32" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="M32" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O32" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="C33" t="n">
         <v>2.8</v>
       </c>
       <c r="D33" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="E33" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0288</v>
+        <v>0.0146</v>
       </c>
       <c r="H33" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J33" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="K33" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="L33" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="M33" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N33" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O33" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C34" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M34" t="n">
         <v>2.8</v>
       </c>
-      <c r="D34" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N34" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="O34" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3380,224 +3384,216 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>2.75</v>
       </c>
       <c r="C35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M35" t="n">
         <v>2.84</v>
       </c>
-      <c r="D35" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N35" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="O35" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="C36" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="D36" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="E36" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.026</v>
       </c>
       <c r="H36" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I36" t="n">
         <v>2.59</v>
       </c>
       <c r="J36" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="K36" t="n">
         <v>2.72</v>
       </c>
       <c r="L36" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="M36" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N36" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O36" t="n">
         <v>2.91</v>
       </c>
-      <c r="O36" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="C37" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E37" t="n">
         <v>2.91</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2.84</v>
       </c>
       <c r="F37" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.026</v>
+        <v>0.0229</v>
       </c>
       <c r="H37" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I37" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="J37" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K37" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L37" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="M37" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="O37" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3608,7 +3604,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="11" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3618,15 +3614,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3636,47 +3630,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K38" t="n">
         <v>2.86</v>
       </c>
-      <c r="C38" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2.78</v>
-      </c>
       <c r="L38" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="O38" t="n">
         <v>3.04</v>
@@ -3687,18 +3681,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3706,60 +3700,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="C39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E39" t="n">
         <v>2.93</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K39" t="n">
         <v>2.84</v>
       </c>
-      <c r="E39" t="n">
+      <c r="L39" t="n">
         <v>2.89</v>
       </c>
-      <c r="F39" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>-0.0065</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L39" t="n">
-        <v>2.9</v>
-      </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N39" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="O39" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3772,13 +3770,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3786,64 +3786,64 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="C40" t="n">
         <v>2.95</v>
       </c>
       <c r="D40" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="E40" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F40" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="H40" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I40" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J40" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="K40" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L40" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="M40" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="N40" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="O40" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3856,15 +3856,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3872,7 +3870,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3886,47 +3884,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C41" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K41" t="n">
         <v>2.85</v>
       </c>
-      <c r="E41" t="n">
+      <c r="L41" t="n">
         <v>2.9</v>
       </c>
-      <c r="F41" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L41" t="n">
-        <v>2.91</v>
-      </c>
       <c r="M41" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N41" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="O41" t="n">
         <v>3.06</v>
@@ -3937,18 +3935,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3956,64 +3954,60 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C42" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M42" t="n">
         <v>3</v>
       </c>
-      <c r="D42" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L42" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M42" t="n">
-        <v>2.96</v>
-      </c>
       <c r="N42" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4021,17 +4015,19 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4040,60 +4036,64 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="C43" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N43" t="n">
         <v>3.03</v>
       </c>
-      <c r="D43" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3</v>
-      </c>
-      <c r="N43" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O43" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4101,183 +4101,181 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2.93</v>
       </c>
       <c r="C44" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="D44" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E44" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="F44" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0198</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I44" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J44" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="K44" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="L44" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="M44" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N44" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="O44" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+  